--- a/ot/output/통합_OT보안위협_매트릭스_v2.xlsx
+++ b/ot/output/통합_OT보안위협_매트릭스_v2.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>고유 기법 22/111개 작성 — 나머지는 ATT&amp;CK 원문 첫 문장(회색, '작성 예정')</t>
+          <t>고유 기법 48/111개 작성 — 나머지는 ATT&amp;CK 원문 첫 문장(회색, '작성 예정')</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>◆ OTC-PV-05 시스템 서비스 생성·변조 [9]</t>
+          <t>◆ OTC-PV-03 예약 작업 [7]</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>OTC-DS-01 네트워크 연결 열거 [8]</t>
+          <t>OTC-DS-01 네트워크 연결 열거 [7]</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>OTC-IR-02 데이터 파괴 [13]</t>
+          <t>OTC-IR-02 데이터 파괴 [11]</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>OTC-IA-12 원격 서비스 악용 [10]</t>
+          <t>OTC-IA-12 원격 서비스 악용 [9]</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>◆ OTC-PV-03 예약 작업 [7]</t>
+          <t>◆ OTC-PV-05 시스템 서비스 생성·변조 [7]</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>OTC-EV-02 위장 [11]</t>
+          <t>OTC-EV-02 위장 [10]</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>◆ OTC-IM-13 데이터 암호화(랜섬웨어) [15]</t>
+          <t>◆ OTC-IM-13 데이터 암호화(랜섬웨어) [14]</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>◆ OTC-PE-08 시스템 서비스 생성·변조 [9]</t>
+          <t>◆ OTC-PE-06 예약 작업 [7]</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>OTC-DS-03.1 포트 스캔 [5]</t>
+          <t>OTC-DS-05 원격 시스템 정보 탐색 [5]</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>OTC-LM-04 내부 도구 전송 [12]</t>
+          <t>OTC-LM-04 내부 도구 전송 [11]</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>OTC-CO-06 화면 캡처 [4]</t>
+          <t>OTC-CO-11 로컬 시스템 데이터 수집 [4]</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>OTC-IA-10 원격 서비스 취약점 악용 [8]</t>
+          <t>OTC-IA-09 스피어피싱 첨부파일 [7]</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>◆ OTC-PE-06 예약 작업 [7]</t>
+          <t>◆ OTC-PE-08 시스템 서비스 생성·변조 [7]</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2042,27 +2042,27 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>◆ OTC-EV-09 보안 도구 무력화 [7]</t>
+          <t>◆ OTC-EV-09 보안 도구 무력화 [6]</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>OTC-DS-05 원격 시스템 정보 탐색 [5]</t>
+          <t>OTC-DS-02 네트워크 스니핑 [3]</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>OTC-LM-05 원격 서비스 악용 [10]</t>
+          <t>OTC-LM-05 원격 서비스 악용 [9]</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>OTC-CO-11 로컬 시스템 데이터 수집 [4]</t>
+          <t>OTC-CO-02 자동 수집 [3]</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>OTC-IR-09 서비스 중지 [5]</t>
+          <t>OTC-IR-12.1 시스템 펌웨어 변조 [5]</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>OTC-IA-09 스피어피싱 첨부파일 [7]</t>
+          <t>OTC-IA-10 원격 서비스 취약점 악용 [7]</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -2109,22 +2109,22 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>OTC-DS-02 네트워크 스니핑 [3]</t>
+          <t>OTC-DS-03.1 포트 스캔 [3]</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>◆ OTC-LM-07 OS·저장 자격증명 탈취 [9]</t>
+          <t>◆ OTC-LM-07 OS·저장 자격증명 탈취 [8]</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>OTC-CO-02 자동 수집 [3]</t>
+          <t>OTC-CO-06 화면 캡처 [3]</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>OTC-IR-12.1 시스템 펌웨어 변조 [5]</t>
+          <t>OTC-IR-09 서비스 중지 [4]</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>OTC-EX-04 네이티브 API 악용 [4]</t>
+          <t>OTC-EX-05 스크립트 실행 [4]</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>OTC-LM-03 원격 서비스 취약점 악용 [8]</t>
+          <t>OTC-LM-03 원격 서비스 취약점 악용 [7]</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>OTC-EX-05 스크립트 실행 [4]</t>
+          <t>OTC-EX-04 네이티브 API 악용 [3]</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>OTC-IM-06 감시 상실 [11]</t>
+          <t>OTC-IM-06 감시 상실 [10]</t>
         </is>
       </c>
     </row>
@@ -3546,12 +3546,23 @@
           <t>드라이브바이 침해</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may gain access to a system during a drive-by compromise, when a user visits a website as part of a regular browsing session.</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr"/>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 종사자·협력업체가 자주 찾는 업계·공급업체 웹사이트를 침해해(워터링 홀), 방문한 업무 단말에 악성코드를 내려받게 할 수 있음
+- 정상 업무 사이트 방문만으로 감염되고 특정 업계 종사자를 골라 노릴 수 있으며, 이렇게 확보한 자격증명·단말이 이후 OT 접근의 발판이 됨</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 엔지니어·운영자의 업무용 워크스테이션과 원격 접속 단말 — 인터넷을 쓰는 단말이 OT 접근 권한을 함께 가진 경우 위험이 큼 (L3~L4)
+- 수법: 에너지 업계 사이트에 리디렉션 iframe 삽입(Dragonfly), 산업 종사자 대상 워터링 홀(TEMP.Veles·ALLANITE), 정상 사이트의 가짜 Flash 설치 파일(Bad Rabbit)
+- 통합: Enterprise 드라이브바이 침해(T1189)
+■ 실제 사례
+- [실제 사고] Dragonfly 2.0(2018-03): 에너지 업계 대상 워터링 홀과 스피어피싱으로 자격증명을 모으고 제어 시스템 정보에 접근 (INC-036)
+- [실제 사고] Bad Rabbit(2017-10): 침해된 웹사이트의 가짜 Flash 설치 파일로 퍼져 우크라이나 교통 기관 시스템을 암호화 (INC-017, ATT&amp;CK S0606)</t>
+        </is>
+      </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
           <t>T0817</t>
@@ -3574,7 +3585,7 @@
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L10" s="17" t="inlineStr">
@@ -3675,7 +3686,16 @@
           <t>https://attack.mitre.org/techniques/T0817</t>
         </is>
       </c>
-      <c r="AM10" s="17" t="inlineStr"/>
+      <c r="AM10" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹 프록시·IDS로 알려진 악성 스크립트·리디렉션과 브라우저 하위 프로세스 생성 탐지
+- 업무 단말에서 OT 영역으로 향하는 새로운 접속을 경보
+■ 대응
+- OT 접근 단말에서 인터넷 사용을 분리(점프 호스트·전용 단말)하고 브라우저 격리·익스플로잇 보호 적용
+- 웹 필터링과 브라우저·플러그인의 신속한 업데이트</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -3698,12 +3718,24 @@
           <t>공개 애플리케이션 취약점 악용</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage weaknesses to exploit internet-facing software for initial access into an industrial network.</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 인터넷에 노출된 HMI·SCADA 웹 서버·VPN·방화벽·라우터·IoT 기기의 취약점을 악용해 OT 환경이나 그 경계에 처음 들어올 수 있음
+- 원격 관리를 위해 일부러 노출한 장비가 많고 패치 주기가 길어, 공개된 취약점이 오랫동안 악용 가능한 상태로 남음</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 인터넷 노출 HMI·웹 SCADA, OT 경계 VPN·방화벽(FortiOS·PAN-OS 탑재 산업용 방화벽 포함), 산업용 라우터·셀룰러 게이트웨이, IP 카메라·NVR (L3.5·IoT)
+- KEV에서 OT·IoT 제품과 OT 네트워크 장비 OS 취약점 30건이 이 기법의 실제 악용으로 확인됨 — 카메라·NVR·출입통제·산업용 라우터 다수가 봇넷 편입에 쓰임
+- 통합: Enterprise 공개 애플리케이션 악용(T1190) — 경계 장비 정보 수집(T1590.006)은 외부 원격 서비스(OTC-IA-03)에 통합
+■ 실제 사례
+- [실제 사고] 덴마크 에너지 기업(2023-05): Zyxel 방화벽 취약점(CVE-2023-28771)으로 22곳의 경계 방화벽이 침해 (INC-055)
+- [실제 사고] 리비우 지역난방(2024-01): 외부에 노출된 라우터의 알려지지 않은 취약점을 악용해 진입한 것으로 추정 (INC-007, ATT&amp;CK C0041)
+- [실제 사고] BlackEnergy HMI 캠페인(2014-10): 인터넷에 노출된 GE CIMPLICITY·Advantech WebAccess HMI 취약점을 악용 (INC-030)</t>
+        </is>
+      </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
           <t>T0819</t>
@@ -3726,7 +3758,7 @@
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L11" s="17" t="inlineStr">
@@ -3840,7 +3872,16 @@
           <t>https://attack.mitre.org/techniques/T0819</t>
         </is>
       </c>
-      <c r="AM11" s="17" t="inlineStr"/>
+      <c r="AM11" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 노출 장비의 웹 접근 로그·WAF로 익스플로잇 패턴과 비정상 요청을 탐지하고 장비의 비정상 프로세스·재시작 확인
+- 경계 장비의 관리 접속·설정 변경·새 계정 생성을 중앙으로 수집
+■ 대응
+- OT 장비의 인터넷 노출을 없애고 불가피하면 VPN·점프 호스트 뒤로 옮기며, KEV 등재 취약점은 우선 패치
+- 외부 공격 표면 점검(인터넷 스캔 결과 확인)을 정기 수행하고 노출 장비 대장 관리</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
@@ -3863,12 +3904,24 @@
           <t>외부 원격 서비스 악용</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage external remote services as a point of initial access into your network.</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 VPN·원격 데스크톱·원격 접속 도구·무선 원격 링크 같은 외부 원격 서비스에 탈취하거나 남아 있는 계정으로 접속해, 정상 원격 운영자처럼 OT 환경에 들어올 수 있음
+- 정상 원격 유지보수 경로를 쓰므로 공격 트래픽이 구분되지 않고, 다중 인증이 없는 휴면·퇴사자 계정이 반복해서 침투 경로가 됨</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 운영자·벤더용 VPN, OT 원격 접속 게이트웨이·점프 호스트, TeamViewer 같은 원격 접속 도구, 현장 무선 원격 링크 (L3.5)
+- 통합: Enterprise 외부 원격 서비스(T1133)·신뢰 관계 악용(T1199, 벤더·유지보수 업체 접속)·경계 장비 정보 수집(T1590.006)
+- 유효 계정 악용(OTC-PE-01)과 함께 쓰이며, 인터넷 노출 장치 직접 접속(OTC-IA-11)과 달리 원격 접속 체계를 거침
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): 도메인 컨트롤러에서 탈취한 계정으로 배전 운영자용 제어 시스템 VPN에 접속 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 2025 폴란드(2025-12): 인터넷에 노출된 FortiGate VPN 인터페이스로 진입 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] 콜로니얼 파이프라인(2021-05): 다중 인증이 없는 휴면 VPN 계정과 유출된 암호로 진입 (INC-044)</t>
+        </is>
+      </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
           <t>T0822</t>
@@ -3891,7 +3944,7 @@
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L12" s="17" t="inlineStr">
@@ -4024,7 +4077,16 @@
           <t>https://attack.mitre.org/techniques/T0822</t>
         </is>
       </c>
-      <c r="AM12" s="17" t="inlineStr"/>
+      <c r="AM12" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- VPN·원격 접속 인증 로그에서 비정상 시간대·출발지·동시 세션과 휴면 계정 사용을 경보
+- 원격 접속 세션 중 OT 자산 접근·설정 변경을 세션 기록과 대조
+■ 대응
+- 원격 접속은 다중 인증·점프 호스트 경유·세션 기록·필요할 때만 여는 승인제로 운영하고, 퇴사자·벤더 계정을 즉시 회수
+- 경계 VPN 장비는 KEV 취약점을 우선 패치하고 관리 인터페이스를 인터넷에서 분리</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
@@ -4047,12 +4109,24 @@
           <t>이동식 매체 전파</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may move onto systems, such as those separated from the enterprise network, by copying malware to removable media which is inserted into the control systems environment.</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 USB 같은 이동식 매체에 악성코드를 실어, 업무망과 분리된 제어계통 단말까지 감염을 옮길 수 있음
+- 협력업체·유지보수 인력이 가져오는 매체가 경로가 되는 경우가 많고, 폐쇄망이라는 믿음 때문에 매체 반입 통제가 느슨한 시설이 많음</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 폐쇄망의 EWS·HMI·SCADA 서버와 프로젝트 파일을 주고받는 단말 (L1~L3)
+- 수법: 자동 실행(autorun)·LNK 취약점으로 매체를 연결하면 실행, 감염 단말이 다시 매체와 공유 드라이브로 복제
+- 통합: Enterprise 이동식 매체 전파(T1091)
+■ 실제 사례
+- [실제 사고] Stuxnet(2010-06): 이동식 드라이브로 자기 복제하며 폐쇄망에 유입된 것으로 분석 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] 독일 원전(2016-04): 연료 취급 설비용 PC와 이동식 저장장치에서 Conficker 등 악성코드가 발견 (INC-014, ATT&amp;CK S0608)
+- [실제 사고] Flame(2012-05): USB를 감염시켜 자동 실행으로 다른 Windows 시스템에 퍼지는 모듈을 갖춤 (INC-011)</t>
+        </is>
+      </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
           <t>T0847</t>
@@ -4075,7 +4149,7 @@
       </c>
       <c r="K13" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L13" s="17" t="inlineStr">
@@ -4205,7 +4279,16 @@
           <t>https://attack.mitre.org/techniques/T0847</t>
         </is>
       </c>
-      <c r="AM13" s="17" t="inlineStr"/>
+      <c r="AM13" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이동식 매체 연결 뒤 실행된 프로세스와 매체에서 시작된 파일 쓰기를 엔드포인트 감시로 탐지
+- 매체 반입 기록과 단말별 매체 사용 로그 대조
+■ 대응
+- 자동 실행을 끄고 허가된 매체만 쓰게 하며, 반입 전 검사 키오스크 운영
+- 협력업체 매체 반입 절차와 교육, 프로젝트 파일은 검사된 전용 경로로 전달</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -4228,12 +4311,22 @@
           <t>위장 마스터</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may setup a rogue master to leverage control server functions to communicate with outstations.</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr"/>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 마스터(제어 서버)를 가장한 장치를 통신망에 붙여, 현장 장치에 정상 형식의 제어 메시지를 보내거나 실제 마스터로 가는 트래픽을 가로챌 수 있음
+- 인증 없는 프로토콜에서는 현장 장치가 진짜와 가짜 마스터를 구분하지 못해 명령이 그대로 실행됨</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 마스터-슬레이브 구조의 SCADA 통신(Modbus·DNP3·IEC 101/104)과 무선 원격 링크로 연결된 RTU·PLC·IED (L1~L2)
+- 수법: 네트워크 주소 위조, 같은 주파수의 무선 장비 사용, 빼돌린 엔지니어링 장비·소프트웨어 사용
+- 비인가 명령 메시지(OTC-IP-03.1)·위조 보고 메시지(OTC-IP-03.2)의 전달 수단 — 무선 구간은 무선 통신 침해(OTC-IA-06)와 결합
+■ 실제 사례
+- [실제 사고] 마루치 하수처리(2000-03): 네트워크 주소를 위조해 펌프장에 거짓 데이터와 명령을 보냄 (INC-001, ATT&amp;CK C0020)</t>
+        </is>
+      </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
           <t>T0848</t>
@@ -4252,7 +4345,7 @@
       <c r="J14" s="17" t="inlineStr"/>
       <c r="K14" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L14" s="17" t="inlineStr">
@@ -4375,7 +4468,16 @@
           <t>https://attack.mitre.org/techniques/T0848</t>
         </is>
       </c>
-      <c r="AM14" s="17" t="inlineStr"/>
+      <c r="AM14" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자산 대장에 없는 장치·주소에서 나오는 마스터 기능 트래픽을 OT 네트워크 감시로 경보
+- 같은 슬레이브에 명령하는 마스터가 둘 이상인지 확인
+■ 대응
+- 통신 인증(IEC 62351·DNP3-SA)과 장치 허용 목록, 포트 보안(미사용 포트 차단) 적용
+- 무선 원격 링크는 암호화·주파수 관리를 하고, 장비 분실·퇴사 시 키 교체</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -4398,12 +4500,24 @@
           <t>무선 통신 침해</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may perform wireless compromise as a method of gaining communications and unauthorized access to a wireless network.</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 같은 주파수의 무선 장비나 침해한 무선 기기로 OT 무선 통신망에 접근해, 원거리에서도 현장 장치와 통신할 수 있음
+- 무선 경보·원격 제어 신호는 인증·암호화 없이 동작하는 경우가 많아, 녹음·재전송만으로도 정상 명령처럼 받아들여짐</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 원격 감시·제어용 무선 링크(라디오 중계국), 옥외 경보 사이렌, 철도 무선 비상정지, 적외선·근거리 무선 제어 장치, 산업용 Wi-Fi (L0~L2)
+- 수법: 무선 장비로 주파수 설정·통신, 신호 녹음 뒤 재전송, 개조 리모컨 — 무선 구간 재밍은 와이파이 차단(OTC-IR-13.3)
+- 결과는 대부분 비인가 명령 메시지(OTC-IP-03.1)로 이어짐
+■ 실제 사례
+- [실제 사고] 폴란드 철도 Radio-Stop(2023-08): 인증 없는 무선 비상정지 신호를 송신해 열차 20여 대를 세움 (INC-057)
+- [실제 사고] 댈러스 경보 사이렌(2017-04): 무선 신호로 옥외 경보 사이렌 156기를 반복 작동 (INC-034)
+- [실제 사고] 폴란드 우치 트램(2008-01): 개조한 리모컨의 적외선 신호로 선로 전환기를 조작 (INC-027)</t>
+        </is>
+      </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
           <t>T0860</t>
@@ -4422,7 +4536,7 @@
       <c r="J15" s="17" t="inlineStr"/>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L15" s="17" t="inlineStr">
@@ -4532,7 +4646,16 @@
           <t>https://attack.mitre.org/techniques/T0860</t>
         </is>
       </c>
-      <c r="AM15" s="17" t="inlineStr"/>
+      <c r="AM15" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 무선 네트워크의 새 장치·세션과 비정상 트래픽을 감시하고 무선 명령 이력을 운영 기록과 대조
+- 스펙트럼 감시로 비인가 송신·재밍 확인
+■ 대응
+- 무선 제어 신호에 암호화·재전송 방지·발신자 인증을 적용하고 신호 전파 범위를 최소화
+- 중요 명령은 무선으로 받은 뒤에도 현장 확인·인터록을 거치게 설계</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4555,12 +4678,23 @@
           <t>공급망 침해</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may perform supply chain compromise to gain control systems environment access by means of infected products, software, and workflows.</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr"/>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 ICS 장비·소프트웨어 공급업체의 배포 경로나 설치 과정을 침해해, 정상 제품·업데이트·설치 작업에 악성 요소를 섞어 OT 환경에 들여올 수 있음
+- 신뢰하는 공급업체 경로로 들어와 검사를 거치지 않는 경우가 많고, 같은 제품을 쓰는 여러 고객사로 동시에 퍼짐</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 벤더 웹사이트의 설치 파일·펌웨어, 장비 반입·설치 과정의 소프트웨어, 통합업체·유지보수 업체가 가져오는 도구 (L1~L3)
+- 수법: 벤더 사이트의 정상 설치 파일을 트로이 목마로 바꿈(Dragonfly·Havex), 새 장비 설치 때 검사하지 않은 소프트웨어 유입, ICS 벤더·제조사 표적화(TEMP.Veles)
+- 펌웨어 단계 유입은 펌웨어 변조(OTC-PE-04.0)와 연결 — 기기에 내장된 구성요소(임베디드 스택)의 공급망 결함은 원격 서비스 취약점 악용(OTC-IA-10)에서 다룸
+■ 실제 사례
+- [실제 사고] Dragonfly·Havex(2014-06): ICS 원격 접속 장비·산업용 카메라 업체 사이트의 설치 파일을 트로이 목마로 바꿔 배포 (INC-013, ATT&amp;CK S0093)
+- [실제 사고] TSMC(2018-08): 신규 장비 설치 중 검사하지 않은 소프트웨어로 WannaCry 변종이 들어와 생산 차질 (INC-037)</t>
+        </is>
+      </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
           <t>T0862</t>
@@ -4579,7 +4713,7 @@
       <c r="J16" s="17" t="inlineStr"/>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L16" s="17" t="inlineStr">
@@ -4717,7 +4851,16 @@
           <t>https://attack.mitre.org/techniques/T0862</t>
         </is>
       </c>
-      <c r="AM16" s="17" t="inlineStr"/>
+      <c r="AM16" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 배포 파일의 해시·서명을 벤더 공식 값과 대조하고 다운로드 파일 검사
+- 신규 장비·소프트웨어 설치 뒤 단말의 비정상 프로세스·통신을 집중 감시
+■ 대응
+- 공급업체 보안 요구사항(서명 배포·보안 개발 절차)을 계약에 반영하고 반입 전 검사 절차 운영
+- 설치·유지보수 작업에는 검사된 매체·도구만 쓰게 하고 작업 뒤 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
@@ -4740,12 +4883,22 @@
           <t>임시 접속 자산 악용</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may target devices that are transient across ICS networks and external networks.</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 정비 노트북·진단 장비처럼 OT와 외부망을 오가는 임시 접속 자산을 감염시키거나 빼돌려, OT 환경에 직접 연결되는 통로로 쓸 수 있음
+- 임시 자산은 상주 자산과 달리 보안 관리 대상에서 빠지기 쉽고, 엔지니어링 소프트웨어와 접속 정보를 함께 갖고 있음</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 엔지니어·협력업체의 정비용 노트북, 진단·프로그래밍 장비, 임시로 연결하는 원격 접속 장치 (L1~L3)
+- 원격 관리가 어려운 현장에서 많이 쓰이며, 외부망에서 감염된 뒤 OT에 연결되면 이동식 매체 전파(OTC-IA-04)와 같은 효과
+- 빼돌린 정비 장비는 위장 마스터(OTC-IA-05)로 쓰이기도 함
+■ 실제 사례
+- [실제 사고] 마루치 하수처리(2000-03): 엔지니어링 소프트웨어가 설치된(탈취 추정) 컴퓨터로 하수처리 시스템과 통신 (INC-001, ATT&amp;CK C0020)</t>
+        </is>
+      </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
           <t>T0864</t>
@@ -4764,7 +4917,7 @@
       <c r="J17" s="17" t="inlineStr"/>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L17" s="17" t="inlineStr">
@@ -4866,7 +5019,16 @@
           <t>https://attack.mitre.org/techniques/T0864</t>
         </is>
       </c>
-      <c r="AM17" s="17" t="inlineStr"/>
+      <c r="AM17" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 스위치 로그·네트워크 감시로 새 MAC 주소와 임시 장치 연결 탐지
+- 임시 자산 연결 기록과 작업 지시서 대조
+■ 대응
+- 임시 자산은 등록·검사(백신·패치·무결성)를 마친 뒤에만 연결을 허용하고 전용 연결 구간 운영
+- 정비 장비의 분실·반납 관리와 엔지니어링 소프트웨어 계정 관리</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -4889,12 +5051,24 @@
           <t>스피어피싱 첨부파일</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may use a spearphishing attachment, a variant of spearphishing, as a form of a social engineering attack against specific targets.</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr"/>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 특정 조직·직원을 노린 메일에 악성 문서·설치 파일을 첨부하거나 링크를 넣어, 업무 단말을 감염시키고 OT 접근의 발판을 만들 수 있음
+- OT 공격 대부분이 IT 업무망 침투에서 시작되며, 감염 단말에서 VPN·원격 접속 자격증명을 빼내 제어망으로 넘어감</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 엔지니어·운영자·관리자의 업무 단말, OT 접근 권한이 있는 점프 호스트 사용자 (L3~L4)
+- 수법: 매크로 포함 Office 문서(BlackEnergy·2015 우크라이나), 트로이 목마 설치 파일 첨부(Havex), 스피어피싱 링크(랜섬웨어 사고) — Enterprise 피싱(T1566, 링크 포함) 통합
+- 다음 단계는 대개 자격증명 탈취(OTC-LM-07)와 외부 원격 서비스 접속(OTC-IA-03)
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): 피싱 메일의 Office 첨부파일로 다수 IT 시스템에 첫 거점 확보 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 천연가스 압축 시설(2020-02): 스피어피싱 링크로 IT망에 들어온 뒤 OT망까지 랜섬웨어 확산 (INC-039)
+- [실제 사고] 한국수력원자력(2014-12): 임직원 대상 악성 메일 이후 내부 자료가 유출 (INC-073)</t>
+        </is>
+      </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
           <t>T0865</t>
@@ -4917,7 +5091,7 @@
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L18" s="17" t="inlineStr">
@@ -5023,7 +5197,16 @@
           <t>https://attack.mitre.org/techniques/T0865</t>
         </is>
       </c>
-      <c r="AM18" s="17" t="inlineStr"/>
+      <c r="AM18" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 문서 프로그램이 만드는 비정상 하위 프로세스와 첨부파일 실행을 엔드포인트 감시로 탐지
+- 메일 보안 게이트웨이의 악성 첨부·링크 탐지와 사용자 신고 연계
+■ 대응
+- 매크로·실행 파일 첨부 차단, 메일 샌드박스, OT 담당자 대상 표적 피싱 훈련
+- OT 접근 계정을 업무 메일 계정과 분리하고 다중 인증 적용</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
@@ -5046,12 +5229,24 @@
           <t>원격 서비스 취약점 악용</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit a software vulnerability to take advantage of a programming error in a program, service, or within the operating system software or kernel itself to enable remote service abuse.</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 자산의 원격 서비스(SMB·RPC·데이터베이스·장치 웹 서버 등) 취약점을 악용해, 처음 진입하거나 내부에서 다른 자산으로 이동할 수 있음
+- 패치하기 어려운 노후 운영체제와 장치가 많아 오래된 취약점이 계속 유효하고, 웜형 악성코드는 IT에서 OT로 자동 확산됨</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 HMI·EWS·SCADA 서버·히스토리언(WinCC DB 등), PLC·RTU·IED의 웹·관리 서비스, 임베디드 네트워크 스택 (L1~L3.5)
+- CISA ICS 권고에서 원격 코드 실행·인증 우회류 공개 취약점 2,213건(이 매트릭스의 CWE 규칙 기준), KEV에서 OT 제품·임베디드 구성요소 실제 악용 17건 확인
+- 통합: Enterprise 원격 서비스 취약점 악용(T1210) — [IA]·[LM] 두 전술에 같은 근거로 표시
+■ 실제 사례
+- [실제 사고] WannaCry·NotPetya(2017-05·2017-06): SMBv1 취약점(MS17-010)으로 IT망에서 산업망까지 자동 확산 (INC-015, INC-016)
+- [실제 사고] Stuxnet(2010-06): WinCC 데이터베이스 서버에 악성 SQL 명령을 실행하고 Windows 취약점(MS08-067·MS10-061)으로 확산 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] 데이비스-베시 원전(2003-01): SQL Slammer 웜이 협력업체 연결로 들어와 안전 변수 표시 시스템을 마비 (INC-025)</t>
+        </is>
+      </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
           <t>T0866</t>
@@ -5074,7 +5269,7 @@
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L19" s="17" t="inlineStr">
@@ -5164,7 +5359,7 @@
       </c>
       <c r="Z19" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 8건(최근 0) · ATT&amp;CK 사례 6건 · 공개 취약점 2213건 · KEV 17건 · 실증·연구 1건</t>
+          <t>실제 사고 7건(최근 0) · ATT&amp;CK 사례 6건 · 공개 취약점 2213건 · KEV 17건 · 실증·연구 1건</t>
         </is>
       </c>
       <c r="AA19" s="17" t="inlineStr">
@@ -5173,7 +5368,7 @@
         </is>
       </c>
       <c r="AB19" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC19" s="17" t="n">
         <v>0</v>
@@ -5197,12 +5392,12 @@
       </c>
       <c r="AI19" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 6 · 분석 3</t>
+          <t>ATT&amp;CK 공식 5 · 분석 3</t>
         </is>
       </c>
       <c r="AJ19" s="17" t="inlineStr">
         <is>
-          <t>INC-009, INC-011, INC-014, INC-015, INC-016, INC-017, INC-025, INC-037
+          <t>INC-009, INC-011, INC-015, INC-016, INC-017, INC-025, INC-037
 실증: INC-080</t>
         </is>
       </c>
@@ -5216,7 +5411,16 @@
           <t>https://attack.mitre.org/techniques/T0866</t>
         </is>
       </c>
-      <c r="AM19" s="17" t="inlineStr"/>
+      <c r="AM19" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 네트워크 감시(DPI)로 익스플로잇 패턴과 내부의 대량 SMB·RPC 연결 확산 탐지
+- 서비스 충돌·비정상 종료 로그를 모아 악용 시도 확인
+■ 대응
+- 위험 기반 패치(운영 영향 검증 뒤 적용)와 패치할 수 없는 자산의 보완 통제(서비스 비활성화·구간 분리·허용 목록)
+- OT 구간 사이의 불필요한 SMB·RPC를 막고 망 분리</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
@@ -5239,12 +5443,24 @@
           <t>인터넷 노출 장치 악용</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may gain access into industrial environments through systems exposed directly to the internet for remote access rather than through External Remote Services.</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr"/>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 원격 관리를 위해 인터넷에 직접 노출된 PLC·HMI·제어 장치에 접속해, 별도의 침투 없이 곧바로 OT 환경에 들어올 수 있음
+- 기본·약한 암호나 인증 없는 프로토콜이 그대로인 경우가 많아, 인터넷 스캔만으로 대상을 찾는 핵티비스트·봇넷의 손쉬운 표적이 됨</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 인터넷에 노출된 PLC 내장 HMI·웹 제어 화면·VNC 접속 HMI, 원격 감시 장치, 셀룰러 모뎀 연결 SCADA, IoT 기기 (L1~L2·IoT)
+- 2023년 이후 노출 장치를 노린 핵티비스트형 조작(화면 변조·설정값 변경·운영자 잠금)이 수도·댐·지역 유틸리티에서 반복되며, IoT 봇넷도 같은 경로를 씀
+- 외부 원격 서비스(OTC-IA-03)와 달리 원격 접속 체계를 거치지 않고 장치 자체가 노출된 것이 원인
+■ 실제 사례
+- [실제 사고] Unitronics(2023-11): 인터넷에 연결된 Unitronics PLC·HMI에 접속해 화면을 바꿈 (INC-005, ATT&amp;CK C0031)
+- [실제 사고] 노르웨이 브레망에르 댐(2025-04): 약한 암호의 웹 제어 화면에 접속해 방류 밸브를 엶 (INC-068)
+- [실제 사고] 캐나다 핵티비스트(2025-10): 노출된 제어 장치로 수도 압력·탱크 게이지·사일로 온습도를 조작 (INC-072)</t>
+        </is>
+      </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
           <t>T0883</t>
@@ -5263,7 +5479,7 @@
       <c r="J20" s="17" t="inlineStr"/>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L20" s="17" t="inlineStr">
@@ -5373,7 +5589,16 @@
           <t>https://attack.mitre.org/techniques/T0883</t>
         </is>
       </c>
-      <c r="AM20" s="17" t="inlineStr"/>
+      <c r="AM20" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 인터넷 출발지의 OT 장치 로그인·프로토콜 접속을 경보하고, 외부 스캔 서비스 결과로 자사 노출 장치를 정기 확인
+- 장치 화면·설정 변경을 접속 출발지와 대조
+■ 대응
+- OT 장치의 인터넷 직접 노출을 없애고(방화벽·VPN 뒤로) 셀룰러 모뎀 같은 숨은 연결을 점검
+- 기본 암호 변경과 인증 강화, 노출이 불가피하면 출발지 제한과 접속 감시</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
@@ -5396,12 +5621,24 @@
           <t>원격 서비스 악용</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage remote services to move between assets and network segments.</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr"/>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 RDP·SSH·SMB·WMI·데이터베이스 접속·원격 지원 소프트웨어 같은 정상 원격 서비스로 OT 자산 사이를 오가며 운영자처럼 시스템을 조작할 수 있음
+- 운영 업무에 쓰는 서비스라 막기 어렵고, 탈취한 정상 계정으로 접속하면 일상 운영 활동과 구분되지 않음</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 점프 호스트·HMI·SCADA 서버·히스토리언·데이터베이스 서버, 제어기의 관리 프로토콜(CODESYS·Telnet) (L1~L3.5)
+- 수법: 점프 호스트 RDP와 허술한 OT 방화벽 규칙(Triton), 헬프데스크 원격 제어 소프트웨어로 HMI 마우스 조작(2015 우크라이나), MS-SQL 피벗(2016 우크라이나), 관리자 공유·PsExec·WMI 확산
+- 통합: Enterprise 원격 서비스(T1021, RDP·SMB)·WMI(T1047)·RDP 세션 가로채기(T1563.002) — [IA]·[LM] 두 전술에 같은 근거로 표시
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): IT 헬프데스크 원격 제어 소프트웨어로 ICS 단말의 마우스를 움직여 차단기를 개방 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] Triton(2017-08): RDP 점프 박스와 허술한 OT 방화벽 설정으로 ICS 영역에 이동 (INC-004, ATT&amp;CK C0030)
+- [실제 사고] 2025 폴란드(2025-12): 침해한 Fortinet 경계 장비로 OT에 들어와 SSH·RDP·SMB로 장치에 접속 (INC-008, ATT&amp;CK C0063)</t>
+        </is>
+      </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
           <t>T0886</t>
@@ -5424,7 +5661,7 @@
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L21" s="17" t="inlineStr">
@@ -5499,7 +5736,7 @@
       </c>
       <c r="Z21" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 10건(최근 1) · ATT&amp;CK 사례 14건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
+          <t>실제 사고 9건(최근 1) · ATT&amp;CK 사례 14건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
         </is>
       </c>
       <c r="AA21" s="17" t="inlineStr">
@@ -5508,7 +5745,7 @@
         </is>
       </c>
       <c r="AB21" s="17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21" s="17" t="n">
         <v>1</v>
@@ -5532,12 +5769,12 @@
       </c>
       <c r="AI21" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 11</t>
+          <t>ATT&amp;CK 공식 10</t>
         </is>
       </c>
       <c r="AJ21" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-004, INC-008, INC-009, INC-010, INC-014, INC-015, INC-016, INC-020
+          <t>INC-002, INC-003, INC-004, INC-008, INC-009, INC-010, INC-015, INC-016, INC-020
 위협인텔: INC-022</t>
         </is>
       </c>
@@ -5551,7 +5788,16 @@
           <t>https://attack.mitre.org/techniques/T0886</t>
         </is>
       </c>
-      <c r="AM21" s="17" t="inlineStr"/>
+      <c r="AM21" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 서비스 접속의 출발지·시간대·계정을 기준선과 비교하고 IT 계정의 OT 자산 접속을 경보
+- 점프 호스트 세션 기록과 OT 자산 변경 이력 대조
+■ 대응
+- OT 원격 접속을 점프 호스트로 일원화하고 다중 인증·세션 기록을 적용하며 구간 사이 RDP·SMB 직접 연결 차단
+- 원격 지원 소프트웨어 사용을 승인된 도구·시간으로 제한</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
@@ -6165,7 +6411,7 @@
       </c>
       <c r="Z25" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 4건(최근 0) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 1건</t>
+          <t>실제 사고 3건(최근 0) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 1건</t>
         </is>
       </c>
       <c r="AA25" s="17" t="inlineStr">
@@ -6174,7 +6420,7 @@
         </is>
       </c>
       <c r="AB25" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC25" s="17" t="n">
         <v>0</v>
@@ -6198,12 +6444,12 @@
       </c>
       <c r="AI25" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 5</t>
+          <t>ATT&amp;CK 공식 4</t>
         </is>
       </c>
       <c r="AJ25" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-004, INC-009, INC-017
+          <t>INC-004, INC-009, INC-017
 실증: INC-024</t>
         </is>
       </c>
@@ -9508,7 +9754,7 @@
       </c>
       <c r="Z45" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 9건(최근 0) · ATT&amp;CK 사례 10건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 7건(최근 0) · ATT&amp;CK 사례 10건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA45" s="17" t="inlineStr">
@@ -9517,7 +9763,7 @@
         </is>
       </c>
       <c r="AB45" s="17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC45" s="17" t="n">
         <v>0</v>
@@ -9541,12 +9787,12 @@
       </c>
       <c r="AI45" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 9</t>
+          <t>ATT&amp;CK 공식 7</t>
         </is>
       </c>
       <c r="AJ45" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-006, INC-009, INC-010, INC-014, INC-015, INC-016, INC-017</t>
+          <t>INC-003, INC-006, INC-009, INC-010, INC-015, INC-016, INC-017</t>
         </is>
       </c>
       <c r="AK45" s="17" t="inlineStr">
@@ -10342,7 +10588,7 @@
       </c>
       <c r="Z50" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 9건(최근 0) · ATT&amp;CK 사례 10건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 7건(최근 0) · ATT&amp;CK 사례 10건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA50" s="17" t="inlineStr">
@@ -10351,7 +10597,7 @@
         </is>
       </c>
       <c r="AB50" s="17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC50" s="17" t="n">
         <v>0</v>
@@ -10375,12 +10621,12 @@
       </c>
       <c r="AI50" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 9</t>
+          <t>ATT&amp;CK 공식 7</t>
         </is>
       </c>
       <c r="AJ50" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-006, INC-009, INC-010, INC-014, INC-015, INC-016, INC-017</t>
+          <t>INC-003, INC-006, INC-009, INC-010, INC-015, INC-016, INC-017</t>
         </is>
       </c>
       <c r="AK50" s="17" t="inlineStr">
@@ -10686,7 +10932,7 @@
       </c>
       <c r="Z52" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 11건(최근 1) · ATT&amp;CK 사례 15건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 10건(최근 1) · ATT&amp;CK 사례 15건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA52" s="17" t="inlineStr">
@@ -10695,7 +10941,7 @@
         </is>
       </c>
       <c r="AB52" s="17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC52" s="17" t="n">
         <v>1</v>
@@ -10719,12 +10965,12 @@
       </c>
       <c r="AI52" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 11</t>
+          <t>ATT&amp;CK 공식 10</t>
         </is>
       </c>
       <c r="AJ52" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-004, INC-006, INC-008, INC-009, INC-011, INC-016, INC-017, INC-019, INC-020</t>
+          <t>INC-003, INC-004, INC-006, INC-008, INC-009, INC-011, INC-016, INC-017, INC-019, INC-020</t>
         </is>
       </c>
       <c r="AK52" s="17" t="inlineStr">
@@ -12073,7 +12319,7 @@
       </c>
       <c r="Z60" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 7건(최근 0) · ATT&amp;CK 사례 11건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 6건(최근 0) · ATT&amp;CK 사례 11건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA60" s="17" t="inlineStr">
@@ -12082,7 +12328,7 @@
         </is>
       </c>
       <c r="AB60" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC60" s="17" t="n">
         <v>0</v>
@@ -12106,12 +12352,12 @@
       </c>
       <c r="AI60" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 7</t>
+          <t>ATT&amp;CK 공식 6</t>
         </is>
       </c>
       <c r="AJ60" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-009, INC-014, INC-016, INC-019, INC-020</t>
+          <t>INC-002, INC-003, INC-009, INC-016, INC-019, INC-020</t>
         </is>
       </c>
       <c r="AK60" s="17" t="inlineStr">
@@ -12405,7 +12651,7 @@
       </c>
       <c r="Z62" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 8건(최근 1) · ATT&amp;CK 사례 9건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 7건(최근 1) · ATT&amp;CK 사례 9건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA62" s="17" t="inlineStr">
@@ -12414,7 +12660,7 @@
         </is>
       </c>
       <c r="AB62" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC62" s="17" t="n">
         <v>1</v>
@@ -12438,12 +12684,12 @@
       </c>
       <c r="AI62" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 8</t>
+          <t>ATT&amp;CK 공식 7</t>
         </is>
       </c>
       <c r="AJ62" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-008, INC-009, INC-010, INC-013, INC-015, INC-020</t>
+          <t>INC-003, INC-008, INC-009, INC-010, INC-013, INC-015, INC-020</t>
         </is>
       </c>
       <c r="AK62" s="17" t="inlineStr">
@@ -12966,7 +13212,7 @@
       </c>
       <c r="Z65" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 5건(최근 1) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 1건 · 위협인텔 1건</t>
+          <t>실제 사고 3건(최근 1) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 1건 · 위협인텔 1건</t>
         </is>
       </c>
       <c r="AA65" s="17" t="inlineStr">
@@ -12975,7 +13221,7 @@
         </is>
       </c>
       <c r="AB65" s="17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC65" s="17" t="n">
         <v>1</v>
@@ -12999,12 +13245,12 @@
       </c>
       <c r="AI65" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 7</t>
+          <t>ATT&amp;CK 공식 5</t>
         </is>
       </c>
       <c r="AJ65" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-008, INC-013, INC-014
+          <t>INC-003, INC-008, INC-013
 실증: INC-024
 위협인텔: INC-022</t>
         </is>
@@ -14566,12 +14812,24 @@
           <t>원격 서비스 취약점 악용</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit a software vulnerability to take advantage of a programming error in a program, service, or within the operating system software or kernel itself to enable remote service abuse.</t>
-        </is>
-      </c>
-      <c r="F75" s="17" t="inlineStr"/>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 자산의 원격 서비스(SMB·RPC·데이터베이스·장치 웹 서버 등) 취약점을 악용해, 처음 진입하거나 내부에서 다른 자산으로 이동할 수 있음
+- 패치하기 어려운 노후 운영체제와 장치가 많아 오래된 취약점이 계속 유효하고, 웜형 악성코드는 IT에서 OT로 자동 확산됨</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 HMI·EWS·SCADA 서버·히스토리언(WinCC DB 등), PLC·RTU·IED의 웹·관리 서비스, 임베디드 네트워크 스택 (L1~L3.5)
+- CISA ICS 권고에서 원격 코드 실행·인증 우회류 공개 취약점 2,213건(이 매트릭스의 CWE 규칙 기준), KEV에서 OT 제품·임베디드 구성요소 실제 악용 17건 확인
+- 통합: Enterprise 원격 서비스 취약점 악용(T1210) — [IA]·[LM] 두 전술에 같은 근거로 표시
+■ 실제 사례
+- [실제 사고] WannaCry·NotPetya(2017-05·2017-06): SMBv1 취약점(MS17-010)으로 IT망에서 산업망까지 자동 확산 (INC-015, INC-016)
+- [실제 사고] Stuxnet(2010-06): WinCC 데이터베이스 서버에 악성 SQL 명령을 실행하고 Windows 취약점(MS08-067·MS10-061)으로 확산 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] 데이비스-베시 원전(2003-01): SQL Slammer 웜이 협력업체 연결로 들어와 안전 변수 표시 시스템을 마비 (INC-025)</t>
+        </is>
+      </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
           <t>T0866</t>
@@ -14594,7 +14852,7 @@
       </c>
       <c r="K75" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L75" s="17" t="inlineStr">
@@ -14684,7 +14942,7 @@
       </c>
       <c r="Z75" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 8건(최근 0) · ATT&amp;CK 사례 6건 · 공개 취약점 2213건 · KEV 17건 · 실증·연구 1건</t>
+          <t>실제 사고 7건(최근 0) · ATT&amp;CK 사례 6건 · 공개 취약점 2213건 · KEV 17건 · 실증·연구 1건</t>
         </is>
       </c>
       <c r="AA75" s="17" t="inlineStr">
@@ -14693,7 +14951,7 @@
         </is>
       </c>
       <c r="AB75" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC75" s="17" t="n">
         <v>0</v>
@@ -14717,12 +14975,12 @@
       </c>
       <c r="AI75" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 6 · 분석 3</t>
+          <t>ATT&amp;CK 공식 5 · 분석 3</t>
         </is>
       </c>
       <c r="AJ75" s="17" t="inlineStr">
         <is>
-          <t>INC-009, INC-011, INC-014, INC-015, INC-016, INC-017, INC-025, INC-037
+          <t>INC-009, INC-011, INC-015, INC-016, INC-017, INC-025, INC-037
 실증: INC-080</t>
         </is>
       </c>
@@ -14736,7 +14994,16 @@
           <t>https://attack.mitre.org/techniques/T0866</t>
         </is>
       </c>
-      <c r="AM75" s="17" t="inlineStr"/>
+      <c r="AM75" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 네트워크 감시(DPI)로 익스플로잇 패턴과 내부의 대량 SMB·RPC 연결 확산 탐지
+- 서비스 충돌·비정상 종료 로그를 모아 악용 시도 확인
+■ 대응
+- 위험 기반 패치(운영 영향 검증 뒤 적용)와 패치할 수 없는 자산의 보완 통제(서비스 비활성화·구간 분리·허용 목록)
+- OT 구간 사이의 불필요한 SMB·RPC를 막고 망 분리</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
@@ -14847,7 +15114,7 @@
       </c>
       <c r="Z76" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 12건(최근 1) · ATT&amp;CK 사례 15건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
+          <t>실제 사고 11건(최근 1) · ATT&amp;CK 사례 15건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
         </is>
       </c>
       <c r="AA76" s="17" t="inlineStr">
@@ -14856,7 +15123,7 @@
         </is>
       </c>
       <c r="AB76" s="17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC76" s="17" t="n">
         <v>1</v>
@@ -14880,12 +15147,12 @@
       </c>
       <c r="AI76" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 13</t>
+          <t>ATT&amp;CK 공식 12</t>
         </is>
       </c>
       <c r="AJ76" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-004, INC-006, INC-008, INC-009, INC-013, INC-014, INC-015, INC-016, INC-017, INC-019
+          <t>INC-002, INC-003, INC-004, INC-006, INC-008, INC-009, INC-013, INC-015, INC-016, INC-017, INC-019
 위협인텔: INC-022</t>
         </is>
       </c>
@@ -14922,12 +15189,24 @@
           <t>원격 서비스 악용</t>
         </is>
       </c>
-      <c r="E77" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage remote services to move between assets and network segments.</t>
-        </is>
-      </c>
-      <c r="F77" s="17" t="inlineStr"/>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 RDP·SSH·SMB·WMI·데이터베이스 접속·원격 지원 소프트웨어 같은 정상 원격 서비스로 OT 자산 사이를 오가며 운영자처럼 시스템을 조작할 수 있음
+- 운영 업무에 쓰는 서비스라 막기 어렵고, 탈취한 정상 계정으로 접속하면 일상 운영 활동과 구분되지 않음</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 점프 호스트·HMI·SCADA 서버·히스토리언·데이터베이스 서버, 제어기의 관리 프로토콜(CODESYS·Telnet) (L1~L3.5)
+- 수법: 점프 호스트 RDP와 허술한 OT 방화벽 규칙(Triton), 헬프데스크 원격 제어 소프트웨어로 HMI 마우스 조작(2015 우크라이나), MS-SQL 피벗(2016 우크라이나), 관리자 공유·PsExec·WMI 확산
+- 통합: Enterprise 원격 서비스(T1021, RDP·SMB)·WMI(T1047)·RDP 세션 가로채기(T1563.002) — [IA]·[LM] 두 전술에 같은 근거로 표시
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): IT 헬프데스크 원격 제어 소프트웨어로 ICS 단말의 마우스를 움직여 차단기를 개방 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] Triton(2017-08): RDP 점프 박스와 허술한 OT 방화벽 설정으로 ICS 영역에 이동 (INC-004, ATT&amp;CK C0030)
+- [실제 사고] 2025 폴란드(2025-12): 침해한 Fortinet 경계 장비로 OT에 들어와 SSH·RDP·SMB로 장치에 접속 (INC-008, ATT&amp;CK C0063)</t>
+        </is>
+      </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
           <t>T0886</t>
@@ -14950,7 +15229,7 @@
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L77" s="17" t="inlineStr">
@@ -15025,7 +15304,7 @@
       </c>
       <c r="Z77" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 10건(최근 1) · ATT&amp;CK 사례 14건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
+          <t>실제 사고 9건(최근 1) · ATT&amp;CK 사례 14건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
         </is>
       </c>
       <c r="AA77" s="17" t="inlineStr">
@@ -15034,7 +15313,7 @@
         </is>
       </c>
       <c r="AB77" s="17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC77" s="17" t="n">
         <v>1</v>
@@ -15058,12 +15337,12 @@
       </c>
       <c r="AI77" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 11</t>
+          <t>ATT&amp;CK 공식 10</t>
         </is>
       </c>
       <c r="AJ77" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-004, INC-008, INC-009, INC-010, INC-014, INC-015, INC-016, INC-020
+          <t>INC-002, INC-003, INC-004, INC-008, INC-009, INC-010, INC-015, INC-016, INC-020
 위협인텔: INC-022</t>
         </is>
       </c>
@@ -15077,7 +15356,16 @@
           <t>https://attack.mitre.org/techniques/T0886</t>
         </is>
       </c>
-      <c r="AM77" s="17" t="inlineStr"/>
+      <c r="AM77" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 서비스 접속의 출발지·시간대·계정을 기준선과 비교하고 IT 계정의 OT 자산 접속을 경보
+- 점프 호스트 세션 기록과 OT 자산 변경 이력 대조
+■ 대응
+- OT 원격 접속을 점프 호스트로 일원화하고 다중 인증·세션 기록을 적용하며 구간 사이 RDP·SMB 직접 연결 차단
+- 원격 지원 소프트웨어 사용을 승인된 도구·시간으로 제한</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="17" t="inlineStr">
@@ -15697,7 +15985,7 @@
       </c>
       <c r="Z81" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 9건(최근 1) · ATT&amp;CK 사례 8건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 8건(최근 1) · ATT&amp;CK 사례 8건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA81" s="17" t="inlineStr">
@@ -15706,7 +15994,7 @@
         </is>
       </c>
       <c r="AB81" s="17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC81" s="17" t="n">
         <v>1</v>
@@ -15730,12 +16018,12 @@
       </c>
       <c r="AI81" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 8 · 분석 1</t>
+          <t>ATT&amp;CK 공식 7 · 분석 1</t>
         </is>
       </c>
       <c r="AJ81" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-004, INC-007, INC-008, INC-013, INC-016, INC-017, INC-063</t>
+          <t>INC-003, INC-004, INC-007, INC-008, INC-013, INC-016, INC-017, INC-063</t>
         </is>
       </c>
       <c r="AK81" s="17" t="inlineStr">
@@ -16995,7 +17283,7 @@
       </c>
       <c r="Z89" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 4건(최근 1) · ATT&amp;CK 사례 5건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 3건(최근 1) · ATT&amp;CK 사례 5건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA89" s="17" t="inlineStr">
@@ -17004,7 +17292,7 @@
         </is>
       </c>
       <c r="AB89" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC89" s="17" t="n">
         <v>1</v>
@@ -17028,12 +17316,12 @@
       </c>
       <c r="AI89" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 3 · 분석 1</t>
+          <t>ATT&amp;CK 공식 2 · 분석 1</t>
         </is>
       </c>
       <c r="AJ89" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-008, INC-011, INC-036</t>
+          <t>INC-008, INC-011, INC-036</t>
         </is>
       </c>
       <c r="AK89" s="17" t="inlineStr">
@@ -19038,7 +19326,7 @@
       </c>
       <c r="Z101" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 13건(최근 1) · ATT&amp;CK 사례 13건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
+          <t>실제 사고 11건(최근 1) · ATT&amp;CK 사례 13건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건 · 위협인텔 1건</t>
         </is>
       </c>
       <c r="AA101" s="17" t="inlineStr">
@@ -19047,7 +19335,7 @@
         </is>
       </c>
       <c r="AB101" s="17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC101" s="17" t="n">
         <v>1</v>
@@ -19071,12 +19359,12 @@
       </c>
       <c r="AI101" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 10 · 분석 4</t>
+          <t>ATT&amp;CK 공식 8 · 분석 4</t>
         </is>
       </c>
       <c r="AJ101" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-006, INC-008, INC-014, INC-015, INC-018, INC-020, INC-023, INC-035, INC-042, INC-047, INC-050
+          <t>INC-003, INC-006, INC-008, INC-015, INC-018, INC-020, INC-023, INC-035, INC-042, INC-047, INC-050
 위협인텔: INC-022</t>
         </is>
       </c>
@@ -20406,7 +20694,7 @@
       </c>
       <c r="Z108" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 5건(최근 0) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 4건(최근 0) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA108" s="17" t="inlineStr">
@@ -20415,7 +20703,7 @@
         </is>
       </c>
       <c r="AB108" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC108" s="17" t="n">
         <v>0</v>
@@ -20439,12 +20727,12 @@
       </c>
       <c r="AI108" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 5</t>
+          <t>ATT&amp;CK 공식 4</t>
         </is>
       </c>
       <c r="AJ108" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-015, INC-020, INC-021</t>
+          <t>INC-003, INC-015, INC-020, INC-021</t>
         </is>
       </c>
       <c r="AK108" s="17" t="inlineStr">
@@ -23532,12 +23820,23 @@
           <t>제어 거부</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause a denial of control to temporarily prevent operators and engineers from interacting with process controls.</t>
-        </is>
-      </c>
-      <c r="F125" s="17" t="inlineStr"/>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어 장치와의 통신을 끊거나 원격 복구에 필요한 장치를 무력화해, 운영자·엔지니어가 한동안 공정을 조작하지 못하게 할 수 있음
+- 공정은 계속 돌아가지만 이상이 생겨도 원격으로 개입할 수 없어, 다른 조작과 결합되면 피해가 걷잡을 수 없이 커짐</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 결과 기법: 통신 차단(OTC-IR-13.1)·장치 무력화(OTC-IR-02, OTC-PE-04.1)·네트워크 접근 차단의 결과로 나타나며, 일시적이면 제어 거부, 지속되면 제어 상실(OTC-IM-04)
+- 원격 운전에 의존하는 배전·상하수도·파이프라인처럼 현장이 넓게 흩어진 시설에서 영향이 큼
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): KillDisk와 변환기 펌웨어 덮어쓰기로 RTU 등 원격 복구에 필요한 장치를 쓸 수 없게 만듦 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 마루치 하수처리(2000-03): 조사자를 네트워크에서 일시 차단해 제어 명령을 내리지 못하게 함 (INC-001, ATT&amp;CK C0020)
+- [실제 사고] 2016 우크라이나(2016-12): Industroyer가 직렬 COM 채널을 일시 차단 (INC-003, ATT&amp;CK S0604)</t>
+        </is>
+      </c>
       <c r="G125" s="17" t="inlineStr">
         <is>
           <t>T0813</t>
@@ -23556,7 +23855,7 @@
       <c r="J125" s="17" t="inlineStr"/>
       <c r="K125" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L125" s="17" t="inlineStr"/>
@@ -23644,7 +23943,16 @@
           <t>https://attack.mitre.org/techniques/T0813</t>
         </is>
       </c>
-      <c r="AM125" s="17" t="inlineStr"/>
+      <c r="AM125" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ATT&amp;CK에 표준 탐지 방법이 없는 결과 기법 — 원인 기법(통신 차단·장치 정지·데이터 파괴) 탐지로 대응
+- 제어 명령 실패·무응답 이벤트를 장치·채널별로 모아 동시다발 여부 확인
+■ 대응
+- 대역 외 통신 채널과 서비스 이중화로 원격 제어 경로를 확보하고 수동 운전 절차를 정기 훈련
+- 장치 설정·프로그램 백업으로 재구성 시간 단축</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="17" t="inlineStr">
@@ -23667,12 +23975,22 @@
           <t>감시 거부</t>
         </is>
       </c>
-      <c r="E126" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause a denial of view in attempt to disrupt and prevent operator oversight on the status of an ICS environment.</t>
-        </is>
-      </c>
-      <c r="F126" s="17" t="inlineStr"/>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치와 제어 시스템 사이 통신을 일시적으로 방해해, 운영자가 공정 상태를 보지 못하게 할 수 있음
+- 방해가 그치면 화면이 회복되는 일시적 현상이라 통신 장애로 넘기기 쉽고, 그 사이 이뤄진 조작은 운영자 눈에 띄지 않음</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 결과 기법: 직렬 채널 차단(OTC-IR-13.1)·보고 메시지 차단(OTC-IR-11.2)·네트워크 접근 차단의 결과로 나타나며, 지속되면 감시 상실(OTC-IM-06)
+- 운영자 판단은 화면에 의존하므로 감시 거부 구간에 제어 조작(OTC-IM-07)이 겹치면 대응이 늦어짐
+■ 실제 사례
+- [실제 사고] 마루치 하수처리(2000-03): 조사자를 네트워크에서 일시 차단해 시스템 상태를 보지 못하게 함 (INC-001, ATT&amp;CK C0020)
+- [실제 사고] 2016 우크라이나(2016-12): Industroyer가 직렬 COM 채널을 일시 차단해 감시 거부를 일으킴 (INC-003, ATT&amp;CK S0604)</t>
+        </is>
+      </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
           <t>T0815</t>
@@ -23691,7 +24009,7 @@
       <c r="J126" s="17" t="inlineStr"/>
       <c r="K126" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L126" s="17" t="inlineStr"/>
@@ -23779,7 +24097,16 @@
           <t>https://attack.mitre.org/techniques/T0815</t>
         </is>
       </c>
-      <c r="AM126" s="17" t="inlineStr"/>
+      <c r="AM126" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 텔레메트리 공백·갱신 지연을 장치·채널별로 감시해 원인 기법 추적
+- 통신 장애 기록과 같은 시간대의 운영 변경·명령 이력을 함께 검토
+■ 대응
+- 대역 외 감시 수단(현장 계측·독립 감시 경로) 확보와 감시 서비스 이중화
+- 통신 장애 시 현장 확인 절차를 운영 매뉴얼에 포함</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="17" t="inlineStr">
@@ -23802,12 +24129,24 @@
           <t>가용성 상실</t>
         </is>
       </c>
-      <c r="E127" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to disrupt essential components or systems to prevent owner and operator from delivering products or services.</t>
-        </is>
-      </c>
-      <c r="F127" s="17" t="inlineStr"/>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 핵심 구성요소를 방해하거나 HMI·워크스테이션·데이터베이스의 데이터를 지우거나 암호화해, 운영 조직이 제품·서비스를 공급하지 못하게 할 수 있음
+- 전력·난방·연료·철도처럼 공공 서비스가 끊기면 피해가 조직 밖 사회 전체로 번지고, 예방 차원의 운영 중단도 같은 결과를 낳음</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 결과 기법: 제어 조작(차단기 개방·설정 변경), 장치·HMI 무력화, 랜섬웨어(OTC-IM-13), 무선 신호 악용 등 여러 경로의 결과
+- 생산·매출 손실(OTC-IM-05)이 조직의 경제적 피해라면 이 행은 서비스 공급 중단 자체 — 둘이 함께 나타나는 경우가 많음
+- 사고 DB에서 OT 직접 조작(배전·지역난방·철도 무선 정지)과 IT 경유 중단(연료 결제·배급 시스템)이 모두 확인됨
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): 차단기를 열어 수천 곳의 사업장·가구가 약 6시간 정전 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 리비우 지역난방(2024-01): 제어기 파라미터를 바꿔 지역난방 공급이 끊김 (INC-007, ATT&amp;CK C0041)
+- [실제 사고] 이란 주유소(2021-10·2023-12): 연료 배급·결제 시스템 마비로 전국 주유소 운영 차질 (INC-048, INC-060)</t>
+        </is>
+      </c>
       <c r="G127" s="17" t="inlineStr">
         <is>
           <t>T0826</t>
@@ -23826,7 +24165,7 @@
       <c r="J127" s="17" t="inlineStr"/>
       <c r="K127" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L127" s="17" t="inlineStr"/>
@@ -23914,7 +24253,16 @@
           <t>https://attack.mitre.org/techniques/T0826</t>
         </is>
       </c>
-      <c r="AM127" s="17" t="inlineStr"/>
+      <c r="AM127" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 원인 기법 탐지와 함께 공급량·가동률 같은 서비스 지표의 급변을 감시
+- 공급 중단 시 IT·OT 이벤트 시간대를 맞춰 원인 영역(OT 직접 조작 vs IT 경유)을 빠르게 판정
+■ 대응
+- 서비스 이중화, 대역 외 운영 수단, 수동 운전·현장 복구 절차를 준비하고 정기 훈련
+- 핵심 데이터·설정을 오프라인으로 백업하고, IT 장애 시에도 OT를 독립 운전할 수 있게 의존성 축소</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="17" t="inlineStr">
@@ -23937,12 +24285,23 @@
           <t>제어 상실</t>
         </is>
       </c>
-      <c r="E128" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may seek to achieve a sustained loss of control or a runaway condition in which operators cannot issue any commands even if the malicious interference has subsided.</t>
-        </is>
-      </c>
-      <c r="F128" s="17" t="inlineStr"/>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치·HMI를 파괴하거나 주변 기기 사용을 막아, 간섭이 멈춘 뒤에도 운영자가 어떤 명령도 내릴 수 없는 지속적 제어 상실 상태를 만들 수 있음
+- 제어 상실은 공정 폭주나 설비 손상으로 직결될 수 있고, 복구가 장치 교체·재구성과 수동 운전에 의존해 길어짐</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 결과 기법: 데이터 파괴(OTC-IR-02)·펌웨어 변조(OTC-PE-04.1)·HMI 무력화의 결과로 나타나며, 일시적이면 제어 거부(OTC-IM-01)
+- IT 랜섬웨어가 생산 시스템까지 번져 수동 운전으로 전환한 경우도 ATT&amp;CK은 제어 상실로 기록
+■ 실제 사례
+- [실제 사고] 독일 제철소(2014-12): 제어 구성요소가 잇따라 고장 나 용광로를 정상적으로 정지하지 못함 (INC-029)
+- [실제 사고] 2025 폴란드(2025-12): RTU·보호 계전기·HMI가 손상돼 통신과 제어를 잃음 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] 노르스크 하이드로(2019-03): LockerGoga 감염으로 생산 시스템 일부의 제어를 잃고 수동 운전으로 전환 (INC-019, ATT&amp;CK S0372)</t>
+        </is>
+      </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
           <t>T0827</t>
@@ -23961,7 +24320,7 @@
       <c r="J128" s="17" t="inlineStr"/>
       <c r="K128" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L128" s="17" t="inlineStr"/>
@@ -24049,7 +24408,16 @@
           <t>https://attack.mitre.org/techniques/T0827</t>
         </is>
       </c>
-      <c r="AM128" s="17" t="inlineStr"/>
+      <c r="AM128" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 제어 명령 실패·HMI 무응답·장치 통신 두절이 동시에 늘어나는지 감시
+- 원인 기법(와이퍼·펌웨어 변조·랜섬웨어) 탐지와 연계해 확산 범위 판단
+■ 대응
+- 중요 공정에 기계식 보호와 독립 안전계통을 두어 제어를 잃어도 안전 정지 보장
+- 예비 장치·백업 이미지와 수동 운전 절차를 준비하고 정기 훈련</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
@@ -24072,12 +24440,24 @@
           <t>생산·매출 손실</t>
         </is>
       </c>
-      <c r="E129" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause loss of productivity and revenue through disruption and even damage to the availability and integrity of control system operations, devices, and related processes.</t>
-        </is>
-      </c>
-      <c r="F129" s="17" t="inlineStr"/>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 직접 공격이나 분리되지 않은 IT 환경에 대한 랜섬웨어 공격으로 생산·출하·운송을 멈추게 해, 조직에 큰 생산·매출 손실을 일으킬 수 있음
+- 공정이 멀쩡해도 감염 확산을 우려한 예방적 중단이나 생산 관리 시스템 마비로 생산이 멈추며, 피해가 협력업체와 공급망으로 번짐</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 사고 DB에서 실제 사고가 가장 많이 연결된 행 — 대부분 IT 침해가 생산 관리·물류 시스템을 마비시키거나 OT 확산을 우려해 예방 중단한 경우('OT 관련도: IT 경유 OT 영향')
+- 경로: 랜섬웨어(OTC-IM-13), 와이퍼(OTC-IR-02), 협력업체 침해로 인한 부품 공급 중단, OT 직접 조작으로 인한 공정 정지
+- 영향 범위는 IT·OT 의존성에 좌우됨 — 생산 계획·출하 시스템(MES·ERP)이 멈추면 제어계통이 정상이어도 공장이 섬
+■ 실제 사례
+- [실제 사고] 콜로니얼 파이프라인(2021-05): IT 랜섬웨어 이후 OT 확산을 우려해 미국 동부 최대 연료 파이프라인을 약 6일간 세움 (INC-044)
+- [실제 사고] 노르스크 하이드로(2019-03): LockerGoga 감염으로 160여 생산 거점 대부분이 수동 운전으로 전환 (INC-019, ATT&amp;CK S0372)
+- [실제 사고] 재규어 랜드로버(2025-09): IT 시스템 차단으로 전 세계 생산이 5주 넘게 멈추고 협력업체로 피해가 번짐 (INC-070)</t>
+        </is>
+      </c>
       <c r="G129" s="17" t="inlineStr">
         <is>
           <t>T0828</t>
@@ -24096,7 +24476,7 @@
       <c r="J129" s="17" t="inlineStr"/>
       <c r="K129" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L129" s="17" t="inlineStr"/>
@@ -24182,7 +24562,16 @@
           <t>https://attack.mitre.org/techniques/T0828</t>
         </is>
       </c>
-      <c r="AM129" s="17" t="inlineStr"/>
+      <c r="AM129" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 랜섬웨어 전조(자격증명 탈취·대량 권한 상승·백업 삭제)를 IT·OT 경계에서 조기 탐지
+- 생산 실적·가동률 급변을 운영 지표로 감시하고 보안 이벤트와 상관 분석
+■ 대응
+- IT·OT 분리(DMZ·단방향 게이트웨이)와 IT 장애 시 최소 생산을 유지하는 OT 독립 운전 계획 수립
+- MES·히스토리언 등 생산 지원 시스템의 오프라인 백업과 복구 우선순위를 사업 연속성 계획에 반영</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="17" t="inlineStr">
@@ -24205,12 +24594,24 @@
           <t>감시 상실</t>
         </is>
       </c>
-      <c r="E130" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause a sustained or permanent loss of view where the ICS equipment will require local, hands-on operator intervention; for instance, a restart or manual operation.</t>
-        </is>
-      </c>
-      <c r="F130" s="17" t="inlineStr"/>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 HMI·RTU·센서 통신을 파괴하거나 감시 기능이 없는 펌웨어로 바꿔, 운영자가 현장에 가지 않고는 공정 상태를 볼 수 없게 만들 수 있음
+- 물리 공정은 돌아가도 상태를 확인할 수 없어 안전을 위해 수동 운전·운영 중단을 택하게 되며, 지속적 감시 상실은 현장 조치 없이는 회복되지 않음</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 결과 기법: HMI 화면 변조·삭제, 와이퍼, 센서 통신 방해, 펌웨어 다운그레이드, 원격 감시용 통신망(위성·셀룰러) 파괴의 결과
+- 일시적이면 감시 거부(OTC-IM-02), 값을 속이면 감시 화면 조작(OTC-IM-08)
+- 원격 감시에 의존하는 분산 설비(풍력·태양광·센서망)는 통신 장비 하나로 대규모 감시 상실이 일어남
+■ 실제 사례
+- [실제 사고] AcidRain(2022-02): 위성 모뎀이 파괴돼 독일 Enercon 풍력 발전기 약 5,800기의 원격 감시가 끊김 (INC-050)
+- [실제 사고] Unitronics(2023-11): HMI 화면을 공격자 그래픽으로 바꿔 운영자가 장치 상태를 볼 수 없게 함 (INC-005, ATT&amp;CK C0031)
+- [실제 사고] Fuxnet(2024-04): 센서 통신을 방해해 전체 감시 시스템에 감시 상실을 일으킴 (INC-023, ATT&amp;CK S1157)</t>
+        </is>
+      </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
           <t>T0829</t>
@@ -24229,7 +24630,7 @@
       <c r="J130" s="17" t="inlineStr"/>
       <c r="K130" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L130" s="17" t="inlineStr"/>
@@ -24266,7 +24667,7 @@
       </c>
       <c r="Z130" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 11건(최근 1) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 10건(최근 1) · ATT&amp;CK 사례 7건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA130" s="17" t="inlineStr">
@@ -24275,7 +24676,7 @@
         </is>
       </c>
       <c r="AB130" s="17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC130" s="17" t="n">
         <v>1</v>
@@ -24299,12 +24700,12 @@
       </c>
       <c r="AI130" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 7 · 분석 4</t>
+          <t>ATT&amp;CK 공식 6 · 분석 4</t>
         </is>
       </c>
       <c r="AJ130" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-003, INC-005, INC-007, INC-008, INC-019, INC-023, INC-025, INC-038, INC-039, INC-050</t>
+          <t>INC-003, INC-005, INC-007, INC-008, INC-019, INC-023, INC-025, INC-038, INC-039, INC-050</t>
         </is>
       </c>
       <c r="AK130" s="17" t="inlineStr">
@@ -24317,7 +24718,16 @@
           <t>https://attack.mitre.org/techniques/T0829</t>
         </is>
       </c>
-      <c r="AM130" s="17" t="inlineStr"/>
+      <c r="AM130" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 텔레메트리 공백이 여러 장치·사이트에서 동시에 생기는지 감시
+- HMI 화면·프로젝트 파일의 무결성과 통신 장비 상태를 정기 점검
+■ 대응
+- 독립 감시 경로(현장 표시기·대체 통신)와 감시 서비스 이중화 확보
+- 감시 상실 시 안전 상태 판단·현장 순회 절차를 마련하고 정기 훈련</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="inlineStr">
@@ -24340,12 +24750,24 @@
           <t>제어 조작</t>
         </is>
       </c>
-      <c r="E131" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may manipulate physical process control within the industrial environment.</t>
-        </is>
-      </c>
-      <c r="F131" s="17" t="inlineStr"/>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 설정값·태그·파라미터를 바꾸거나 직접 명령을 보내 물리 공정을 의도대로 움직일 수 있음
+- 차단기 개방·밸브 개폐·원심분리기 속도 변화처럼 결과가 곧바로 물리 세계에 나타나며, 운영자 화면까지 속이면 조작 사실을 늦게 알아챔</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 결과 기법: 비인가 명령 메시지(OTC-IP-03.1)·파라미터 변조(OTC-IP-02)·제어 프로그램 변조(OTC-PE-03)·HMI 원격 조작(OTC-EX-03)의 결과
+- 고도화된 공격(Stuxnet·Industroyer)과 인터넷 노출 HMI를 노린 단순 조작(핵티비스트·내부자)이 모두 같은 결과에 이름
+- 2024년 이후 노출 HMI 조작 사고가 수도·댐·지역 유틸리티에서 반복됨 — 원격 접속 관리 부재가 공통 원인
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): 운영자 HMI를 원격 조작해 운전 중인 차단기를 열어 정전 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 노르웨이 브레망에르 댐(2025-04): 약한 암호의 웹 제어 화면으로 방류 밸브를 열어 약 4시간 과다 방류 (INC-068)
+- [실제 사고] 캔자스 수도조합(2019-03): 퇴사 직원이 원격 접속으로 정수장 세척·소독 공정을 정지 (INC-043)</t>
+        </is>
+      </c>
       <c r="G131" s="17" t="inlineStr">
         <is>
           <t>T0831</t>
@@ -24364,7 +24786,7 @@
       <c r="J131" s="17" t="inlineStr"/>
       <c r="K131" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L131" s="17" t="inlineStr"/>
@@ -24452,7 +24874,16 @@
           <t>https://attack.mitre.org/techniques/T0831</t>
         </is>
       </c>
-      <c r="AM131" s="17" t="inlineStr"/>
+      <c r="AM131" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 운영자 조작 기록이 없는 상태 변화, 근무 외 시간 조작, 원격 접속 세션 중 설정 변경을 공정 이력과 접속 로그로 대조
+- 원인 기법(비인가 명령·파라미터 변조) 탐지와 연계
+■ 대응
+- 원격 접속을 다중 인증·세션 기록·승인 절차로 통제하고 퇴사자 계정을 즉시 회수
+- 중요 동작은 현장 인터록·한계값·독립 안전계통으로 보호하고, 통신 인증을 지원하는 프로토콜 적용</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="17" t="inlineStr">
@@ -24475,12 +24906,22 @@
           <t>감시 화면 조작</t>
         </is>
       </c>
-      <c r="E132" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to manipulate the information reported back to operators or controllers.</t>
-        </is>
-      </c>
-      <c r="F132" s="17" t="inlineStr"/>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영자·제어기에 보고되는 정보를 조작해, 실제 공정과 다른 상태를 화면에 보여 줄 수 있음
+- 조작된 화면을 믿은 운영자가 잘못 조치하거나 위험을 놓치게 되며, 보호 기능이 동작해야 할 상황도 가려짐</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 수법: 정상 시기의 공정 입력을 녹화해 재생, I/O 이미지 조작(OTC-IR-05), 위조 보고 메시지(OTC-IP-03.2), 허위 상태 코드 전송
+- 감시 상실(OTC-IM-06)과 달리 화면이 살아 있어 운영자가 이상을 의심하지 않음 — 독립 계측과 대조하지 않으면 드러나지 않음
+■ 실제 사례
+- [실제 사고] Stuxnet(2010-06): 공정 입력을 재생하고 I/O 이미지를 조작해 운영자 화면에 정상값을 보여 줌 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] 2016 우크라이나(2016-12): Industroyer의 OPC 모듈이 '한계 초과' 상태 코드를 보내 운영자가 보호 계전기 상태를 오판하게 함 (INC-003, ATT&amp;CK S0604)</t>
+        </is>
+      </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
           <t>T0832</t>
@@ -24499,7 +24940,7 @@
       <c r="J132" s="17" t="inlineStr"/>
       <c r="K132" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L132" s="17" t="inlineStr"/>
@@ -24587,7 +25028,16 @@
           <t>https://attack.mitre.org/techniques/T0832</t>
         </is>
       </c>
-      <c r="AM132" s="17" t="inlineStr"/>
+      <c r="AM132" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 같은 변수를 독립 계측·현장 표시기와 주기적으로 대조
+- 값이 비정상적으로 일정하거나 반복 패턴을 보이는지 히스토리언으로 분석
+■ 대응
+- 보고 통신 무결성 보호(IEC 62351 등)와 독립 감시 경로 확보
+- 안전 판단은 독립 안전계통과 현장 계측에 두고, 운영자 교육에 '화면 불일치' 대응 시나리오 포함</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
@@ -24610,12 +25060,21 @@
           <t>보호 기능 상실</t>
         </is>
       </c>
-      <c r="E133" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may compromise protective system functions designed to prevent the effects of faults and abnormal conditions.</t>
-        </is>
-      </c>
-      <c r="F133" s="17" t="inlineStr"/>
+      <c r="E133" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 고장·이상 상태의 영향을 막도록 설계된 보호 기능(보호 계전기 등)을 무력화해, 설비 손상과 장기 공정 중단, 인명 위험을 키울 수 있음
+- 많은 고장은 사람이 반응하기에 너무 빨리 진행되므로, 자동 보호가 꺼지면 다른 공격이나 일반 고장이 곧바로 큰 사고로 번짐</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 변전소 보호 계전기·차단기 보호 기능, 설비 보호 인터록 (L0~L1)
+- 경로: 보호 장치 서비스 거부(OTC-IR-03), 펌웨어 업데이트 모드 활성화(OTC-IR-01), 보호 설정 변경 — 안전 상실(OTC-IM-11)이 안전계통을 노린다면 이 행은 설비 보호 기능을 노림
+■ 실제 사례
+- [실제 사고] 2016 우크라이나(2016-12): Industroyer가 CVE-2015-5374로 Siemens SIPROTEC 보호 계전기에 서비스 거부를 일으켜 보호 기능을 무력화 (INC-003, ATT&amp;CK S0604)</t>
+        </is>
+      </c>
       <c r="G133" s="17" t="inlineStr">
         <is>
           <t>T0837</t>
@@ -24634,7 +25093,7 @@
       <c r="J133" s="17" t="inlineStr"/>
       <c r="K133" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L133" s="17" t="inlineStr"/>
@@ -24716,7 +25175,16 @@
           <t>https://attack.mitre.org/techniques/T0837</t>
         </is>
       </c>
-      <c r="AM133" s="17" t="inlineStr"/>
+      <c r="AM133" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 보호 장치 상태 보고 중단·자기진단 경보를 감시
+- 보호 장치를 향한 비정상 통신(취약점 공격 패턴, 업데이트 모드 전환)을 OT 네트워크 감시로 탐지
+■ 대응
+- 보호 계통 이중화, 장치 펌웨어 갱신, 보호 장치 관리 접근 제한
+- 보호 기능이 무력화되면 운전을 제한하고 현장 감시를 강화하는 절차 마련</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="17" t="inlineStr">
@@ -24739,12 +25207,23 @@
           <t>재산·설비 피해</t>
         </is>
       </c>
-      <c r="E134" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause damage and destruction of property to infrastructure, equipment, and the surrounding environment when attacking control systems.</t>
-        </is>
-      </c>
-      <c r="F134" s="17" t="inlineStr"/>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어 시스템을 조작해 설비·기반시설과 주변 환경에 물리적 손상과 파괴를 일으킬 수 있음
+- 피해가 장비 교체·환경 복구·인명 피해로 이어져 사이버 공격 가운데 복구 비용과 시간이 가장 크고, 원인이 단순 고장으로 오인되기도 함</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 결과 기법: 제어 조작(OTC-IM-07)·안전 상실(OTC-IM-11)·I/O 무차별 조작(OTC-IP-01) 등이 설비 한계를 넘을 때 나타남
+- 공개 사고 근거는 하수 방류(환경), 트램 탈선(인명·설비), 용광로 손상(설비)이며, 실증으로 발전기 파괴(Aurora)가 있음
+■ 실제 사례
+- [실제 사고] 독일 제철소(2014-12): 생산망 침투 뒤 용광로를 정상 정지하지 못해 설비가 크게 손상 (INC-029)
+- [실제 사고] 폴란드 우치 트램(2008-01): 적외선 신호로 선로 전환기를 조작해 트램 4대가 탈선하고 승객이 다침 (INC-027)
+- [실증] Aurora 시험(2007-03): 원격 차단기 명령만으로 디젤 발전기를 물리적으로 파괴 (INC-077)</t>
+        </is>
+      </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
           <t>T0879</t>
@@ -24763,7 +25242,7 @@
       <c r="J134" s="17" t="inlineStr"/>
       <c r="K134" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L134" s="17" t="inlineStr"/>
@@ -24852,7 +25331,16 @@
           <t>https://attack.mitre.org/techniques/T0879</t>
         </is>
       </c>
-      <c r="AM134" s="17" t="inlineStr"/>
+      <c r="AM134" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 설비 상태 감시(진동·온도·운전 한계)와 보안 이벤트를 함께 분석해 사이버 원인 가능성을 조기 판단
+- 물리 사고 조사 절차에 사이버 포렌식(제어기 로직·명령 이력 확인)을 포함
+■ 대응
+- 기계식 보호 계층과 독립 안전계통으로 위험 한계를 물리적으로 보장(사이버 조작으로 넘을 수 없게 설계)
+- 결과 중심 위험 평가로 물리 피해를 일으킬 수 있는 제어 경로를 찾아 우선 보호</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
@@ -24875,12 +25363,22 @@
           <t>안전 상실</t>
         </is>
       </c>
-      <c r="E135" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may compromise safety system functions designed to maintain safe operation of a process when unacceptable or dangerous conditions occur.</t>
-        </is>
-      </c>
-      <c r="F135" s="17" t="inlineStr"/>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 위험 상황에서 공정을 안전하게 정지시키는 안전계통(SIS) 기능을 무력화하거나 다시 프로그래밍해, 위험 상태가 계속되게 할 수 있음
+- 안전계통은 사람이 대응하기에 너무 빠른 위험을 막는 마지막 방어선이라, 제어계통 조작과 결합되면 폭발·유독물 누출 같은 인명 사고로 이어질 수 있음</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 안전 계장 시스템(SIS)의 안전 제어기(예: Triconex)와 안전 엔지니어링 워크스테이션 (L1~L2)
+- 수법: 안전 로직 재프로그래밍(OTC-LM-01.3)·펌웨어 메모리 변조(OTC-PE-04.1)로 위험 상태를 허용하게 한 뒤 DCS로 위험 상태를 만듦
+- 안전계통과 제어계통이 네트워크·엔지니어링 단말을 공유하면 그 자체가 공격 경로가 됨
+■ 실제 사례
+- [실제 사고] Triton(2017-08): SIS 로직을 재프로그래밍해 위험 상태를 허용하게 하는 도구로 Triconex 안전 제어기를 공격했고, 오류로 안전 정지가 일어나 발견됨 (INC-004, ATT&amp;CK S1009)</t>
+        </is>
+      </c>
       <c r="G135" s="17" t="inlineStr">
         <is>
           <t>T0880</t>
@@ -24899,7 +25397,7 @@
       <c r="J135" s="17" t="inlineStr"/>
       <c r="K135" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L135" s="17" t="inlineStr"/>
@@ -24986,7 +25484,16 @@
           <t>https://attack.mitre.org/techniques/T0880</t>
         </is>
       </c>
-      <c r="AM135" s="17" t="inlineStr"/>
+      <c r="AM135" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 안전 제어기의 운전 모드(키스위치)·로직 변경·진단 경보를 상시 감시
+- 안전 엔지니어링 단말 접속과 안전 프로토콜(예: TriStation) 통신을 OT 네트워크 감시로 경보
+■ 대응
+- 안전계통을 제어계통과 물리·논리적으로 분리하고 전용 엔지니어링 단말 사용
+- 안전 제어기 키스위치를 RUN에 두고 변경 시 현장 승인을 받게 하며, 기계식 보호 계층 유지</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="17" t="inlineStr">
@@ -25009,12 +25516,24 @@
           <t>운영 정보 탈취</t>
         </is>
       </c>
-      <c r="E136" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may steal operational information on a production environment as a direct mission outcome for personal gain or to inform future operations.</t>
-        </is>
-      </c>
-      <c r="F136" s="17" t="inlineStr"/>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 설계 도면·운전 절차·네트워크 구성·공정 정보 같은 운영 정보를 훔쳐, 직접적인 이득을 얻거나 이후 OT 공격 설계에 쓸 수 있음
+- 탈취 시점에는 물리 피해가 없어 대응 우선순위가 낮아지기 쉽지만, 정밀 공격의 사전 준비이자 기반시설 정보 유출이라 영향이 큼</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: CAD 도면·P&amp;ID·운전 매뉴얼·PLC 프로젝트 파일·네트워크 구성, 공급업체·통합업체가 보관한 고객 프로젝트 파일, 카메라 영상 (L2~L4)
+- 경로: 정보 수집형 악성코드(Duqu·Flame·ACAD/Medre.A), 공급업체 침해, 클라우드 관리 플랫폼 계정 탈취
+- 통합: Enterprise 반출 기법(T1041·T1048.003·T1567.004 등) — 반출 전술이 없는 ICS 매트릭스에서 운영 정보 유출로 표현
+■ 실제 사례
+- [실제 사고] 2025 폴란드(2025-12): 훔친 민감 운영 정보를 OT 시스템 공격 계획에 사용 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] 한국수력원자력(2014-12): 원전 설계도면·운전 매뉴얼이 유출·공개되고 가동 중단 협박이 이어짐 (INC-073)
+- [실제 사고] 텔벤트(2012-09): 파이프라인 SCADA 공급업체가 침해돼 고객사 프로젝트 파일이 유출 (INC-076)</t>
+        </is>
+      </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
           <t>T0882</t>
@@ -25037,7 +25556,7 @@
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L136" s="17" t="inlineStr"/>
@@ -25130,7 +25649,16 @@
           <t>https://attack.mitre.org/techniques/T0882</t>
         </is>
       </c>
-      <c r="AM136" s="17" t="inlineStr"/>
+      <c r="AM136" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 설계·프로젝트 파일 저장소의 대량 접근·압축·외부 전송을 DLP·네트워크 감시로 탐지
+- OT 영역에서 인터넷·클라우드 저장소로 향하는 비정상 전송을 경보
+■ 대응
+- 운영 정보를 기밀 등급으로 분류해 접근 통제·암호화하고, 공급업체에 보관·폐기 보안 요구사항 부과
+- OT 문서 저장소를 업무망과 분리하고 반출 승인 절차 운영</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
@@ -25153,12 +25681,24 @@
           <t>데이터 암호화(랜섬웨어)</t>
         </is>
       </c>
-      <c r="E137" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may encrypt data on target systems or on large numbers of systems in a network to interrupt availability to system and network resources.</t>
-        </is>
-      </c>
-      <c r="F137" s="17" t="inlineStr"/>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 랜섬웨어로 HMI·EWS·히스토리언·생산 관리 서버의 파일과 디스크를 암호화해, 운영 시스템을 쓸 수 없게 만들고 복구 대가를 요구할 수 있음
+- OT 자산까지 암호화되지 않아도 IT 감염과 OT 확산 우려만으로 운영을 멈추게 되며, 실제 OT 영향 사고에서 가장 자주 확인되는 경로임</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 HMI·EWS·SCADA 서버·히스토리언·MES·생산 계획 서버와 공유 드라이브 (L2~L4)
+- 흐름: 피싱·VPN 계정·경계 장비 취약점으로 IT 진입 → 자격증명 탈취(OTC-LM-07)·그룹 정책 배포(OTC-PV-04.1)로 확산 → ICS 서비스 중지(OTC-IR-09)·백업 삭제(OTC-IR-02) 뒤 암호화
+- ICS 매트릭스에 암호화 기법이 없어 Enterprise T1486을 편입 — 결과는 생산·매출 손실(OTC-IM-05)·감시 상실(OTC-IM-06)로 이어짐
+■ 실제 사례
+- [실제 사고] 천연가스 압축 시설(2020-02): 랜섬웨어가 OT망까지 들어와 HMI·히스토리언·폴링 서버를 암호화해 파이프라인 운영이 약 2일 멈춤 (INC-039)
+- [실제 사고] 노르스크 하이드로(2019-03): LockerGoga가 OS 핵심 파일까지 암호화해 생산 거점이 수동 운전으로 전환 (INC-019, ATT&amp;CK S0372)
+- [실제 사고] 나고야항(2023-07): 랜섬웨어로 컨테이너 터미널 시스템이 멈춰 반출입이 약 이틀 중단 (INC-056)</t>
+        </is>
+      </c>
       <c r="G137" s="17" t="inlineStr">
         <is>
           <t>T1486</t>
@@ -25177,7 +25717,7 @@
       <c r="J137" s="17" t="inlineStr"/>
       <c r="K137" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L137" s="17" t="inlineStr">
@@ -25229,7 +25769,7 @@
       </c>
       <c r="Z137" s="17" t="inlineStr">
         <is>
-          <t>실제 사고 15건(최근 1) · ATT&amp;CK 사례 8건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
+          <t>실제 사고 14건(최근 1) · ATT&amp;CK 사례 8건 · 공개 취약점 0건 · KEV 0건 · 실증·연구 0건</t>
         </is>
       </c>
       <c r="AA137" s="17" t="inlineStr">
@@ -25238,7 +25778,7 @@
         </is>
       </c>
       <c r="AB137" s="17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC137" s="17" t="n">
         <v>1</v>
@@ -25262,12 +25802,12 @@
       </c>
       <c r="AI137" s="17" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 공식 6 · 분석 9</t>
+          <t>ATT&amp;CK 공식 5 · 분석 9</t>
         </is>
       </c>
       <c r="AJ137" s="17" t="inlineStr">
         <is>
-          <t>INC-002, INC-015, INC-016, INC-017, INC-019, INC-020, INC-038, INC-039, INC-044, INC-045, INC-051, INC-053, INC-054, INC-056, INC-071</t>
+          <t>INC-015, INC-016, INC-017, INC-019, INC-020, INC-038, INC-039, INC-044, INC-045, INC-051, INC-053, INC-054, INC-056, INC-071</t>
         </is>
       </c>
       <c r="AK137" s="17" t="inlineStr">
@@ -25280,7 +25820,16 @@
           <t>https://attack.mitre.org/techniques/T1486</t>
         </is>
       </c>
-      <c r="AM137" s="17" t="inlineStr"/>
+      <c r="AM137" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 변경·확장자 변경, 섀도 복사본 삭제, ICS 서비스 일괄 종료를 엔드포인트 감시로 경보
+- IT·OT 경계에서 도메인 관리자 계정의 OT 자산 접근과 그룹 정책 변경을 탐지
+■ 대응
+- IT·OT 계정·도메인 분리, OT 단말 애플리케이션 허용 목록, 오프라인·변경 불가 백업과 복원 훈련
+- IT 장애 시 OT 독립 운전 계획을 세워 예방적 중단 범위를 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="17" t="inlineStr">
@@ -25303,12 +25852,23 @@
           <t>대역폭 탈취(봇넷 편입)</t>
         </is>
       </c>
-      <c r="E138" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage the network bandwidth resources of co-opted systems to complete resource-intensive tasks, which may impact system and/or hosted service availability.</t>
-        </is>
-      </c>
-      <c r="F138" s="17" t="inlineStr"/>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 기본 자격증명·알려진 취약점으로 장악한 IoT 기기와 경계 장비를 봇넷에 편입해, 그 대역폭으로 다른 대상에 DDoS를 하거나 공격 트래픽을 중계할 수 있음
+- 기기 소유자는 성능 저하와 평판 손상만 겪어 침해를 알아채지 못하는 경우가 많고, 같은 접근이 이후 OT 공격 거점으로 쓰일 수 있음</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: IP 카메라·DVR·NVR·라우터·산업용 셀룰러 게이트웨이, OT 경계 방화벽 (L3.5·IoT)
+- 경로: 인터넷 노출 장치(OTC-IA-11)·기본 자격증명(OTC-PE-05.1)·공개 애플리케이션 취약점(OTC-IA-02) — KEV에 등재된 IoT 취약점 다수가 봇넷 편입에 쓰임
+- 공격자 관점의 공격 인프라 탈취(OTC-RD-01.1)를 기기 소유자 피해 관점에서 본 행 — 클라우드 매트릭스 대역폭 탈취(T1496.002)와 연계
+■ 실제 사례
+- [실제 사고] Mirai(2016-10): 텔넷 기본 계정으로 IoT 기기 수십만 대를 봇넷에 편입해 대규모 DDoS를 일으킴 (INC-032)
+- [실제 사고] 덴마크 에너지 기업(2023-05): 침해된 경계 방화벽 일부가 Mirai 계열 봇넷에 편입 (INC-055)</t>
+        </is>
+      </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
           <t>T1496.002</t>
@@ -25327,7 +25887,7 @@
       <c r="J138" s="17" t="inlineStr"/>
       <c r="K138" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L138" s="17" t="inlineStr">
@@ -25425,7 +25985,16 @@
           <t>https://attack.mitre.org/techniques/T1496/002</t>
         </is>
       </c>
-      <c r="AM138" s="17" t="inlineStr"/>
+      <c r="AM138" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IoT·경계 장비의 비정상 아웃바운드 트래픽(대량 연결·DDoS 패턴)과 알려진 C2로의 통신을 네트워크 감시로 경보
+- 장치 프로세스·설정 변경과 텔넷·SSH 로그인 시도 수집
+■ 대응
+- 기본 자격증명 변경, 펌웨어 갱신, 인터넷에 노출된 관리 인터페이스 제거
+- IoT 기기는 별도 망으로 분리하고 외부 통신을 허용 목록으로 제한</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:AM138"/>
@@ -25894,9 +26463,10 @@
           <t>드라이브바이 침해</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may gain access to a system during a drive-by compromise, when a user visits a website as part of a regular browsing session.</t>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 종사자·협력업체가 자주 찾는 업계·공급업체 웹사이트를 침해해(워터링 홀), 방문한 업무 단말에 악성코드를 내려받게 할 수 있음
+- 정상 업무 사이트 방문만으로 감염되고 특정 업계 종사자를 골라 노릴 수 있으며, 이렇게 확보한 자격증명·단말이 이후 OT 접근의 발판이 됨</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -25940,7 +26510,16 @@
       <c r="N8" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="O8" s="17" t="inlineStr"/>
+      <c r="O8" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹 프록시·IDS로 알려진 악성 스크립트·리디렉션과 브라우저 하위 프로세스 생성 탐지
+- 업무 단말에서 OT 영역으로 향하는 새로운 접속을 경보
+■ 대응
+- OT 접근 단말에서 인터넷 사용을 분리(점프 호스트·전용 단말)하고 브라우저 격리·익스플로잇 보호 적용
+- 웹 필터링과 브라우저·플러그인의 신속한 업데이트</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
@@ -25963,9 +26542,10 @@
           <t>공개 애플리케이션 취약점 악용</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage weaknesses to exploit internet-facing software for initial access into an industrial network.</t>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 인터넷에 노출된 HMI·SCADA 웹 서버·VPN·방화벽·라우터·IoT 기기의 취약점을 악용해 OT 환경이나 그 경계에 처음 들어올 수 있음
+- 원격 관리를 위해 일부러 노출한 장비가 많고 패치 주기가 길어, 공개된 취약점이 오랫동안 악용 가능한 상태로 남음</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -26009,7 +26589,16 @@
       <c r="N9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O9" s="17" t="inlineStr"/>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 노출 장비의 웹 접근 로그·WAF로 익스플로잇 패턴과 비정상 요청을 탐지하고 장비의 비정상 프로세스·재시작 확인
+- 경계 장비의 관리 접속·설정 변경·새 계정 생성을 중앙으로 수집
+■ 대응
+- OT 장비의 인터넷 노출을 없애고 불가피하면 VPN·점프 호스트 뒤로 옮기며, KEV 등재 취약점은 우선 패치
+- 외부 공격 표면 점검(인터넷 스캔 결과 확인)을 정기 수행하고 노출 장비 대장 관리</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -26032,9 +26621,10 @@
           <t>외부 원격 서비스 악용</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage external remote services as a point of initial access into your network.</t>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 VPN·원격 데스크톱·원격 접속 도구·무선 원격 링크 같은 외부 원격 서비스에 탈취하거나 남아 있는 계정으로 접속해, 정상 원격 운영자처럼 OT 환경에 들어올 수 있음
+- 정상 원격 유지보수 경로를 쓰므로 공격 트래픽이 구분되지 않고, 다중 인증이 없는 휴면·퇴사자 계정이 반복해서 침투 경로가 됨</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -26078,7 +26668,16 @@
       <c r="N10" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="O10" s="17" t="inlineStr"/>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- VPN·원격 접속 인증 로그에서 비정상 시간대·출발지·동시 세션과 휴면 계정 사용을 경보
+- 원격 접속 세션 중 OT 자산 접근·설정 변경을 세션 기록과 대조
+■ 대응
+- 원격 접속은 다중 인증·점프 호스트 경유·세션 기록·필요할 때만 여는 승인제로 운영하고, 퇴사자·벤더 계정을 즉시 회수
+- 경계 VPN 장비는 KEV 취약점을 우선 패치하고 관리 인터페이스를 인터넷에서 분리</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -26101,9 +26700,10 @@
           <t>이동식 매체 전파</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may move onto systems, such as those separated from the enterprise network, by copying malware to removable media which is inserted into the control systems environment.</t>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 USB 같은 이동식 매체에 악성코드를 실어, 업무망과 분리된 제어계통 단말까지 감염을 옮길 수 있음
+- 협력업체·유지보수 인력이 가져오는 매체가 경로가 되는 경우가 많고, 폐쇄망이라는 믿음 때문에 매체 반입 통제가 느슨한 시설이 많음</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -26147,7 +26747,16 @@
       <c r="N11" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O11" s="17" t="inlineStr"/>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이동식 매체 연결 뒤 실행된 프로세스와 매체에서 시작된 파일 쓰기를 엔드포인트 감시로 탐지
+- 매체 반입 기록과 단말별 매체 사용 로그 대조
+■ 대응
+- 자동 실행을 끄고 허가된 매체만 쓰게 하며, 반입 전 검사 키오스크 운영
+- 협력업체 매체 반입 절차와 교육, 프로젝트 파일은 검사된 전용 경로로 전달</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
@@ -26170,9 +26779,10 @@
           <t>위장 마스터</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may setup a rogue master to leverage control server functions to communicate with outstations.</t>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 마스터(제어 서버)를 가장한 장치를 통신망에 붙여, 현장 장치에 정상 형식의 제어 메시지를 보내거나 실제 마스터로 가는 트래픽을 가로챌 수 있음
+- 인증 없는 프로토콜에서는 현장 장치가 진짜와 가짜 마스터를 구분하지 못해 명령이 그대로 실행됨</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -26216,7 +26826,16 @@
       <c r="N12" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="17" t="inlineStr"/>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자산 대장에 없는 장치·주소에서 나오는 마스터 기능 트래픽을 OT 네트워크 감시로 경보
+- 같은 슬레이브에 명령하는 마스터가 둘 이상인지 확인
+■ 대응
+- 통신 인증(IEC 62351·DNP3-SA)과 장치 허용 목록, 포트 보안(미사용 포트 차단) 적용
+- 무선 원격 링크는 암호화·주파수 관리를 하고, 장비 분실·퇴사 시 키 교체</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
@@ -26239,9 +26858,10 @@
           <t>무선 통신 침해</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may perform wireless compromise as a method of gaining communications and unauthorized access to a wireless network.</t>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 같은 주파수의 무선 장비나 침해한 무선 기기로 OT 무선 통신망에 접근해, 원거리에서도 현장 장치와 통신할 수 있음
+- 무선 경보·원격 제어 신호는 인증·암호화 없이 동작하는 경우가 많아, 녹음·재전송만으로도 정상 명령처럼 받아들여짐</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -26285,7 +26905,16 @@
       <c r="N13" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O13" s="17" t="inlineStr"/>
+      <c r="O13" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 무선 네트워크의 새 장치·세션과 비정상 트래픽을 감시하고 무선 명령 이력을 운영 기록과 대조
+- 스펙트럼 감시로 비인가 송신·재밍 확인
+■ 대응
+- 무선 제어 신호에 암호화·재전송 방지·발신자 인증을 적용하고 신호 전파 범위를 최소화
+- 중요 명령은 무선으로 받은 뒤에도 현장 확인·인터록을 거치게 설계</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -26308,9 +26937,10 @@
           <t>공급망 침해</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may perform supply chain compromise to gain control systems environment access by means of infected products, software, and workflows.</t>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 ICS 장비·소프트웨어 공급업체의 배포 경로나 설치 과정을 침해해, 정상 제품·업데이트·설치 작업에 악성 요소를 섞어 OT 환경에 들여올 수 있음
+- 신뢰하는 공급업체 경로로 들어와 검사를 거치지 않는 경우가 많고, 같은 제품을 쓰는 여러 고객사로 동시에 퍼짐</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -26354,7 +26984,16 @@
       <c r="N14" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O14" s="17" t="inlineStr"/>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 배포 파일의 해시·서명을 벤더 공식 값과 대조하고 다운로드 파일 검사
+- 신규 장비·소프트웨어 설치 뒤 단말의 비정상 프로세스·통신을 집중 감시
+■ 대응
+- 공급업체 보안 요구사항(서명 배포·보안 개발 절차)을 계약에 반영하고 반입 전 검사 절차 운영
+- 설치·유지보수 작업에는 검사된 매체·도구만 쓰게 하고 작업 뒤 무결성 점검</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -26377,9 +27016,10 @@
           <t>임시 접속 자산 악용</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may target devices that are transient across ICS networks and external networks.</t>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 정비 노트북·진단 장비처럼 OT와 외부망을 오가는 임시 접속 자산을 감염시키거나 빼돌려, OT 환경에 직접 연결되는 통로로 쓸 수 있음
+- 임시 자산은 상주 자산과 달리 보안 관리 대상에서 빠지기 쉽고, 엔지니어링 소프트웨어와 접속 정보를 함께 갖고 있음</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -26423,7 +27063,16 @@
       <c r="N15" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="17" t="inlineStr"/>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 스위치 로그·네트워크 감시로 새 MAC 주소와 임시 장치 연결 탐지
+- 임시 자산 연결 기록과 작업 지시서 대조
+■ 대응
+- 임시 자산은 등록·검사(백신·패치·무결성)를 마친 뒤에만 연결을 허용하고 전용 연결 구간 운영
+- 정비 장비의 분실·반납 관리와 엔지니어링 소프트웨어 계정 관리</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -26446,9 +27095,10 @@
           <t>스피어피싱 첨부파일</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may use a spearphishing attachment, a variant of spearphishing, as a form of a social engineering attack against specific targets.</t>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 특정 조직·직원을 노린 메일에 악성 문서·설치 파일을 첨부하거나 링크를 넣어, 업무 단말을 감염시키고 OT 접근의 발판을 만들 수 있음
+- OT 공격 대부분이 IT 업무망 침투에서 시작되며, 감염 단말에서 VPN·원격 접속 자격증명을 빼내 제어망으로 넘어감</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -26492,7 +27142,16 @@
       <c r="N16" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="17" t="inlineStr"/>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 문서 프로그램이 만드는 비정상 하위 프로세스와 첨부파일 실행을 엔드포인트 감시로 탐지
+- 메일 보안 게이트웨이의 악성 첨부·링크 탐지와 사용자 신고 연계
+■ 대응
+- 매크로·실행 파일 첨부 차단, 메일 샌드박스, OT 담당자 대상 표적 피싱 훈련
+- OT 접근 계정을 업무 메일 계정과 분리하고 다중 인증 적용</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
@@ -26515,9 +27174,10 @@
           <t>원격 서비스 취약점 악용</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit a software vulnerability to take advantage of a programming error in a program, service, or within the operating system software or kernel itself to enable remote service abuse.</t>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 자산의 원격 서비스(SMB·RPC·데이터베이스·장치 웹 서버 등) 취약점을 악용해, 처음 진입하거나 내부에서 다른 자산으로 이동할 수 있음
+- 패치하기 어려운 노후 운영체제와 장치가 많아 오래된 취약점이 계속 유효하고, 웜형 악성코드는 IT에서 OT로 자동 확산됨</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -26556,12 +27216,21 @@
         </is>
       </c>
       <c r="M17" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N17" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="O17" s="17" t="inlineStr"/>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 네트워크 감시(DPI)로 익스플로잇 패턴과 내부의 대량 SMB·RPC 연결 확산 탐지
+- 서비스 충돌·비정상 종료 로그를 모아 악용 시도 확인
+■ 대응
+- 위험 기반 패치(운영 영향 검증 뒤 적용)와 패치할 수 없는 자산의 보완 통제(서비스 비활성화·구간 분리·허용 목록)
+- OT 구간 사이의 불필요한 SMB·RPC를 막고 망 분리</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -26584,9 +27253,10 @@
           <t>인터넷 노출 장치 악용</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may gain access into industrial environments through systems exposed directly to the internet for remote access rather than through External Remote Services.</t>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 원격 관리를 위해 인터넷에 직접 노출된 PLC·HMI·제어 장치에 접속해, 별도의 침투 없이 곧바로 OT 환경에 들어올 수 있음
+- 기본·약한 암호나 인증 없는 프로토콜이 그대로인 경우가 많아, 인터넷 스캔만으로 대상을 찾는 핵티비스트·봇넷의 손쉬운 표적이 됨</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -26630,7 +27300,16 @@
       <c r="N18" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O18" s="17" t="inlineStr"/>
+      <c r="O18" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 인터넷 출발지의 OT 장치 로그인·프로토콜 접속을 경보하고, 외부 스캔 서비스 결과로 자사 노출 장치를 정기 확인
+- 장치 화면·설정 변경을 접속 출발지와 대조
+■ 대응
+- OT 장치의 인터넷 직접 노출을 없애고(방화벽·VPN 뒤로) 셀룰러 모뎀 같은 숨은 연결을 점검
+- 기본 암호 변경과 인증 강화, 노출이 불가피하면 출발지 제한과 접속 감시</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
@@ -26653,9 +27332,10 @@
           <t>원격 서비스 악용</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage remote services to move between assets and network segments.</t>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 RDP·SSH·SMB·WMI·데이터베이스 접속·원격 지원 소프트웨어 같은 정상 원격 서비스로 OT 자산 사이를 오가며 운영자처럼 시스템을 조작할 수 있음
+- 운영 업무에 쓰는 서비스라 막기 어렵고, 탈취한 정상 계정으로 접속하면 일상 운영 활동과 구분되지 않음</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -26694,12 +27374,21 @@
         </is>
       </c>
       <c r="M19" s="20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N19" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="O19" s="17" t="inlineStr"/>
+      <c r="O19" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 서비스 접속의 출발지·시간대·계정을 기준선과 비교하고 IT 계정의 OT 자산 접속을 경보
+- 점프 호스트 세션 기록과 OT 자산 변경 이력 대조
+■ 대응
+- OT 원격 접속을 점프 호스트로 일원화하고 다중 인증·세션 기록을 적용하며 구간 사이 RDP·SMB 직접 연결 차단
+- 원격 지원 소프트웨어 사용을 승인된 도구·시간으로 제한</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
@@ -26970,7 +27659,7 @@
         </is>
       </c>
       <c r="M23" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N23" s="20" t="n">
         <v>7</v>
@@ -28380,7 +29069,7 @@
         </is>
       </c>
       <c r="M43" s="20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N43" s="20" t="n">
         <v>10</v>
@@ -28725,7 +29414,7 @@
         </is>
       </c>
       <c r="M48" s="20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N48" s="20" t="n">
         <v>10</v>
@@ -28863,7 +29552,7 @@
         </is>
       </c>
       <c r="M50" s="20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N50" s="20" t="n">
         <v>15</v>
@@ -29445,7 +30134,7 @@
         </is>
       </c>
       <c r="M58" s="20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N58" s="20" t="n">
         <v>11</v>
@@ -29583,7 +30272,7 @@
         </is>
       </c>
       <c r="M60" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N60" s="20" t="n">
         <v>9</v>
@@ -29790,7 +30479,7 @@
         </is>
       </c>
       <c r="M63" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N63" s="20" t="n">
         <v>7</v>
@@ -30439,9 +31128,10 @@
           <t>원격 서비스 취약점 악용</t>
         </is>
       </c>
-      <c r="E73" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit a software vulnerability to take advantage of a programming error in a program, service, or within the operating system software or kernel itself to enable remote service abuse.</t>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 자산의 원격 서비스(SMB·RPC·데이터베이스·장치 웹 서버 등) 취약점을 악용해, 처음 진입하거나 내부에서 다른 자산으로 이동할 수 있음
+- 패치하기 어려운 노후 운영체제와 장치가 많아 오래된 취약점이 계속 유효하고, 웜형 악성코드는 IT에서 OT로 자동 확산됨</t>
         </is>
       </c>
       <c r="F73" s="17" t="inlineStr">
@@ -30480,12 +31170,21 @@
         </is>
       </c>
       <c r="M73" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N73" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="O73" s="17" t="inlineStr"/>
+      <c r="O73" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 네트워크 감시(DPI)로 익스플로잇 패턴과 내부의 대량 SMB·RPC 연결 확산 탐지
+- 서비스 충돌·비정상 종료 로그를 모아 악용 시도 확인
+■ 대응
+- 위험 기반 패치(운영 영향 검증 뒤 적용)와 패치할 수 없는 자산의 보완 통제(서비스 비활성화·구간 분리·허용 목록)
+- OT 구간 사이의 불필요한 SMB·RPC를 막고 망 분리</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
@@ -30549,7 +31248,7 @@
         </is>
       </c>
       <c r="M74" s="20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N74" s="20" t="n">
         <v>15</v>
@@ -30577,9 +31276,10 @@
           <t>원격 서비스 악용</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage remote services to move between assets and network segments.</t>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 RDP·SSH·SMB·WMI·데이터베이스 접속·원격 지원 소프트웨어 같은 정상 원격 서비스로 OT 자산 사이를 오가며 운영자처럼 시스템을 조작할 수 있음
+- 운영 업무에 쓰는 서비스라 막기 어렵고, 탈취한 정상 계정으로 접속하면 일상 운영 활동과 구분되지 않음</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr">
@@ -30618,12 +31318,21 @@
         </is>
       </c>
       <c r="M75" s="20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N75" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="O75" s="17" t="inlineStr"/>
+      <c r="O75" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 서비스 접속의 출발지·시간대·계정을 기준선과 비교하고 IT 계정의 OT 자산 접속을 경보
+- 점프 호스트 세션 기록과 OT 자산 변경 이력 대조
+■ 대응
+- OT 원격 접속을 점프 호스트로 일원화하고 다중 인증·세션 기록을 적용하며 구간 사이 RDP·SMB 직접 연결 차단
+- 원격 지원 소프트웨어 사용을 승인된 도구·시간으로 제한</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
@@ -30894,7 +31603,7 @@
         </is>
       </c>
       <c r="M79" s="20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N79" s="20" t="n">
         <v>8</v>
@@ -31446,7 +32155,7 @@
         </is>
       </c>
       <c r="M87" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N87" s="20" t="n">
         <v>5</v>
@@ -32285,7 +32994,7 @@
         </is>
       </c>
       <c r="M99" s="20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N99" s="20" t="n">
         <v>13</v>
@@ -32838,7 +33547,7 @@
         </is>
       </c>
       <c r="M106" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N106" s="20" t="n">
         <v>7</v>
@@ -34139,9 +34848,10 @@
           <t>제어 거부</t>
         </is>
       </c>
-      <c r="E123" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause a denial of control to temporarily prevent operators and engineers from interacting with process controls.</t>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어 장치와의 통신을 끊거나 원격 복구에 필요한 장치를 무력화해, 운영자·엔지니어가 한동안 공정을 조작하지 못하게 할 수 있음
+- 공정은 계속 돌아가지만 이상이 생겨도 원격으로 개입할 수 없어, 다른 조작과 결합되면 피해가 걷잡을 수 없이 커짐</t>
         </is>
       </c>
       <c r="F123" s="17" t="inlineStr">
@@ -34177,7 +34887,16 @@
       <c r="N123" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O123" s="17" t="inlineStr"/>
+      <c r="O123" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- ATT&amp;CK에 표준 탐지 방법이 없는 결과 기법 — 원인 기법(통신 차단·장치 정지·데이터 파괴) 탐지로 대응
+- 제어 명령 실패·무응답 이벤트를 장치·채널별로 모아 동시다발 여부 확인
+■ 대응
+- 대역 외 통신 채널과 서비스 이중화로 원격 제어 경로를 확보하고 수동 운전 절차를 정기 훈련
+- 장치 설정·프로그램 백업으로 재구성 시간 단축</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="17" t="inlineStr">
@@ -34200,9 +34919,10 @@
           <t>감시 거부</t>
         </is>
       </c>
-      <c r="E124" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause a denial of view in attempt to disrupt and prevent operator oversight on the status of an ICS environment.</t>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치와 제어 시스템 사이 통신을 일시적으로 방해해, 운영자가 공정 상태를 보지 못하게 할 수 있음
+- 방해가 그치면 화면이 회복되는 일시적 현상이라 통신 장애로 넘기기 쉽고, 그 사이 이뤄진 조작은 운영자 눈에 띄지 않음</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
@@ -34238,7 +34958,16 @@
       <c r="N124" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O124" s="17" t="inlineStr"/>
+      <c r="O124" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 텔레메트리 공백·갱신 지연을 장치·채널별로 감시해 원인 기법 추적
+- 통신 장애 기록과 같은 시간대의 운영 변경·명령 이력을 함께 검토
+■ 대응
+- 대역 외 감시 수단(현장 계측·독립 감시 경로) 확보와 감시 서비스 이중화
+- 통신 장애 시 현장 확인 절차를 운영 매뉴얼에 포함</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="inlineStr">
@@ -34261,9 +34990,10 @@
           <t>가용성 상실</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to disrupt essential components or systems to prevent owner and operator from delivering products or services.</t>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 핵심 구성요소를 방해하거나 HMI·워크스테이션·데이터베이스의 데이터를 지우거나 암호화해, 운영 조직이 제품·서비스를 공급하지 못하게 할 수 있음
+- 전력·난방·연료·철도처럼 공공 서비스가 끊기면 피해가 조직 밖 사회 전체로 번지고, 예방 차원의 운영 중단도 같은 결과를 낳음</t>
         </is>
       </c>
       <c r="F125" s="17" t="inlineStr">
@@ -34299,7 +35029,16 @@
       <c r="N125" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="O125" s="17" t="inlineStr"/>
+      <c r="O125" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 원인 기법 탐지와 함께 공급량·가동률 같은 서비스 지표의 급변을 감시
+- 공급 중단 시 IT·OT 이벤트 시간대를 맞춰 원인 영역(OT 직접 조작 vs IT 경유)을 빠르게 판정
+■ 대응
+- 서비스 이중화, 대역 외 운영 수단, 수동 운전·현장 복구 절차를 준비하고 정기 훈련
+- 핵심 데이터·설정을 오프라인으로 백업하고, IT 장애 시에도 OT를 독립 운전할 수 있게 의존성 축소</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="17" t="inlineStr">
@@ -34322,9 +35061,10 @@
           <t>제어 상실</t>
         </is>
       </c>
-      <c r="E126" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may seek to achieve a sustained loss of control or a runaway condition in which operators cannot issue any commands even if the malicious interference has subsided.</t>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치·HMI를 파괴하거나 주변 기기 사용을 막아, 간섭이 멈춘 뒤에도 운영자가 어떤 명령도 내릴 수 없는 지속적 제어 상실 상태를 만들 수 있음
+- 제어 상실은 공정 폭주나 설비 손상으로 직결될 수 있고, 복구가 장치 교체·재구성과 수동 운전에 의존해 길어짐</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -34360,7 +35100,16 @@
       <c r="N126" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="O126" s="17" t="inlineStr"/>
+      <c r="O126" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 제어 명령 실패·HMI 무응답·장치 통신 두절이 동시에 늘어나는지 감시
+- 원인 기법(와이퍼·펌웨어 변조·랜섬웨어) 탐지와 연계해 확산 범위 판단
+■ 대응
+- 중요 공정에 기계식 보호와 독립 안전계통을 두어 제어를 잃어도 안전 정지 보장
+- 예비 장치·백업 이미지와 수동 운전 절차를 준비하고 정기 훈련</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="17" t="inlineStr">
@@ -34383,9 +35132,10 @@
           <t>생산·매출 손실</t>
         </is>
       </c>
-      <c r="E127" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause loss of productivity and revenue through disruption and even damage to the availability and integrity of control system operations, devices, and related processes.</t>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 직접 공격이나 분리되지 않은 IT 환경에 대한 랜섬웨어 공격으로 생산·출하·운송을 멈추게 해, 조직에 큰 생산·매출 손실을 일으킬 수 있음
+- 공정이 멀쩡해도 감염 확산을 우려한 예방적 중단이나 생산 관리 시스템 마비로 생산이 멈추며, 피해가 협력업체와 공급망으로 번짐</t>
         </is>
       </c>
       <c r="F127" s="17" t="inlineStr">
@@ -34421,7 +35171,16 @@
       <c r="N127" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="O127" s="17" t="inlineStr"/>
+      <c r="O127" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 랜섬웨어 전조(자격증명 탈취·대량 권한 상승·백업 삭제)를 IT·OT 경계에서 조기 탐지
+- 생산 실적·가동률 급변을 운영 지표로 감시하고 보안 이벤트와 상관 분석
+■ 대응
+- IT·OT 분리(DMZ·단방향 게이트웨이)와 IT 장애 시 최소 생산을 유지하는 OT 독립 운전 계획 수립
+- MES·히스토리언 등 생산 지원 시스템의 오프라인 백업과 복구 우선순위를 사업 연속성 계획에 반영</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="17" t="inlineStr">
@@ -34444,9 +35203,10 @@
           <t>감시 상실</t>
         </is>
       </c>
-      <c r="E128" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause a sustained or permanent loss of view where the ICS equipment will require local, hands-on operator intervention; for instance, a restart or manual operation.</t>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 HMI·RTU·센서 통신을 파괴하거나 감시 기능이 없는 펌웨어로 바꿔, 운영자가 현장에 가지 않고는 공정 상태를 볼 수 없게 만들 수 있음
+- 물리 공정은 돌아가도 상태를 확인할 수 없어 안전을 위해 수동 운전·운영 중단을 택하게 되며, 지속적 감시 상실은 현장 조치 없이는 회복되지 않음</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -34477,12 +35237,21 @@
         </is>
       </c>
       <c r="M128" s="20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N128" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="O128" s="17" t="inlineStr"/>
+      <c r="O128" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 텔레메트리 공백이 여러 장치·사이트에서 동시에 생기는지 감시
+- HMI 화면·프로젝트 파일의 무결성과 통신 장비 상태를 정기 점검
+■ 대응
+- 독립 감시 경로(현장 표시기·대체 통신)와 감시 서비스 이중화 확보
+- 감시 상실 시 안전 상태 판단·현장 순회 절차를 마련하고 정기 훈련</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
@@ -34505,9 +35274,10 @@
           <t>제어 조작</t>
         </is>
       </c>
-      <c r="E129" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may manipulate physical process control within the industrial environment.</t>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 설정값·태그·파라미터를 바꾸거나 직접 명령을 보내 물리 공정을 의도대로 움직일 수 있음
+- 차단기 개방·밸브 개폐·원심분리기 속도 변화처럼 결과가 곧바로 물리 세계에 나타나며, 운영자 화면까지 속이면 조작 사실을 늦게 알아챔</t>
         </is>
       </c>
       <c r="F129" s="17" t="inlineStr">
@@ -34543,7 +35313,16 @@
       <c r="N129" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O129" s="17" t="inlineStr"/>
+      <c r="O129" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 운영자 조작 기록이 없는 상태 변화, 근무 외 시간 조작, 원격 접속 세션 중 설정 변경을 공정 이력과 접속 로그로 대조
+- 원인 기법(비인가 명령·파라미터 변조) 탐지와 연계
+■ 대응
+- 원격 접속을 다중 인증·세션 기록·승인 절차로 통제하고 퇴사자 계정을 즉시 회수
+- 중요 동작은 현장 인터록·한계값·독립 안전계통으로 보호하고, 통신 인증을 지원하는 프로토콜 적용</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="17" t="inlineStr">
@@ -34566,9 +35345,10 @@
           <t>감시 화면 조작</t>
         </is>
       </c>
-      <c r="E130" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to manipulate the information reported back to operators or controllers.</t>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영자·제어기에 보고되는 정보를 조작해, 실제 공정과 다른 상태를 화면에 보여 줄 수 있음
+- 조작된 화면을 믿은 운영자가 잘못 조치하거나 위험을 놓치게 되며, 보호 기능이 동작해야 할 상황도 가려짐</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -34604,7 +35384,16 @@
       <c r="N130" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O130" s="17" t="inlineStr"/>
+      <c r="O130" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 같은 변수를 독립 계측·현장 표시기와 주기적으로 대조
+- 값이 비정상적으로 일정하거나 반복 패턴을 보이는지 히스토리언으로 분석
+■ 대응
+- 보고 통신 무결성 보호(IEC 62351 등)와 독립 감시 경로 확보
+- 안전 판단은 독립 안전계통과 현장 계측에 두고, 운영자 교육에 '화면 불일치' 대응 시나리오 포함</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="inlineStr">
@@ -34627,9 +35416,10 @@
           <t>보호 기능 상실</t>
         </is>
       </c>
-      <c r="E131" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may compromise protective system functions designed to prevent the effects of faults and abnormal conditions.</t>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 고장·이상 상태의 영향을 막도록 설계된 보호 기능(보호 계전기 등)을 무력화해, 설비 손상과 장기 공정 중단, 인명 위험을 키울 수 있음
+- 많은 고장은 사람이 반응하기에 너무 빨리 진행되므로, 자동 보호가 꺼지면 다른 공격이나 일반 고장이 곧바로 큰 사고로 번짐</t>
         </is>
       </c>
       <c r="F131" s="17" t="inlineStr">
@@ -34665,7 +35455,16 @@
       <c r="N131" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O131" s="17" t="inlineStr"/>
+      <c r="O131" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 보호 장치 상태 보고 중단·자기진단 경보를 감시
+- 보호 장치를 향한 비정상 통신(취약점 공격 패턴, 업데이트 모드 전환)을 OT 네트워크 감시로 탐지
+■ 대응
+- 보호 계통 이중화, 장치 펌웨어 갱신, 보호 장치 관리 접근 제한
+- 보호 기능이 무력화되면 운전을 제한하고 현장 감시를 강화하는 절차 마련</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="17" t="inlineStr">
@@ -34688,9 +35487,10 @@
           <t>재산·설비 피해</t>
         </is>
       </c>
-      <c r="E132" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may cause damage and destruction of property to infrastructure, equipment, and the surrounding environment when attacking control systems.</t>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어 시스템을 조작해 설비·기반시설과 주변 환경에 물리적 손상과 파괴를 일으킬 수 있음
+- 피해가 장비 교체·환경 복구·인명 피해로 이어져 사이버 공격 가운데 복구 비용과 시간이 가장 크고, 원인이 단순 고장으로 오인되기도 함</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
@@ -34726,7 +35526,16 @@
       <c r="N132" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O132" s="17" t="inlineStr"/>
+      <c r="O132" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 설비 상태 감시(진동·온도·운전 한계)와 보안 이벤트를 함께 분석해 사이버 원인 가능성을 조기 판단
+- 물리 사고 조사 절차에 사이버 포렌식(제어기 로직·명령 이력 확인)을 포함
+■ 대응
+- 기계식 보호 계층과 독립 안전계통으로 위험 한계를 물리적으로 보장(사이버 조작으로 넘을 수 없게 설계)
+- 결과 중심 위험 평가로 물리 피해를 일으킬 수 있는 제어 경로를 찾아 우선 보호</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
@@ -34749,9 +35558,10 @@
           <t>안전 상실</t>
         </is>
       </c>
-      <c r="E133" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may compromise safety system functions designed to maintain safe operation of a process when unacceptable or dangerous conditions occur.</t>
+      <c r="E133" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 위험 상황에서 공정을 안전하게 정지시키는 안전계통(SIS) 기능을 무력화하거나 다시 프로그래밍해, 위험 상태가 계속되게 할 수 있음
+- 안전계통은 사람이 대응하기에 너무 빠른 위험을 막는 마지막 방어선이라, 제어계통 조작과 결합되면 폭발·유독물 누출 같은 인명 사고로 이어질 수 있음</t>
         </is>
       </c>
       <c r="F133" s="17" t="inlineStr">
@@ -34787,7 +35597,16 @@
       <c r="N133" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O133" s="17" t="inlineStr"/>
+      <c r="O133" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 안전 제어기의 운전 모드(키스위치)·로직 변경·진단 경보를 상시 감시
+- 안전 엔지니어링 단말 접속과 안전 프로토콜(예: TriStation) 통신을 OT 네트워크 감시로 경보
+■ 대응
+- 안전계통을 제어계통과 물리·논리적으로 분리하고 전용 엔지니어링 단말 사용
+- 안전 제어기 키스위치를 RUN에 두고 변경 시 현장 승인을 받게 하며, 기계식 보호 계층 유지</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="17" t="inlineStr">
@@ -34810,9 +35629,10 @@
           <t>운영 정보 탈취</t>
         </is>
       </c>
-      <c r="E134" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may steal operational information on a production environment as a direct mission outcome for personal gain or to inform future operations.</t>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 설계 도면·운전 절차·네트워크 구성·공정 정보 같은 운영 정보를 훔쳐, 직접적인 이득을 얻거나 이후 OT 공격 설계에 쓸 수 있음
+- 탈취 시점에는 물리 피해가 없어 대응 우선순위가 낮아지기 쉽지만, 정밀 공격의 사전 준비이자 기반시설 정보 유출이라 영향이 큼</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
@@ -34852,7 +35672,16 @@
       <c r="N134" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="O134" s="17" t="inlineStr"/>
+      <c r="O134" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 표준 탐지 방법이 없는 결과 기법 — 설계·프로젝트 파일 저장소의 대량 접근·압축·외부 전송을 DLP·네트워크 감시로 탐지
+- OT 영역에서 인터넷·클라우드 저장소로 향하는 비정상 전송을 경보
+■ 대응
+- 운영 정보를 기밀 등급으로 분류해 접근 통제·암호화하고, 공급업체에 보관·폐기 보안 요구사항 부과
+- OT 문서 저장소를 업무망과 분리하고 반출 승인 절차 운영</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
@@ -34875,9 +35704,10 @@
           <t>데이터 암호화(랜섬웨어)</t>
         </is>
       </c>
-      <c r="E135" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may encrypt data on target systems or on large numbers of systems in a network to interrupt availability to system and network resources.</t>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 랜섬웨어로 HMI·EWS·히스토리언·생산 관리 서버의 파일과 디스크를 암호화해, 운영 시스템을 쓸 수 없게 만들고 복구 대가를 요구할 수 있음
+- OT 자산까지 암호화되지 않아도 IT 감염과 OT 확산 우려만으로 운영을 멈추게 되며, 실제 OT 영향 사고에서 가장 자주 확인되는 경로임</t>
         </is>
       </c>
       <c r="F135" s="17" t="inlineStr">
@@ -34916,12 +35746,21 @@
         </is>
       </c>
       <c r="M135" s="20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N135" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O135" s="17" t="inlineStr"/>
+      <c r="O135" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 변경·확장자 변경, 섀도 복사본 삭제, ICS 서비스 일괄 종료를 엔드포인트 감시로 경보
+- IT·OT 경계에서 도메인 관리자 계정의 OT 자산 접근과 그룹 정책 변경을 탐지
+■ 대응
+- IT·OT 계정·도메인 분리, OT 단말 애플리케이션 허용 목록, 오프라인·변경 불가 백업과 복원 훈련
+- IT 장애 시 OT 독립 운전 계획을 세워 예방적 중단 범위를 최소화</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="17" t="inlineStr">
@@ -34944,9 +35783,10 @@
           <t>대역폭 탈취(봇넷 편입)</t>
         </is>
       </c>
-      <c r="E136" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage the network bandwidth resources of co-opted systems to complete resource-intensive tasks, which may impact system and/or hosted service availability.</t>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 기본 자격증명·알려진 취약점으로 장악한 IoT 기기와 경계 장비를 봇넷에 편입해, 그 대역폭으로 다른 대상에 DDoS를 하거나 공격 트래픽을 중계할 수 있음
+- 기기 소유자는 성능 저하와 평판 손상만 겪어 침해를 알아채지 못하는 경우가 많고, 같은 접근이 이후 OT 공격 거점으로 쓰일 수 있음</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
@@ -34990,7 +35830,16 @@
       <c r="N136" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="O136" s="17" t="inlineStr"/>
+      <c r="O136" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- IoT·경계 장비의 비정상 아웃바운드 트래픽(대량 연결·DDoS 패턴)과 알려진 C2로의 통신을 네트워크 감시로 경보
+- 장치 프로세스·설정 변경과 텔넷·SSH 로그인 시도 수집
+■ 대응
+- 기본 자격증명 변경, 펌웨어 갱신, 인터넷에 노출된 관리 인터페이스 제거
+- IoT 기기는 별도 망으로 분리하고 외부 통신을 허용 목록으로 제한</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:O136"/>
@@ -35211,7 +36060,7 @@
         <is>
           <t>OTC-IA-11 인터넷 노출 장치 악용 (높음)
 OTC-IA-12 원격 서비스 악용 (높음)
-OTC-IA-10 원격 서비스 취약점 악용 (높음)</t>
+OTC-IA-03 외부 원격 서비스 악용 (높음)</t>
         </is>
       </c>
     </row>
@@ -35319,7 +36168,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="17" t="inlineStr">
         <is>
@@ -35376,7 +36225,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O6" s="17" t="inlineStr">
         <is>
@@ -35433,13 +36282,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O7" s="17" t="inlineStr">
         <is>
           <t>OTC-EV-07.1 비인가 명령 메시지 (매우 높음)
 OTC-EV-02 위장 (높음)
-OTC-EV-09 보안 도구 무력화 (높음)</t>
+OTC-EV-06 시스템 바이너리 대리 실행 (높음)</t>
         </is>
       </c>
     </row>
@@ -35490,13 +36339,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O8" s="17" t="inlineStr">
         <is>
           <t>OTC-DS-01 네트워크 연결 열거 (보통)
 OTC-DS-03.0 원격 시스템 탐색 (일반·상위기법) (보통)
-OTC-DS-03.1 포트 스캔 (보통)</t>
+OTC-DS-05 원격 시스템 정보 탐색 (보통)</t>
         </is>
       </c>
     </row>
@@ -35547,7 +36396,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O9" s="17" t="inlineStr">
         <is>
@@ -35610,7 +36459,7 @@
         <is>
           <t>OTC-CO-04 중간자 공격 (높음)
 OTC-CO-01 공정 상태 감시 (보통)
-OTC-CO-06 화면 캡처 (보통)</t>
+OTC-CO-11 로컬 시스템 데이터 수집 (보통)</t>
         </is>
       </c>
     </row>
@@ -35718,13 +36567,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O12" s="17" t="inlineStr">
         <is>
           <t>OTC-IR-02 데이터 파괴 (매우 높음)
 OTC-IR-03 서비스 거부 (매우 높음)
-OTC-IR-09 서비스 중지 (매우 높음)</t>
+OTC-IR-04 장치 재시작·정지 (매우 높음)</t>
         </is>
       </c>
     </row>
@@ -37552,8 +38401,7 @@
       </c>
       <c r="L3" s="17" t="inlineStr">
         <is>
-          <t>T0809 데이터 파괴 (ATT&amp;CK 공식)
-T0813 제어 거부 (ATT&amp;CK 공식)
+          <t>T0813 제어 거부 (ATT&amp;CK 공식)
 T0814 서비스 거부 (ATT&amp;CK 공식)
 T0816 장치 재시작·정지 (ATT&amp;CK 공식)
 T0822 외부 원격 서비스 악용 (ATT&amp;CK 공식)
@@ -37561,15 +38409,9 @@
 T0826 가용성 상실 (ATT&amp;CK 공식)
 T0827 제어 상실 (ATT&amp;CK 공식)
 T0828 생산·매출 손실 (ATT&amp;CK 공식)
-T0829 감시 상실 (ATT&amp;CK 공식)
 T0831 제어 조작 (ATT&amp;CK 공식)
-T0834 네이티브 API 악용 (ATT&amp;CK 공식)
-T0840 네트워크 연결 열거 (ATT&amp;CK 공식)
 T0842 네트워크 스니핑 (ATT&amp;CK 공식)
 T0846 원격 시스템 탐색 (ATT&amp;CK 공식)
-T0846.001 포트 스캔 (ATT&amp;CK 공식)
-T0849 위장 (ATT&amp;CK 공식)
-T0852 화면 캡처 (ATT&amp;CK 공식)
 T0853 스크립트 실행 (ATT&amp;CK 공식)
 T0859 유효 계정 악용 (ATT&amp;CK 공식)
 T0863 사용자 실행 유도 (ATT&amp;CK 공식)
@@ -37578,15 +38420,11 @@
 T0869 표준 응용 계층 프로토콜 (ATT&amp;CK 공식)
 T0872 호스트 흔적 삭제 (ATT&amp;CK 공식)
 T0874 후킹 (ATT&amp;CK 공식)
-T0881 서비스 중지 (ATT&amp;CK 공식)
 T0884 연결 프록시 (ATT&amp;CK 공식)
 T0885 일반 포트 사용 (ATT&amp;CK 공식)
 T0886 원격 서비스 악용 (ATT&amp;CK 공식)
 T0894 시스템 바이너리 대리 실행 (ATT&amp;CK 공식)
-T1003 OS·저장 자격증명 탈취 (ATT&amp;CK 공식)
 T1056 입력 캡처 (ATT&amp;CK 공식)
-T1486 데이터 암호화(랜섬웨어) (ATT&amp;CK 공식)
-T1543 시스템 서비스 생성·변조 (ATT&amp;CK 공식)
 T1685 보안 도구 무력화 (ATT&amp;CK 공식)
 T1691.001 명령 메시지 차단 (ATT&amp;CK 공식)
 T1691.002 보고 메시지 차단 (ATT&amp;CK 공식)
@@ -38668,16 +39506,9 @@
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>T0809 데이터 파괴 (ATT&amp;CK 공식)
-T0826 가용성 상실 (ATT&amp;CK 공식)
+          <t>T0826 가용성 상실 (ATT&amp;CK 공식)
 T0828 생산·매출 손실 (ATT&amp;CK 공식)
-T0846.001 포트 스캔 (ATT&amp;CK 공식)
-T0847 이동식 매체 전파 (ATT&amp;CK 공식)
-T0866 원격 서비스 취약점 악용 (ATT&amp;CK 공식)
-T0867 내부 도구 전송 (ATT&amp;CK 공식)
-T0886 원격 서비스 악용 (ATT&amp;CK 공식)
-T1543 시스템 서비스 생성·변조 (ATT&amp;CK 공식)
-T1685 보안 도구 무력화 (ATT&amp;CK 공식)</t>
+T0847 이동식 매체 전파 (ATT&amp;CK 공식)</t>
         </is>
       </c>
       <c r="M15" s="17" t="inlineStr">

--- a/ot/output/통합_OT보안위협_매트릭스_v2.xlsx
+++ b/ot/output/통합_OT보안위협_매트릭스_v2.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>고유 기법 48/111개 작성 — 나머지는 ATT&amp;CK 원문 첫 문장(회색, '작성 예정')</t>
+          <t>고유 기법 76/111개 작성 — 나머지는 ATT&amp;CK 원문 첫 문장(회색, '작성 예정')</t>
         </is>
       </c>
     </row>
@@ -5820,12 +5820,24 @@
           <t>명령줄 인터페이스</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may utilize command-line interfaces (CLIs) to interact with systems and execute commands.</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr"/>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 EWS·HMI·SCADA 서버의 명령 셸과 RTU·방화벽의 장비 CLI로 명령을 실행해, 도구를 설치하고 설정을 바꾸거나 제어 소프트웨어를 직접 호출할 수 있음
+- 운영·유지보수에 늘 쓰는 인터페이스라 실행 자체가 정상 행위와 같고, 내장 명령만 쓰면 별도 악성 파일 없이도 공격이 진행됨</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언, Linux 기반 RTU·데이터 게이트웨이, OT 경계 방화벽·스위치의 관리 CLI (L1~L3.5)
+- 수법: SCADA 명령 도구 호출(MicroSCADA scilc.exe), MS-SQL xp_cmdshell, 공격 도구에 대상 IP·페이로드를 명령줄 인자로 전달(Triton·Industroyer), RTU에 SSH로 접속해 파일 삭제, 방화벽 CLI로 설정 변경
+- 통합: Enterprise Windows 명령 셸(T1059.003)·Unix 셸(T1059.004)·네트워크 장비 CLI(T1059.008) — PowerShell·VBS 같은 스크립트는 스크립트 실행(OTC-EX-05)
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): MicroSCADA의 scilc.exe로 SCIL-API 명령을 실행해 변전소 차단기를 개방 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2025 폴란드(2025-12): HMI에서 PowerShell로 관리 공유·방화벽 규칙을 바꾸고, Mikronika RTU에 root로 SSH 접속해 파일을 모두 지워 장치를 고장 냄 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] Triton(2017-08): 대상 Triconex 장치의 IP 주소 하나를 명령줄 인자로 받아 공격 도구를 실행 (INC-004, ATT&amp;CK C0030)</t>
+        </is>
+      </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
           <t>T0807</t>
@@ -5848,7 +5860,7 @@
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L22" s="17" t="inlineStr">
@@ -5963,7 +5975,16 @@
           <t>https://attack.mitre.org/techniques/T0807</t>
         </is>
       </c>
-      <c r="AM22" s="17" t="inlineStr"/>
+      <c r="AM22" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 호스트에서 명령 셸·PowerShell 실행과 인자를 기록(명령줄 감사)하고, 제어 소프트웨어 명령 도구(scilc.exe 등)를 평소와 다른 부모 프로세스·계정이 호출하면 경보
+- RTU·네트워크 장비의 SSH 접속과 CLI 명령 이력(AAA 기록)을 중앙 수집해 승인되지 않은 명령·설정 변경 확인
+■ 대응
+- OT 호스트에서 쓰지 않는 셸·관리 도구를 제거하거나 애플리케이션 허용 목록으로 막고, 관리자 셸은 점프 호스트·지정 계정에서만 사용
+- 장치·장비 관리 인터페이스는 관리망에서만 열고 root 직접 로그인을 막으며, 명령 권한을 역할별로 나눔</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
@@ -5986,12 +6007,24 @@
           <t>제어기 태스크 변조</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify the tasking of a controller to allow for the execution of their own programs.</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 태스크 설정(태스크와 프로그램 조직 단위의 연결·주기·우선순위)을 바꾸거나 새 태스크를 넣어, 자신이 심은 코드를 매 스캔 주기나 특정 조건에서 실행시킬 수 있음
+- 기존 로직은 그대로 두고 실행 흐름만 바꿀 수 있어 로직 비교만으로는 놓치기 쉽고, 태스크 변경을 경보하지 않는 장치가 많음</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: IEC 61131-3 기반 PLC·PAC·DCS 제어기와 안전 제어기(SIS)의 태스크·조직 블록(OB)·프로그램 테이블 (L1)
+- 수법: 주기 실행 블록 감염(Stuxnet의 OB1·OB35), 제어기가 자동 인식하는 새 조직 블록 추가(PLC-Blaster의 OB9999), 안전 제어기 프로그램 테이블에 공격 코드 등록(Triton)
+- 전제: 운전 모드 변경(OTC-EX-06)과 프로그램 추가 다운로드(OTC-LM-01.3)로 쓰기 권한을 얻어야 하며, 결과는 제어 프로그램 변조(OTC-PE-03)·운전 파라미터 변조(OTC-IP-02)로 이어짐
+■ 실제 사례
+- [실제 사고] Stuxnet(2010-06): 주기 실행 블록 OB1과 감시용 OB35를 감염시켜 매 스캔 주기 시작에 악성 코드가 먼저 실행되게 함 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] Triton(2017-08): Tricon 안전 제어기의 프로그램 테이블에 인자 설정 코드와 셸코드를 추가해 펌웨어가 매 주기 실행하게 함 (INC-004, ATT&amp;CK S1009)
+- [실증] PLC-Blaster(2016-03): 기존 코드를 건드리지 않고 OB9999에 웜 코드를 넣어 PLC가 자동으로 실행하게 함 (INC-024, ATT&amp;CK S1006)</t>
+        </is>
+      </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
           <t>T0821</t>
@@ -6010,7 +6043,7 @@
       <c r="J23" s="17" t="inlineStr"/>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L23" s="17" t="inlineStr">
@@ -6119,7 +6152,16 @@
           <t>https://attack.mitre.org/techniques/T0821</t>
         </is>
       </c>
-      <c r="AM23" s="17" t="inlineStr"/>
+      <c r="AM23" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기의 태스크 구성(태스크 목록·주기·우선순위·연결 블록)과 블록 목록을 승인된 기준 프로젝트와 정기 비교하고, 진단 버퍼·변경 경보를 수집
+- 다운로드·온라인 편집 같은 엔지니어링 기능 코드가 지정 EWS 밖에서 오거나 작업 일정 밖에 발생하면 OT 네트워크 감시로 경보
+■ 대응
+- 제어기 접근 보호(암호·보호 레벨)를 켜고 운전 중에는 키 스위치를 RUN에 두어 원격 프로그램 변경을 막음
+- 변경 관리로 승인된 변경만 반영하고, 코드 서명·무결성 검증을 지원하는 제어기를 우선 도입</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -6142,12 +6184,23 @@
           <t>그래픽 사용자 인터페이스 조작</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to gain access to a machine via a Graphical User Interface (GUI) to enhance execution capabilities.</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 원격 데스크톱·VNC·원격 지원 도구로 HMI·EWS 화면을 넘겨받아, 운영자와 같은 방식으로 클릭해 차단기 개방·설정 변경 같은 제어 기능을 실행할 수 있음
+- 운영자 화면에서 이뤄지는 정상 조작이라 명령 자체로는 구분되지 않고, HMI가 공정 배치를 보여주므로 깊은 공정 지식 없이도 의미 있는 조작이 가능함</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: SCADA·DCS 운영자 HMI, EWS, 원격 접속 도구가 깔린 운전 단말과 OT 도메인 컨트롤러 (L2~L3)
+- 경로: 탈취 계정으로 RDP·VNC 접속(OTC-IA-12), 원격 지원 도구(TeamViewer 등), 인터넷에 직접 노출된 HMI 웹·VNC 화면(OTC-IA-11)
+- 올즈마 정수장 설정값 변경(2021-02)은 원격 지원 화면 조작 사례로 널리 알려졌으나, 이후 직원 실수 가능성이 제기돼 실제 사고 집계에서 제외(INC-041)
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): SCADA 환경의 HMI 화면을 원격으로 조작해 배전 변전소 차단기를 개방 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 2025 폴란드(2025-12): RDP로 Mikronika HMI에 접속해 GUI로 명령을 실행하고, 도메인 컨트롤러에도 GUI로 접속해 데이터를 빼내고 파괴를 시도 (INC-008, ATT&amp;CK C0063)</t>
+        </is>
+      </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
           <t>T0823</t>
@@ -6166,7 +6219,7 @@
       <c r="J24" s="17" t="inlineStr"/>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L24" s="17" t="inlineStr">
@@ -6281,7 +6334,16 @@
           <t>https://attack.mitre.org/techniques/T0823</t>
         </is>
       </c>
-      <c r="AM24" s="17" t="inlineStr"/>
+      <c r="AM24" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- HMI·EWS로 들어오는 원격 화면 세션(RDP·VNC·원격 지원 도구)의 생성·출발지·시간대를 기록하고, 운영자 콘솔이 아닌 세션에서 일어난 제어 조작을 경보
+- HMI 운영자 조작 기록을 로그인 세션과 대조해 근무하지 않는 계정이나 원격 세션의 조작 확인
+■ 대응
+- HMI·EWS 원격 화면 접속은 점프 호스트·다중 인증을 거친 지정 경로로만 허용하고, 쓰지 않는 원격 지원 도구 제거
+- 중요 제어 조작은 확인 창 외에 2인 승인·현장 확인을 거치게 하고, 원격 세션은 녹화·감독</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
@@ -6304,12 +6366,24 @@
           <t>네이티브 API 악용</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may directly interact with the native OS application programming interface (API) to access system functions.</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr"/>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영체제나 제어기 펌웨어가 제공하는 저수준 API(시스템 호출·시스템 함수 블록)를 직접 불러, 메모리·프로세스·통신 같은 하위 기능을 정상 도구 없이 다룰 수 있음
+- 제어기의 시스템 함수 블록은 정상 로직에도 쓰여 악용 호출이 구분되지 않고, 장치 내부의 API 호출을 기록·감시할 수단이 거의 없음</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: PLC·안전 제어기의 시스템 함수(SFC·SFB)와 펌웨어 시스템 호출, Windows·Linux 기반 HMI·EWS·SCADA 서버의 네이티브 API (L1~L3)
+- 제어기 쪽 수법: 시스템 함수 블록으로 시계 읽기·데이터 블록 생성(Stuxnet), TCON·TSEND로 PLC에서 임의 TCP 연결 생성(PLC-Blaster), 펌웨어 시스템 호출로 메모리·레지스터 읽기·쓰기(Triton)
+- 호스트 쪽: Windows API로 디스크 핸들 확보·프로세스 주입(KillDisk·Bad Rabbit 등) — 통합: Enterprise 네이티브 API(T1106)
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 펌웨어 시스템 호출을 쓰는 imain.bin으로 안전 제어기 메모리·레지스터를 읽고 쓰고 실행 (INC-004, ATT&amp;CK S1009)
+- [실제 사고] Stuxnet(2010-06): PLC 시스템 함수 블록으로 시계를 읽고 데이터 블록을 실행 중에 생성 (INC-009, ATT&amp;CK S0603)
+- [실증] PLC-Blaster(2016-03): 시스템 함수 블록 TCON·TSEND·TRCV로 다른 PLC에 연결해 웜을 퍼뜨림 (INC-024, ATT&amp;CK S1006)</t>
+        </is>
+      </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
           <t>T0834</t>
@@ -6332,7 +6406,7 @@
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L25" s="17" t="inlineStr">
@@ -6463,7 +6537,16 @@
           <t>https://attack.mitre.org/techniques/T0834</t>
         </is>
       </c>
-      <c r="AM25" s="17" t="inlineStr"/>
+      <c r="AM25" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기 프로그램의 통신·메모리 관련 시스템 함수 사용을 기준 프로젝트와 비교하고, PLC가 평소 없던 TCP 연결을 만들면 OT 네트워크 감시로 경보
+- HMI·EWS에서는 EDR로 프로세스 주입·디스크 직접 접근 같은 의심 API 호출 패턴 탐지(OT 벤더 호환성 확인 후 적용)
+■ 대응
+- 제어기 접근 보호로 프로그램 변경을 막고 쓰지 않는 통신 기능(PUT/GET·개방형 통신)을 끔
+- 호스트에는 애플리케이션 허용 목록을 적용해 비인가 실행 파일이 API를 호출할 기회를 줄임</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -6486,12 +6569,24 @@
           <t>스크립트 실행</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may use scripting languages to execute arbitrary code in the form of a pre-written script or in the form of user-supplied code to an interpreter.</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr"/>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 PowerShell·VBScript·배치 파일·Python 같은 스크립트로 공격 도구를 실행하고 작업을 자동화해, 정상 관리 작업처럼 보이게 할 수 있음
+- OT 호스트에도 운영 자동화용 스크립트 환경이 기본으로 깔려 있고, 메모리에서만 실행하거나 난독화하면 파일 기반 검사로 잡기 어려움</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언, 도메인 정책을 받는 OT 호스트, Python 등 스크립트 엔진이 설치된 엔지니어링 단말 (L2~L3)
+- 수법: VBS → 배치 파일 → SCADA 명령 도구로 이어지는 실행(2022 MicroSCADA), PowerShell 도구로 그룹 정책 경유 와이퍼 배포(TANKTRAP), 메모리 내 자격증명 수집, 문서 매크로로 최초 감염, Python으로 재구성한 산업 프로토콜 프레임워크(Triton)
+- 통합: Enterprise PowerShell(T1059.001)·Visual Basic(T1059.005) — 명령 셸 직접 실행은 OTC-EX-01, 그룹 정책 경유 배포는 OTC-PV-04.1
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): lun.vbs가 n.bat을 실행하고 n.bat이 MicroSCADA scilc.exe로 차단기 명령을 보냄 — PowerShell 도구 TANKTRAP으로 와이퍼도 배포 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2016 우크라이나(2016-12): VBS·배치 스크립트로 파일을 옮기고 PowerShell로 자격증명 수집 도구를 메모리에서 실행 (INC-003, ATT&amp;CK C0025)
+- [실제 사고] Triton(2017-08): PowerShell 기반 공개 도구 WMImplant를 쓰고, Python으로 짠 TriStation 통신 프레임워크로 안전 제어기를 조작 (INC-004, ATT&amp;CK C0030)</t>
+        </is>
+      </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
           <t>T0853</t>
@@ -6514,7 +6609,7 @@
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L26" s="17" t="inlineStr">
@@ -6630,7 +6725,16 @@
           <t>https://attack.mitre.org/techniques/T0853</t>
         </is>
       </c>
-      <c r="AM26" s="17" t="inlineStr"/>
+      <c r="AM26" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 호스트에도 PowerShell 스크립트 블록 로깅과 명령줄 감사를 켜고, wscript·cscript·powershell이 제어 소프트웨어 명령 도구를 부르는 프로세스 체인을 경보
+- 그룹 정책·예약 작업으로 새로 배포된 스크립트 파일과 WMI·PsExec를 통한 원격 스크립트 실행 감시
+■ 대응
+- OT 호스트에서 쓰지 않는 스크립트 엔진을 막고, PowerShell 제한 언어 모드와 서명된 스크립트만 실행하도록 설정
+- 문서 매크로를 기본 차단하고, 운영 자동화 스크립트는 승인된 저장소에서만 배포</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -6653,12 +6757,24 @@
           <t>운전 모드 변경</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may change the operating mode of a controller to gain additional access to engineering functions such as Program Download.</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr"/>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 운전 모드를 RUN에서 PROGRAM·STOP·REMOTE로 바꿔, 프로그램 다운로드·메모리 쓰기 같은 엔지니어링 기능을 열거나 제어 로직 실행을 멈출 수 있음
+- 키 스위치를 원격 변경이 가능한 위치에 둔 채 운영하는 경우가 흔해 프로토콜 명령만으로 모드가 바뀌고, 모드 변경을 기록·경보하지 않는 장치도 많음</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: PLC·PAC·DCS 제어기와 안전 제어기(SIS)의 운전 모드(RUN·PROGRAM·STOP·REMOTE)와 물리 키 스위치 (L1)
+- 수법: 공격 도구에 내장된 정지·실행 명령(Triton의 TriStation halt·run, PLC-Blaster의 프로그램 정지 후 재기동), 장치 웹 인터페이스로 모드 변경(INCONTROLLER의 Omron PLC 대상 HTTP 연결)
+- 모드 변경 뒤에는 제어 프로그램 다운로드(OTC-LM-01.0)·제어기 태스크 변조(OTC-EX-02)·시스템 펌웨어 변조(OTC-PE-04.1)가 이어지고, STOP 상태로 두면 장치 정지(OTC-IR-04)와 같은 결과가 남 — 현재 모드는 운전 모드 탐지(OTC-CO-08)로 먼저 확인
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 키 스위치가 PROGRAM 위치에 있던 Tricon 안전 제어기의 프로그램을 TriStation 프로토콜로 멈추고 다시 실행하며 공격 코드를 심음 (INC-004, ATT&amp;CK S1009)
+- [위협인텔] PIPEDREAM(2022-04): INCONTROLLER가 HTTP로 Omron PLC의 운전 모드를 바꾸는 기능을 갖춘 채 배포 전에 발견 (INC-022, ATT&amp;CK S1045)
+- [실증] PLC-Blaster(2016-03): 대상 PLC의 사용자 프로그램을 멈추고 웜 코드를 복사한 뒤 다시 기동 (INC-024, ATT&amp;CK S1006)</t>
+        </is>
+      </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
           <t>T0858</t>
@@ -6677,7 +6793,7 @@
       <c r="J27" s="17" t="inlineStr"/>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L27" s="17" t="inlineStr">
@@ -6790,7 +6906,16 @@
           <t>https://attack.mitre.org/techniques/T0858</t>
         </is>
       </c>
-      <c r="AM27" s="17" t="inlineStr"/>
+      <c r="AM27" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 운전 모드를 바꾸는 기능 코드(정지·실행·모드 전환)를 OT 네트워크 감시로 탐지하고, 장치 이벤트 로그·진단 버퍼의 모드 변경 기록 수집
+- 키 스위치 위치를 감시 신호로 HMI·SCADA에 올려, PROGRAM·REMOTE 상태가 작업 일정 밖에 나타나거나 오래 유지되면 경보
+■ 대응
+- 정상 운전 중에는 키 스위치를 RUN(잠금)에 두고 키를 관리하며, 모드 변경은 변경 관리 절차로 승인
+- 엔지니어링 프로토콜 접근을 지정 EWS로 제한하고 제어기 접근 암호·인증 기능을 켬</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -6813,12 +6938,25 @@
           <t>사용자 실행 유도</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may rely on a targeted organizations user interaction for the execution of malicious code.</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr"/>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영자·엔지니어가 첨부파일·설치 파일·프로젝트 파일을 직접 열거나 실행하게 만들어, 사용자 권한으로 OT 단말에서 악성 코드를 실행시킬 수 있음
+- 엔지니어링 업무는 벤더 설치 파일·프로젝트 파일을 일상적으로 주고받아 위장이 쉽고, 파일을 여는 행위 자체가 정상 업무라 차단 기준을 세우기 어려움</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: EWS·HMI 운영 단말, 점프 호스트, OT 접근 권한이 있는 업무 단말과 엔지니어링 소프트웨어(프로젝트·설정 파일 편집기) (L2~L3)
+- 수법: 문서 매크로(2015 우크라이나), 트로이 목마화된 설치 파일(Havex), 감염된 엔지니어링 프로젝트 파일(Stuxnet) — 공격자가 장악한 PLC에서 올려받은 프로젝트가 EWS를 감염시키는 역방향 경로도 시연됨(Evil PLC, INC-081)
+- CISA ICS 권고에서 프로젝트·설정 파일 파싱 취약점(로컬 경로의 메모리 손상·역직렬화) 1,491건, 2025년 이후 400건 — 조작된 파일을 여는 것만으로 코드가 실행됨
+- 통합: Enterprise 악성 파일 실행(T1204.002) — 이메일 전달은 스피어피싱 첨부파일(OTC-IA-09), 프로젝트 파일 감염은 OTC-PE-02.1
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): 직원이 첨부 문서의 매크로를 허용하자 BlackEnergy가 설치됨 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] Dragonfly(2014-06): 이메일에 첨부된 트로이 목마 설치 파일을 사용자가 실행해 Havex(Backdoor.Oldrea)에 감염 (INC-013, ATT&amp;CK S0093)
+- [공개 취약점] Delta DOPSoft(CVE-2021-38406): HMI 편집 소프트웨어가 조작된 프로젝트 파일을 열 때 범위 밖 쓰기로 코드가 실행됨 — KEV 등재</t>
+        </is>
+      </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
           <t>T0863</t>
@@ -6841,7 +6979,7 @@
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L28" s="17" t="inlineStr">
@@ -6951,7 +7089,16 @@
           <t>https://attack.mitre.org/techniques/T0863</t>
         </is>
       </c>
-      <c r="AM28" s="17" t="inlineStr"/>
+      <c r="AM28" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Office·PDF 뷰어·압축 프로그램·엔지니어링 소프트웨어가 스크립트 엔진·명령 셸 같은 자식 프로세스를 만들면 EDR로 경보
+- 외부에서 들어온 설치 파일·프로젝트 파일의 출처·해시를 기록하고 벤더 공식 배포본과 대조
+■ 대응
+- OT 단말에서 매크로와 외부 실행 파일을 기본 차단하고, 벤더 소프트웨어는 서명·해시를 확인한 승인 저장소에서만 설치
+- 엔지니어링 소프트웨어를 최신으로 유지하고(KEV·CISA 권고 우선), 출처가 불분명한 프로젝트 파일은 격리 환경에서 먼저 열기</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
@@ -6974,12 +7121,22 @@
           <t>API 경유 실행</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to leverage Application Program Interfaces (APIs) used for communication between control software and the hardware.</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr"/>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어 소프트웨어가 장치와 통신할 때 쓰는 API(엔지니어링 프로토콜 함수·벤더 라이브러리)를 호출해, 프로그램 다운로드·메모리 쓰기·장치 설정 같은 기능을 엔지니어링 도구 없이 실행할 수 있음
+- 장치 입장에서는 정상 엔지니어링 요청과 같고, 역분석한 프로토콜이나 공개된 벤더 라이브러리만 있으면 재현할 수 있음</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 엔지니어링 프로토콜(TriStation·S7comm·CIP 등)과 벤더 API를 받아들이는 PLC·안전 제어기·RTU·HMI·데이터 게이트웨이 (L1~L2)
+- 수법: 역분석으로 재구성한 프로토콜 라이브러리로 프로그램 다운로드·할당·변경 함수를 호출(Triton) — 공개된 벤더 SDK·엔지니어링 라이브러리를 불러 같은 기능을 쓰는 방식도 가능
+- 구분: 비인가 명령 메시지(OTC-IP-03.1)가 운전 명령(쓰기·동작)을 보낸다면, 이 기법은 장치 관리·프로그래밍 기능을 부르는 데 초점 — OS·펌웨어 수준 호출은 네이티브 API 악용(OTC-EX-04)
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 재구성한 TriStation 프로토콜 프레임워크로 안전 제어기의 프로그램 다운로드·할당·변경 API를 호출 (INC-004, ATT&amp;CK S1009)</t>
+        </is>
+      </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
           <t>T0871</t>
@@ -6998,7 +7155,7 @@
       <c r="J29" s="17" t="inlineStr"/>
       <c r="K29" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L29" s="17" t="inlineStr">
@@ -7126,7 +7283,16 @@
           <t>https://attack.mitre.org/techniques/T0871</t>
         </is>
       </c>
-      <c r="AM29" s="17" t="inlineStr"/>
+      <c r="AM29" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 엔지니어링 프로토콜의 프로그램 다운로드·메모리 쓰기 함수 호출을 OT 네트워크 감시로 탐지하고, 지정 EWS 밖 발신지나 작업 일정 밖 호출을 경보
+- 장치 감사 로그(지원 시)를 엔지니어링 소프트웨어 작업 기록과 대조해 도구 밖에서 이뤄진 호출 확인
+■ 대응
+- 엔지니어링 기능에 인증과 역할별 권한을 적용하고 지정 EWS에서만 허용
+- 키 스위치·접근 보호로 운전 중 프로그래밍 API 사용을 막음</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -7149,12 +7315,24 @@
           <t>후킹</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may hook into application programming interface (API) functions used by processes to redirect calls for execution and privilege escalation means.</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr"/>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 API 함수 주소·명령 처리기를 가로채거나 정상 프로세스에 코드를 주입해, 정상 기능이 호출될 때 자신의 코드가 먼저 실행되게 할 수 있음
+- 신뢰된 프로세스·펌웨어 안에서 실행돼 실행 주체가 정상으로 보이고, 반환값까지 바꿀 수 있어 감염 사실을 숨기는 데도 쓰임</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 엔지니어링 소프트웨어·HMI가 쓰는 Windows DLL, 신뢰된 시스템 프로세스(svchost·explorer), 안전 제어기 펌웨어의 명령 처리기 (L1~L3)
+- 수법: 프로젝트 파일을 여는 API의 가져오기 주소 테이블(IAT) 후킹(Stuxnet), 안전 제어기 진단 명령 처리기의 함수 포인터 변경(Triton), 정상 프로세스 DLL 주입·프로세스 할로잉(BlackEnergy·Duqu·Havex)
+- 엔지니어링 소프트웨어의 PLC 통신 DLL을 가짜로 바꿔 블록 읽기·쓰기를 가로채는 수법은 루트킷(OTC-EV-03)으로 분류 — 통합: Enterprise 프로세스 주입(T1055)·DLL 주입(T1055.001)·프로세스 할로잉(T1055.012)
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 'get main processor diagnostic data' 명령 처리기의 함수 포인터를 imain.bin 주소로 바꿔 정상 처리 전에 공격 코드가 실행되게 함 (INC-004, ATT&amp;CK S1009)
+- [실제 사고] Stuxnet(2010-06): 프로젝트 파일을 여는 API를 IAT 후킹으로 가로채고 신뢰된 프로세스에 DLL 전체를 주입 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] 2015 우크라이나(2015-12): BlackEnergy를 svchost.exe에 올린 뒤 C2 통신용 브라우저 프로세스를 띄움 (INC-002, ATT&amp;CK C0028)</t>
+        </is>
+      </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
           <t>T0874</t>
@@ -7177,7 +7355,7 @@
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L30" s="17" t="inlineStr">
@@ -7308,7 +7486,16 @@
           <t>https://attack.mitre.org/techniques/T0874</t>
         </is>
       </c>
-      <c r="AM30" s="17" t="inlineStr"/>
+      <c r="AM30" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- EDR로 원격 스레드 생성·타 프로세스 메모리 쓰기 같은 주입 패턴과 엔지니어링 소프트웨어에 로드된 미서명 DLL 탐지(OT 벤더 호환성 확인 후 적용)
+- PLC·안전 제어기는 벤더 진단 도구로 펌웨어·메모리 무결성을 점검하고, 평소 쓰지 않는 진단 명령 사용을 OT 네트워크 감시로 확인
+■ 대응
+- 엔지니어링 소프트웨어·HMI 설치 경로의 쓰기 권한을 제한하고 DLL 서명 검증·애플리케이션 허용 목록 적용
+- 제어기 펌웨어 무결성 검증 기능을 켜고, 안전 제어기의 원격 프로그래밍은 운전 중 차단</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
@@ -7331,12 +7518,22 @@
           <t>자동 실행 이미지</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage AutoRun functionality or scripts to execute malicious code.</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr"/>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 이동식 매체나 디스크 이미지(ISO)의 자동 실행 기능을 이용해, 매체를 연결·마운트하는 순간 악성 코드를 실행시킬 수 있음
+- 레거시 운영체제를 오래 쓰는 OT 호스트에는 자동 실행이 켜진 채 남은 경우가 있고, 가상화 환경에서는 하이퍼바이저에서 이미지를 붙이기만 해도 VM 안에서 실행이 일어남</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 레거시 Windows를 쓰는 HMI·EWS·SCADA 서버, 가상화된 SCADA 서버(하이퍼바이저 관리 권한 경유), 현장에서 USB를 쓰는 단말 (L2~L3)
+- 수법: 하이퍼바이저 권한으로 SCADA 서버 VM에 ISO 이미지를 연결해 자동 실행(2022 우크라이나), USB 매체의 자동 실행 설정 — USB를 통한 침투·전파 자체는 이동식 매체 전파(OTC-IA-04)
+- 가상화 관리 권한이 있으면 OT 네트워크를 거치지 않고 VM 내부에서 실행되므로 네트워크 감시를 우회함
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): 기존 하이퍼바이저 접근으로 SCADA 서버 VM에 a.iso를 연결했고, CD-ROM 자동 실행이 켜진 서버에서 이미지 속 VBS가 자동 실행됨 (INC-006, ATT&amp;CK C0034)</t>
+        </is>
+      </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
           <t>T0895</t>
@@ -7355,7 +7552,7 @@
       <c r="J31" s="17" t="inlineStr"/>
       <c r="K31" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L31" s="17" t="inlineStr">
@@ -7462,7 +7659,16 @@
           <t>https://attack.mitre.org/techniques/T0895</t>
         </is>
       </c>
-      <c r="AM31" s="17" t="inlineStr"/>
+      <c r="AM31" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 드라이브 문자·마운트 생성과 이동식 매체·이미지에서 시작된 프로세스를 감시하고, 하이퍼바이저의 가상 매체 연결 이벤트를 수집
+- 하이퍼바이저 관리 콘솔 로그인과 VM 설정 변경을 OT 변경 이력과 대조
+■ 대응
+- OT 호스트의 자동 실행·자동 재생을 정책으로 끄고, 이동식 매체는 검사 키오스크를 거친 뒤 사용
+- 가상화 관리 콘솔을 별도 관리망·다중 인증으로 보호하고 VM 가상 매체 연결 권한을 제한</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -7485,12 +7691,24 @@
           <t>예약 작업</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse task scheduling functionality to facilitate initial or recurring execution of malicious code.</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr"/>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 작업 스케줄러·cron·네트워크 장비 예약 작업에 악성 명령을 등록해, 정한 시각에 실행하거나 재부팅 뒤에도 유지하고, 원격 호스트에 작업을 만들어 확산할 수 있음
+- 운영·백업 자동화용 예약 작업이 많아 새 작업이 눈에 띄지 않고, 파괴형 공격은 여러 호스트에서 같은 시각에 동시 실행되게 맞춰 복구를 어렵게 함</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언, 도메인 그룹 정책을 받는 OT 호스트, OT 경계 방화벽의 예약 작업 기능 (L2~L3.5)
+- 수법: 그룹 정책 개체(GPO)로 예약 작업을 배포해 와이퍼를 일제히 실행(2022 우크라이나), 방화벽 예약 작업으로 공격자 CLI 스크립트를 매주 실행(2025 폴란드), 감염 직후 실행·재부팅 예약(Stuxnet·NotPetya)
+- 실행·지속·권한 상승 전술에 같은 기법으로 나타남(OTC-EX-11·PE-06·PV-03) — 통합: Enterprise 예약 작업(T1053.005), 그룹 정책 변조는 OTC-PV-04.1
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): GPO에 등록한 예약 작업으로 정해진 시각에 CaddyWiper를 실행 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2025 폴란드(2025-12): FortiGate 예약 작업에 공격자가 만든 CLI 스크립트를 걸어 매주 실행 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] NotPetya(2017-06): 감염 1시간 뒤 재부팅하는 작업을 만들어 디스크 암호화를 실행 (INC-016, ATT&amp;CK S0368)</t>
+        </is>
+      </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
           <t>T1053</t>
@@ -7513,7 +7731,7 @@
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L32" s="17" t="inlineStr">
@@ -7619,7 +7837,16 @@
           <t>https://attack.mitre.org/techniques/T1053</t>
         </is>
       </c>
-      <c r="AM32" s="17" t="inlineStr"/>
+      <c r="AM32" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 작업 스케줄러의 작업 생성·변경 이벤트와 원격 작업 생성(schtasks /s 등)을 수집하고, 승인된 예약 작업 목록과 정기 비교
+- 그룹 정책 변경과 방화벽·네트워크 장비의 예약 작업 설정 변경을 중앙 로그로 경보
+■ 대응
+- 예약 작업 생성 권한을 관리자 계정으로 제한하고, OT 도메인을 IT 도메인과 분리해 GPO 경유 일괄 배포를 막음
+- OT 호스트·경계 장비의 예약 작업을 변경 관리 대상으로 등록하고 설정 백업과 비교 점검</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -7642,12 +7869,25 @@
           <t>유효 계정 악용</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may steal the credentials of a specific user or service account using credential access techniques.</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr"/>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취하거나 새로 만든 유효 계정(도메인·로컬·서비스·장치 계정)으로 VPN·원격 서비스·제어 장치에 로그인해, 정상 사용자 권한으로 OT 환경에 머물고 이동할 수 있음
+- 인증을 정상 통과하므로 접근 통제와 다수 탐지 수단을 그대로 지나치며, 퇴사자·휴면·공용 계정 관리가 허술한 OT 환경에서 반복적으로 악용됨</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: IT·OT 도메인 계정, VPN·원격 접속 계정, EWS·HMI 로컬 계정, SQL 서버 계정, RTU·보호 계전기·시리얼 서버 같은 현장 장치 계정, 카메라 클라우드 관리 계정 (L1~L3.5·IoT)
+- 수법: 기업망에서 모은 자격증명으로 VPN·이중 연결(dual-homed) 시스템을 거쳐 제어망 진입(2015·2016 우크라이나), RDP 점프 박스 경유(Triton), 새 관리자·도메인 계정 생성, 해시 재사용 — 계정 탈취 수단은 OTC-LM-07·LM-08·LM-09
+- 통합: Enterprise 유효 계정(T1078·.002~.004)·계정 조작(T1098)·계정 생성(T1136·.001·.002)·해시 전달(T1550.002) — 기본·하드코딩 자격증명은 OTC-PE-05.1·05.2
+- 지속(OTC-PE-01)·측면 이동(OTC-LM-02) 전술에 같은 기법으로 나타나며, 퇴사자에게 남은 원격 접속 권한이 내부자 조작으로 이어진 수도 사고가 반복됨(INC-042, INC-043)
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): 기업망에서 탈취한 계정으로 VPN과 이중 연결 시스템을 거쳐 제어망에 들어가고, 권한 있는 도메인 계정을 새로 만들어 머묾 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 2025 폴란드(2025-12): 유효 계정으로 Hitachi·Mikronika RTU, 보호 계전기, Mikronika HMI, Moxa NPort에 접근하고, 권한 계정으로 FortiGate VPN을 거쳐 하위 망으로 이동 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] 미국 베이 지역 정수장(2021-01): 퇴사한 직원의 TeamViewer 계정으로 제어 시스템에 접속해 정수 처리 프로그램을 삭제 (INC-042)</t>
+        </is>
+      </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
           <t>T0859</t>
@@ -7670,7 +7910,7 @@
       </c>
       <c r="K33" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L33" s="17" t="inlineStr">
@@ -7818,7 +8058,16 @@
           <t>https://attack.mitre.org/techniques/T0859</t>
         </is>
       </c>
-      <c r="AM33" s="17" t="inlineStr"/>
+      <c r="AM33" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 계정의 로그인 시간·출발지·대상 장치를 기준선과 비교하고, 휴면·퇴사자·서비스 계정의 대화형 로그인과 새 관리자 계정 생성을 경보
+- 현장 장치(RTU·계전기·시리얼 서버) 로그인 기록을 VPN·점프 호스트 세션과 상관 분석해 승인된 원격 세션 없이 일어난 장치 접근 확인
+■ 대응
+- OT 계정·도메인을 IT와 분리하고, 원격·특권 접근에 다중 인증과 승인 기반 일시 권한(JIT)을 적용
+- 퇴사·계약 종료 때 원격 접속 계정을 즉시 폐기하고, 공용 계정을 개인 계정으로 바꾸며 계정 목록을 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -7841,12 +8090,22 @@
           <t>지멘스 프로젝트 파일</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may infect Siemens PLC project files (i.e., Step 7, WinCC, etc.) to achieve Execution, Persistence, and Lateral Movement objectives.</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr"/>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 Step 7·WinCC 같은 지멘스 PLC 프로젝트 파일에 악성 코드를 심거나 감염된 프로젝트를 들여와, 엔지니어가 프로젝트를 열 때마다 코드가 실행되게 할 수 있음
+- 프로젝트 파일은 EWS 사이와 협력업체 간에 정상적으로 오가므로 감염이 엔지니어링 업무를 따라 퍼지고, 정상 수정과 함께 바뀌면 변경 분석으로 가려내기 어려움</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: SIMATIC Step 7·WinCC가 설치된 EWS와 프로젝트 저장소·공유 폴더, 협력업체와 주고받는 프로젝트 사본 (L2~L3)
+- 수법: 프로젝트를 불러올 때 자동 실행되도록 프로젝트 폴더에 자신을 복사하고, 감염된 엔지니어링 소프트웨어로 연 깨끗한 프로젝트도 다시 감염(Stuxnet)
+- 감염된 EWS는 PLC로 내려보내는 코드까지 바꿀 수 있어 제어 프로그램 변조(OTC-PE-03)와 측면 이동의 발판이 됨 — 사용자가 파일을 열어야 실행되므로 사용자 실행 유도(OTC-EX-07)와 같은 방어가 필요
+■ 실제 사례
+- [실제 사고] Stuxnet(2010-06): Step 7 프로젝트에 자신을 복사해 프로젝트를 열 때 자동 실행되게 하고, 감염된 매니저로 연 프로젝트 파일도 감염시킴 (INC-009, ATT&amp;CK S0603)</t>
+        </is>
+      </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
           <t>T0873.001</t>
@@ -7865,7 +8124,7 @@
       <c r="J34" s="17" t="inlineStr"/>
       <c r="K34" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L34" s="17" t="inlineStr">
@@ -7966,7 +8225,16 @@
           <t>https://attack.mitre.org/techniques/T0873/001</t>
         </is>
       </c>
-      <c r="AM34" s="17" t="inlineStr"/>
+      <c r="AM34" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 프로젝트 파일·폴더의 예상치 못한 변경(새 DLL·실행 파일, 해시 변화)을 감시하고 버전 관리 저장소의 승인 본과 비교
+- 엔지니어링 소프트웨어가 프로젝트를 열 때 만드는 비정상 자식 프로세스·DLL 로드를 EDR로 확인
+■ 대응
+- 프로젝트 파일을 접근 통제된 버전 관리 저장소에서 관리하고, 협력업체에서 받은 프로젝트는 검사한 뒤 반입
+- 엔지니어링 소프트웨어의 프로젝트 보호(암호·무결성) 기능을 켜고 최신 패치 적용</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -7989,12 +8257,24 @@
           <t>제어 프로그램 변조</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify or add a program on a controller to affect how it interacts with the physical process, peripheral devices and other hosts on the network.</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr"/>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 프로그램을 바꾸거나 새 블록을 추가해, 제어기가 물리 공정·주변 장치·다른 호스트와 상호작용하는 방식을 바꾸고 그 상태로 오래 머물 수 있음
+- 바뀐 프로그램은 제어기를 재시작해도 그대로 실행되고, 엔지니어링 소프트웨어로 읽을 때 원래 코드를 보여주도록 숨길 수도 있어 오프라인 비교 없이는 찾기 어려움</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: PLC·PAC·DCS 제어기와 안전 제어기(SIS)의 사용자 프로그램(코드 블록·데이터 블록·함수 블록) (L1)
+- 수법: 대상 설비 구성에 맞춘 감염 코드 내려받기(Stuxnet), 프로그램 구성 단위(POU)에 웜 코드 복사(PLC-Blaster), 위장 엔지니어링 스테이션으로 실행 코드와 다른 소스를 심기(Rogue7)
+- 전달은 제어 프로그램 다운로드(OTC-LM-01.1~01.3), 실행 흐름 조작은 제어기 태스크 변조(OTC-EX-02), 결과는 운전 파라미터 변조(OTC-IP-02)·제어 조작(OTC-IM-07)으로 이어짐
+■ 실제 사례
+- [실제 사고] Stuxnet(2010-06): 대상 PLC 구성에 맞는 코드·데이터 블록을 내려받아 원심분리기 제어 로직을 바꾸고, 읽기 요청에는 원래 코드를 보여줌 (INC-009, ATT&amp;CK S0603)
+- [실증] PLC-Blaster(2016-03): 데이터 블록·함수·함수 블록에 자신을 복사해 PLC 사이로 퍼지는 웜 (INC-024, ATT&amp;CK S1006)
+- [실증] Rogue7(2019-08): S7-1500 PLC에 위장 엔지니어링 스테이션으로 로직을 내려받고 운영자에게는 원래 로직을 보여줌 (INC-078)</t>
+        </is>
+      </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
           <t>T0889</t>
@@ -8013,7 +8293,7 @@
       <c r="J35" s="17" t="inlineStr"/>
       <c r="K35" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L35" s="17" t="inlineStr">
@@ -8122,7 +8402,16 @@
           <t>https://attack.mitre.org/techniques/T0889</t>
         </is>
       </c>
-      <c r="AM35" s="17" t="inlineStr"/>
+      <c r="AM35" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기에서 프로그램을 정기적으로 올려받아 승인 기준본과 블록 단위로 비교(체크섬·해시)하고, 온라인 편집·프로그램 추가 기능 코드를 OT 네트워크 감시로 탐지
+- 장치 변경 경보·진단 버퍼와 엔지니어링 소프트웨어 변경 기록을 수집해 변경 관리 기록과 대조
+■ 대응
+- 제어기 접근 보호(읽기·쓰기 암호)와 키 스위치 RUN을 유지하고, 프로그램 변경은 승인 후 지정 EWS에서만 수행
+- 코드 서명·무결성 검증을 지원하는 제어기를 도입하고 승인된 프로그램 백업을 오프라인으로 보관</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -8706,12 +8995,23 @@
           <t>취약한 자격증명 (일반·상위기법)</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may target insecure credentials as a means to persist on a system or device or move laterally from one system or device to another.</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr"/>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치·소프트웨어에 미리 설정돼 공개된 기본 자격증명이나 펌웨어에 박힌 하드코딩 자격증명, 허술하게 저장된 자격증명을 써서, 계정을 탈취하지 않고도 제어 장치·서버에 로그인하고 머물거나 이동할 수 있음
+- 장치 교체 주기가 길고 일부 자격증명은 사용자가 바꿀 수 없어 노출 상태가 오래 이어지며, 로그인 자체는 정상이라 탐지가 어려움</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: PLC·HMI·RTU·IED·산업용 스위치·시리얼 서버·IoT 기기의 웹·텔넷·SSH·엔지니어링 접속과 SCADA·히스토리언 서버의 DB 계정 (L1~L3·IoT)
+- 하위 기법: 기본 자격증명(OTC-PE-05.1)·하드코딩 자격증명(OTC-PE-05.2) — 이 행은 자격증명을 평문·되돌릴 수 있는 형태로 저장하거나 약한 암호를 허용하는 결함처럼 하위 기법으로 나누기 어려운 근거를 모음
+- CISA ICS 권고에서 보호되지 않은 자격증명·약한 암호 정책(CWE-522·256·257·260·521) 199건, 2025년 이후 48건
+- 지속(OTC-PE-05.0)·측면 이동(OTC-LM-06.0) 전술에 같은 기법으로 나타나며, 실제 사고는 하위 기법에서 집계
+■ 실제 사례
+- [공개 취약점] CISA ICS 권고: 설정 파일·백업·통신에 자격증명이 평문이나 약한 형태로 남는 취약점 다수 — 장치 설정을 얻은 공격자가 그대로 로그인할 수 있음</t>
+        </is>
+      </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
           <t>T1694</t>
@@ -8730,7 +9030,7 @@
       <c r="J39" s="17" t="inlineStr"/>
       <c r="K39" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L39" s="17" t="inlineStr">
@@ -8853,7 +9153,16 @@
           <t>https://attack.mitre.org/techniques/T1694</t>
         </is>
       </c>
-      <c r="AM39" s="17" t="inlineStr"/>
+      <c r="AM39" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 평문 인증 프로토콜(텔넷·FTP·HTTP)의 로그인과 알려진 기본 계정 사용을 OT 네트워크 감시로 탐지하고 장치 로그인 기록 수집
+- 자산 점검 때 자격증명 관련 CISA ICS·벤더 권고 해당 여부를 자산 목록과 대조
+■ 대응
+- 설치·인수 때 기본 자격증명을 바꾸고 장치별 고유 암호를 관리하며, 바꿀 수 없는 자격증명은 네트워크 분리·허용 목록으로 보완
+- 자격증명 저장 결함을 패치하고 암호화 통신(HTTPS·SSH)을 적용하며, 쓰지 않는 텔넷·FTP 서비스를 끔</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -8876,12 +9185,25 @@
           <t>기본 자격증명</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage manufacturer or supplier set default credentials on control system devices.</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr"/>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제조사가 출하 때 설정해 매뉴얼·인터넷에 공개된 기본 계정·암호로 PLC·HMI·RTU·IoT 기기에 로그인해, 관리자 권한을 바로 얻고 설정·화면·프로그램을 바꿀 수 있음
+- 검색 엔진으로 노출 장치를 찾아 기본 암호를 넣는 것만으로 대규모 공격이 가능해, 숙련도가 낮은 핵티비스트와 IoT 봇넷이 가장 많이 쓰는 경로임</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Unitronics Vision 같은 일체형 PLC·HMI, RTU·보호 계전기·시리얼 서버, VNC 기반 HMI, IP 카메라·DVR 등 IoT 기기 (L1~L2·IoT)
+- 인터넷 노출 장치 악용(OTC-IA-11)과 결합해 화면 변조·설정값 조작·관리자 암호 변경(OTC-IR-10)으로 이어지고, IoT 기기는 봇넷 편입(OTC-IM-14.1)이나 기기 파괴로 이어짐
+- CISA ICS 권고에서 기본 자격증명·안전하지 않은 기본 설정(CWE-1392·1393·1188) 48건, 2025년 이후 27건 — KEV: Unitronics Vision 기본 암호(CVE-2023-6448)
+- 통합: Enterprise 기본 계정(T1078.001)
+■ 실제 사례
+- [실제 사고] Unitronics 화면 변조(2023-11): CyberAv3ngers가 인터넷에 노출된 Unitronics PLC·HMI에 기본 암호로 접속해 화면을 바꿨고, 알리퀴파 수도국 가압장은 수동 운전으로 전환 (INC-005, ATT&amp;CK C0031)
+- [실제 사고] 2025 폴란드(2025-12): 기본 자격증명으로 Hitachi·Mikronika RTU, 보호 계전기, Moxa NPort 등에 접근 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] Mirai(2016-10): 텔넷 기본 계정으로 IP 카메라·DVR 수십만 대를 감염시켜 대규모 DDoS 봇넷을 구성 (INC-032)</t>
+        </is>
+      </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
           <t>T1694.001</t>
@@ -8904,7 +9226,7 @@
       </c>
       <c r="K40" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L40" s="17" t="inlineStr">
@@ -9040,7 +9362,16 @@
           <t>https://attack.mitre.org/techniques/T1694/001</t>
         </is>
       </c>
-      <c r="AM40" s="17" t="inlineStr"/>
+      <c r="AM40" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 장치 로그인 기록과 OT 네트워크 감시로 기본 계정 이름의 로그인과 반복 로그인 시도를 탐지
+- 외부 공격 표면 점검과 내부 자산 점검으로 기본 암호가 남은 장치를 정기 확인
+■ 대응
+- 설치·인수 시험 항목에 기본 암호 변경을 넣고, 장치별 고유 암호를 암호 관리 도구로 관리
+- 첫 사용 때 암호 변경을 강제하는 제품을 우선 도입하고 장치의 인터넷 노출을 없앰</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
@@ -9063,12 +9394,24 @@
           <t>하드코딩 자격증명</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage credentials that are hardcoded in software or firmware to gain an unauthorized interactive user session to an asset.</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr"/>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 소프트웨어·펌웨어에 박혀 있는 계정·암호·암호키를 찾아내, 같은 제품을 쓰는 모든 현장의 장치에 로그인하거나 엔지니어링 인증을 우회할 수 있음
+- 사용자가 바꾸거나 끌 수 없는 경우가 많아 패치 전까지 노출이 이어지고, 한 번 공개되면 같은 제품군 전체가 동시에 위험해짐</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: SCADA·HMI 소프트웨어의 DB 계정, PLC·제어기의 엔지니어링 인증 키, 임베디드 장치의 서비스·유지보수 계정과 인증서·API 토큰 (L1~L2)
+- 수법: WinCC DB 서버의 하드코딩 암호로 인근 시스템 감염(Stuxnet), Omron PLC의 하드코딩 자격증명으로 로그인(INCONTROLLER, CVE-2022-34151)
+- CISA ICS 권고에서 하드코딩 자격증명·키(CWE-798·321·259) 270건, 2025년 이후 69건 — KEV: Rockwell Logix 제어기 인증 키 노출(CVE-2021-22681)
+■ 실제 사례
+- [실제 사고] Stuxnet(2010-06): WinCC 소프트웨어 DB 서버에 하드코딩된 암호로 인근 시스템에 퍼짐 (INC-009, ATT&amp;CK S0603)
+- [위협인텔] PIPEDREAM(2022-04): INCONTROLLER가 Omron PLC의 하드코딩 자격증명(CVE-2022-34151)으로 로그인하는 기능을 갖춘 채 발견 (INC-022, ATT&amp;CK S1045)
+- [공개 취약점] Rockwell Logix(CVE-2021-22681): 엔지니어링 소프트웨어와 제어기 사이 인증 키가 노출돼 원격에서 제어기 인증을 우회 — KEV 등재</t>
+        </is>
+      </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
           <t>T1694.002</t>
@@ -9087,7 +9430,7 @@
       <c r="J41" s="17" t="inlineStr"/>
       <c r="K41" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L41" s="17" t="inlineStr">
@@ -9190,7 +9533,16 @@
           <t>https://attack.mitre.org/techniques/T1694/002</t>
         </is>
       </c>
-      <c r="AM41" s="17" t="inlineStr"/>
+      <c r="AM41" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CISA ICS·벤더 권고의 하드코딩 자격증명 해당 제품을 자산 목록과 대조하고, 해당 계정·키를 쓰는 로그인을 OT 네트워크 감시 규칙으로 탐지
+- 엔지니어링 프로토콜 세션의 발신지를 지정 EWS 목록과 비교
+■ 대응
+- 벤더 패치·펌웨어 업데이트로 하드코딩 자격증명을 없애고, 패치 전에는 장치 접근을 허용 목록·네트워크 분리로 제한
+- 조달 요건에 하드코딩 자격증명 금지와 자격증명 변경 기능을 명시</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -9213,12 +9565,24 @@
           <t>예약 작업</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse task scheduling functionality to facilitate initial or recurring execution of malicious code.</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr"/>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 작업 스케줄러·cron·네트워크 장비 예약 작업에 악성 명령을 등록해, 정한 시각에 실행하거나 재부팅 뒤에도 유지하고, 원격 호스트에 작업을 만들어 확산할 수 있음
+- 운영·백업 자동화용 예약 작업이 많아 새 작업이 눈에 띄지 않고, 파괴형 공격은 여러 호스트에서 같은 시각에 동시 실행되게 맞춰 복구를 어렵게 함</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언, 도메인 그룹 정책을 받는 OT 호스트, OT 경계 방화벽의 예약 작업 기능 (L2~L3.5)
+- 수법: 그룹 정책 개체(GPO)로 예약 작업을 배포해 와이퍼를 일제히 실행(2022 우크라이나), 방화벽 예약 작업으로 공격자 CLI 스크립트를 매주 실행(2025 폴란드), 감염 직후 실행·재부팅 예약(Stuxnet·NotPetya)
+- 실행·지속·권한 상승 전술에 같은 기법으로 나타남(OTC-EX-11·PE-06·PV-03) — 통합: Enterprise 예약 작업(T1053.005), 그룹 정책 변조는 OTC-PV-04.1
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): GPO에 등록한 예약 작업으로 정해진 시각에 CaddyWiper를 실행 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2025 폴란드(2025-12): FortiGate 예약 작업에 공격자가 만든 CLI 스크립트를 걸어 매주 실행 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] NotPetya(2017-06): 감염 1시간 뒤 재부팅하는 작업을 만들어 디스크 암호화를 실행 (INC-016, ATT&amp;CK S0368)</t>
+        </is>
+      </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
           <t>T1053</t>
@@ -9241,7 +9605,7 @@
       </c>
       <c r="K42" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L42" s="17" t="inlineStr">
@@ -9347,7 +9711,16 @@
           <t>https://attack.mitre.org/techniques/T1053</t>
         </is>
       </c>
-      <c r="AM42" s="17" t="inlineStr"/>
+      <c r="AM42" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 작업 스케줄러의 작업 생성·변경 이벤트와 원격 작업 생성(schtasks /s 등)을 수집하고, 승인된 예약 작업 목록과 정기 비교
+- 그룹 정책 변경과 방화벽·네트워크 장비의 예약 작업 설정 변경을 중앙 로그로 경보
+■ 대응
+- 예약 작업 생성 권한을 관리자 계정으로 제한하고, OT 도메인을 IT 도메인과 분리해 GPO 경유 일괄 배포를 막음
+- OT 호스트·경계 장비의 예약 작업을 변경 관리 대상으로 등록하고 설정 백업과 비교 점검</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -9370,12 +9743,23 @@
           <t>SQL 저장 프로시저</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse SQL stored procedures to establish persistent access to systems.</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr"/>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 SCADA·히스토리언이 쓰는 MS-SQL 등 데이터베이스의 저장 프로시저(xp_cmdshell 등)를 악용하거나 새로 등록해, DB 서버에서 OS 명령을 실행하고 접근을 유지할 수 있음
+- DB는 SCADA 운영에 필수라 끌 수 없고, 저장 프로시저 실행은 DB 내부 활동이라 호스트 보안 도구가 잘 보지 못함</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: SCADA 서버·데이터 히스토리언·MES의 MS-SQL 데이터베이스와 WinCC 같은 HMI 소프트웨어의 내장 DB (L2~L3)
+- 수법: xp_cmdshell로 OS 명령 실행·악성 코드 추출(Stuxnet), 여러 MS-SQL 저장 프로시저로 명령 실행과 서버 간 연결(2016 우크라이나)
+- 하드코딩·기본 DB 계정(OTC-PE-05.1·05.2)과 함께 쓰이며, 명령 실행은 명령줄 인터페이스(OTC-EX-01)로 이어짐
+■ 실제 사례
+- [실제 사고] 2016 우크라이나(2016-12): 여러 MS-SQL 저장 프로시저와 xp_cmdshell로 DB 서버에서 명령을 실행 (INC-003, ATT&amp;CK C0025)
+- [실제 사고] Stuxnet(2010-06): WinCC DB에 SQL 코드를 저장하고 xp_cmdshell로 자신을 추출·실행 (INC-009, ATT&amp;CK S0603)</t>
+        </is>
+      </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
           <t>T1505.001</t>
@@ -9394,7 +9778,7 @@
       <c r="J43" s="17" t="inlineStr"/>
       <c r="K43" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L43" s="17" t="inlineStr">
@@ -9496,7 +9880,16 @@
           <t>https://attack.mitre.org/techniques/T1505/001</t>
         </is>
       </c>
-      <c r="AM43" s="17" t="inlineStr"/>
+      <c r="AM43" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- DB 감사로 xp_cmdshell 활성화·실행, 새 저장 프로시저·시작 프로시저 등록, 연결 서버 생성을 기록하고 경보
+- SQL 서버 프로세스가 명령 셸을 만드는 프로세스 체인을 EDR로 탐지
+■ 대응
+- xp_cmdshell 같은 위험 확장 프로시저를 끄고, SCADA·히스토리언 DB 계정을 최소 권한으로 운영하며 기본·공용 DB 계정 제거
+- DB 서버 접속을 OT 내부 지정 클라이언트로 제한하고 벤더 권고 보안 설정 적용</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -9519,12 +9912,23 @@
           <t>웹셸</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may backdoor web servers with web shells to establish persistent access to systems.</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr"/>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 인터넷이나 OT 경계에 노출된 웹 서버에 웹셸을 심어, 이후 언제든 그 서버로 명령을 실행하고 내부망으로 터널을 뚫을 수 있음
+- 정상 웹 요청처럼 보이는 HTTP(S) 트래픽으로 동작하고 웹 서버 파일 하나만 남아, 처음 악용한 취약점을 패치한 뒤에도 접근이 유지됨</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 인터넷 노출 웹 서버, 웹 기반 HMI·SCADA 서버, 히스토리언·원격 감시 포털, OT DMZ의 웹 애플리케이션 서버 (L3~L3.5)
+- 수법: reGeorg 계열 웹셸로 HTTP 터널을 만들어 내부망에 접근(2022 우크라이나 Neo-REGEORG, 리비우 지역난방 ReGeorg 변종) — 연결 프록시(OTC-C2-02)와 결합
+- 공개 애플리케이션 취약점 악용(OTC-IA-02) 직후 지속 수단으로 쓰이므로, 패치에 그치지 말고 웹셸 존재를 함께 점검해야 함
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): 인터넷에 노출된 서버에 Neo-REGEORG 웹셸을 심어 내부 접근 경로로 사용 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 리비우 지역난방(2024-01): 최초 침투 뒤 ReGeorg 변종 웹셸을 설치해 접근을 유지 (INC-007, ATT&amp;CK C0041)</t>
+        </is>
+      </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
           <t>T1505.003</t>
@@ -9543,7 +9947,7 @@
       <c r="J44" s="17" t="inlineStr"/>
       <c r="K44" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L44" s="17" t="inlineStr">
@@ -9644,7 +10048,16 @@
           <t>https://attack.mitre.org/techniques/T1505/003</t>
         </is>
       </c>
-      <c r="AM44" s="17" t="inlineStr"/>
+      <c r="AM44" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹 서버 디렉터리의 새·변경 스크립트 파일을 파일 무결성 감시로 탐지하고, 웹 서버 프로세스가 명령 셸을 만들면 경보
+- 웹 로그에서 특정 파일로 반복되는 POST 요청과 HTTP 터널링 패턴 탐지
+■ 대응
+- OT 관련 웹 서버를 인터넷에서 분리하거나 WAF·리버스 프록시 뒤에 두고, 웹 루트 쓰기 권한을 제한
+- 침해 복구 때 패치와 함께 웹 서버 파일 전체의 무결성을 점검하거나 재구축</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -9667,12 +10080,24 @@
           <t>시스템 서비스 생성·변조</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may create or modify system-level processes to repeatedly execute malicious payloads as part of persistence.</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr"/>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 Windows 서비스·Linux systemd 같은 시스템 서비스를 새로 만들거나 기존 서비스의 실행 경로를 바꿔, 부팅 때마다 높은 권한으로 악성 코드를 실행할 수 있음
+- OT 호스트에는 SCADA·통신 드라이버 같은 벤더 서비스가 많아 낯선 서비스가 섞여도 눈에 띄지 않고, 서명된 드라이버를 쓰면 정상 구성요소로 보임</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언과 Linux 기반 SCADA·게이트웨이 서버 (L2~L3)
+- 수법: 기존 서비스의 ImagePath를 백도어로 교체(Industroyer), systemd 유닛으로 터널 도구 상주(2022 우크라이나 GOGETTER), 부팅 드라이버 서비스 등록(Stuxnet·Duqu), 서비스 제어 관리자·PsExec로 원격 서비스 실행(NotPetya·Bad Rabbit)
+- 지속(OTC-PE-08)·권한 상승(OTC-PV-05) 전술에 같은 기법으로 나타남 — 통합: Enterprise systemd 서비스(T1543.002)·Windows 서비스(T1543.003)·서비스 실행(T1569.002)
+■ 실제 사례
+- [실제 사고] 2016 우크라이나(2016-12): 임의 시스템 서비스로 Industroyer를 부팅 때 실행하고, 기존 서비스의 ImagePath를 새 백도어로 바꿈 (INC-003, ATT&amp;CK C0025)
+- [실제 사고] 2022 우크라이나(2022-10): systemd에 GOGETTER를 등록해 시스템 시작 때마다 실행되게 함 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] WannaCry(2017-05): 'mssecsvc2.0' 서비스를 만들어 퍼지며 공장 생산 라인을 멈춤 (INC-015, ATT&amp;CK S0366)</t>
+        </is>
+      </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
           <t>T1543</t>
@@ -9695,7 +10120,7 @@
       </c>
       <c r="K45" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L45" s="17" t="inlineStr">
@@ -9805,7 +10230,16 @@
           <t>https://attack.mitre.org/techniques/T1543</t>
         </is>
       </c>
-      <c r="AM45" s="17" t="inlineStr"/>
+      <c r="AM45" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 생성·변경 이벤트(Windows 7045·4697, systemd 유닛 파일 변경)를 수집하고 승인된 서비스 목록과 정기 비교
+- 서비스 실행 파일의 경로·서명 변화와 PsExec 같은 원격 서비스 생성을 경보
+■ 대응
+- 서비스 생성·변경 권한을 관리자로 제한하고, 드라이버 서명 강제와 취약 드라이버 차단 목록 적용
+- 벤더 서비스 기준 목록을 자산 관리에 등록하고, 서비스 변경은 변경 관리로 승인</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
@@ -9828,12 +10262,24 @@
           <t>후킹</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may hook into application programming interface (API) functions used by processes to redirect calls for execution and privilege escalation means.</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr"/>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 API 함수 주소·명령 처리기를 가로채거나 정상 프로세스에 코드를 주입해, 정상 기능이 호출될 때 자신의 코드가 먼저 실행되게 할 수 있음
+- 신뢰된 프로세스·펌웨어 안에서 실행돼 실행 주체가 정상으로 보이고, 반환값까지 바꿀 수 있어 감염 사실을 숨기는 데도 쓰임</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 엔지니어링 소프트웨어·HMI가 쓰는 Windows DLL, 신뢰된 시스템 프로세스(svchost·explorer), 안전 제어기 펌웨어의 명령 처리기 (L1~L3)
+- 수법: 프로젝트 파일을 여는 API의 가져오기 주소 테이블(IAT) 후킹(Stuxnet), 안전 제어기 진단 명령 처리기의 함수 포인터 변경(Triton), 정상 프로세스 DLL 주입·프로세스 할로잉(BlackEnergy·Duqu·Havex)
+- 엔지니어링 소프트웨어의 PLC 통신 DLL을 가짜로 바꿔 블록 읽기·쓰기를 가로채는 수법은 루트킷(OTC-EV-03)으로 분류 — 통합: Enterprise 프로세스 주입(T1055)·DLL 주입(T1055.001)·프로세스 할로잉(T1055.012)
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 'get main processor diagnostic data' 명령 처리기의 함수 포인터를 imain.bin 주소로 바꿔 정상 처리 전에 공격 코드가 실행되게 함 (INC-004, ATT&amp;CK S1009)
+- [실제 사고] Stuxnet(2010-06): 프로젝트 파일을 여는 API를 IAT 후킹으로 가로채고 신뢰된 프로세스에 DLL 전체를 주입 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] 2015 우크라이나(2015-12): BlackEnergy를 svchost.exe에 올린 뒤 C2 통신용 브라우저 프로세스를 띄움 (INC-002, ATT&amp;CK C0028)</t>
+        </is>
+      </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
           <t>T0874</t>
@@ -9856,7 +10302,7 @@
       </c>
       <c r="K46" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L46" s="17" t="inlineStr">
@@ -9987,7 +10433,16 @@
           <t>https://attack.mitre.org/techniques/T0874</t>
         </is>
       </c>
-      <c r="AM46" s="17" t="inlineStr"/>
+      <c r="AM46" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- EDR로 원격 스레드 생성·타 프로세스 메모리 쓰기 같은 주입 패턴과 엔지니어링 소프트웨어에 로드된 미서명 DLL 탐지(OT 벤더 호환성 확인 후 적용)
+- PLC·안전 제어기는 벤더 진단 도구로 펌웨어·메모리 무결성을 점검하고, 평소 쓰지 않는 진단 명령 사용을 OT 네트워크 감시로 확인
+■ 대응
+- 엔지니어링 소프트웨어·HMI 설치 경로의 쓰기 권한을 제한하고 DLL 서명 검증·애플리케이션 허용 목록 적용
+- 제어기 펌웨어 무결성 검증 기능을 켜고, 안전 제어기의 원격 프로그래밍은 운전 중 차단</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
@@ -10010,12 +10465,25 @@
           <t>권한 상승용 취약점 악용</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit software vulnerabilities in an attempt to elevate privileges.</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr"/>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영체제·엔지니어링 소프트웨어·제어기 펌웨어의 취약점을 악용해, 일반 사용자 권한에서 관리자·커널·펌웨어 수준 권한으로 올라갈 수 있음
+- OT 호스트는 패치 주기가 길어 알려진 로컬 권한 상승 취약점이 오래 남고, 제어기 펌웨어 취약점은 공개와 패치 자체가 늦음</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: EWS·HMI·SCADA 서버의 Windows·Linux와 그 위의 엔지니어링·SCADA 소프트웨어, 안전 제어기·PLC 펌웨어, 취약한 서명 드라이버 (L1~L3)
+- 수법: 안전 제어기 펌웨어의 시스템 호출 0-day로 임의 쓰기 권한 확보(Triton), Windows 로컬 권한 상승 취약점(Stuxnet), 취약한 서명 드라이버로 미서명 드라이버 적재(INCONTROLLER)
+- CISA ICS 권고에서 로컬 권한 관리 결함(CWE-269·732·276·250·427·428·266) 273건, 2025년 이후 63건 — 설치 폴더 권한·DLL 검색 경로 결함이 다수
+- 통합: Enterprise 권한 상승 취약점 악용(T1068)
+■ 실제 사례
+- [실제 사고] Triton(2017-08): Tricon MP3008 펌웨어(10.0~10.4)의 미공개 시스템 호출 취약점으로 2바이트 임의 쓰기를 얻어 권한을 높임 (INC-004, ATT&amp;CK S1009)
+- [실제 사고] Stuxnet(2010-06): MS10-073과 당시 미공개였던 작업 스케줄러 취약점으로 Windows 로컬 권한 상승 (INC-009, ATT&amp;CK S0603)
+- [위협인텔] PIPEDREAM(2022-04): 취약한 ASRock 드라이버(CVE-2020-15368)로 자체 미서명 드라이버를 적재하는 기능을 갖춘 채 발견 (INC-022, ATT&amp;CK S1045)</t>
+        </is>
+      </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
           <t>T0890</t>
@@ -10038,7 +10506,7 @@
       </c>
       <c r="K47" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L47" s="17" t="inlineStr">
@@ -10171,7 +10639,16 @@
           <t>https://attack.mitre.org/techniques/T0890</t>
         </is>
       </c>
-      <c r="AM47" s="17" t="inlineStr"/>
+      <c r="AM47" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 일반 계정 프로세스가 SYSTEM·root 권한 프로세스를 만들거나 알려진 취약 드라이버가 적재되면 EDR로 경보
+- 제어기는 벤더 진단으로 메모리·펌웨어 무결성을 점검하고, 비정상 재시작·오류 경보를 확인
+■ 대응
+- 로컬 권한 상승 취약점(KEV 우선)과 엔지니어링 소프트웨어 설치 폴더 권한 결함을 패치하고, 취약 드라이버 차단 목록 적용
+- 운영 계정에 관리자 권한을 주지 않고 애플리케이션 허용 목록·익스플로잇 보호를 적용</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -10194,12 +10671,24 @@
           <t>예약 작업</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse task scheduling functionality to facilitate initial or recurring execution of malicious code.</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr"/>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 작업 스케줄러·cron·네트워크 장비 예약 작업에 악성 명령을 등록해, 정한 시각에 실행하거나 재부팅 뒤에도 유지하고, 원격 호스트에 작업을 만들어 확산할 수 있음
+- 운영·백업 자동화용 예약 작업이 많아 새 작업이 눈에 띄지 않고, 파괴형 공격은 여러 호스트에서 같은 시각에 동시 실행되게 맞춰 복구를 어렵게 함</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언, 도메인 그룹 정책을 받는 OT 호스트, OT 경계 방화벽의 예약 작업 기능 (L2~L3.5)
+- 수법: 그룹 정책 개체(GPO)로 예약 작업을 배포해 와이퍼를 일제히 실행(2022 우크라이나), 방화벽 예약 작업으로 공격자 CLI 스크립트를 매주 실행(2025 폴란드), 감염 직후 실행·재부팅 예약(Stuxnet·NotPetya)
+- 실행·지속·권한 상승 전술에 같은 기법으로 나타남(OTC-EX-11·PE-06·PV-03) — 통합: Enterprise 예약 작업(T1053.005), 그룹 정책 변조는 OTC-PV-04.1
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): GPO에 등록한 예약 작업으로 정해진 시각에 CaddyWiper를 실행 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2025 폴란드(2025-12): FortiGate 예약 작업에 공격자가 만든 CLI 스크립트를 걸어 매주 실행 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] NotPetya(2017-06): 감염 1시간 뒤 재부팅하는 작업을 만들어 디스크 암호화를 실행 (INC-016, ATT&amp;CK S0368)</t>
+        </is>
+      </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
           <t>T1053</t>
@@ -10222,7 +10711,7 @@
       </c>
       <c r="K48" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L48" s="17" t="inlineStr">
@@ -10328,7 +10817,16 @@
           <t>https://attack.mitre.org/techniques/T1053</t>
         </is>
       </c>
-      <c r="AM48" s="17" t="inlineStr"/>
+      <c r="AM48" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 작업 스케줄러의 작업 생성·변경 이벤트와 원격 작업 생성(schtasks /s 등)을 수집하고, 승인된 예약 작업 목록과 정기 비교
+- 그룹 정책 변경과 방화벽·네트워크 장비의 예약 작업 설정 변경을 중앙 로그로 경보
+■ 대응
+- 예약 작업 생성 권한을 관리자 계정으로 제한하고, OT 도메인을 IT 도메인과 분리해 GPO 경유 일괄 배포를 막음
+- OT 호스트·경계 장비의 예약 작업을 변경 관리 대상으로 등록하고 설정 백업과 비교 점검</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
@@ -10351,12 +10849,23 @@
           <t>그룹 정책 변조</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify Group Policy Objects (GPOs) to subvert the intended discretionary access controls for a domain, usually with the intention of escalating privileges on the domain.</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="inlineStr"/>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 도메인 관리자 권한으로 그룹 정책 개체(GPO)를 바꿔, 도메인에 속한 OT 호스트 전체에 악성 코드 실행·보안 설정 해제를 한 번에 내릴 수 있음
+- 정상 관리 기능으로 많은 호스트에 동시에 적용돼 파괴형 공격이 매우 빠르게 퍼지고, OT 호스트가 IT 도메인에 묶여 있으면 IT 침해가 그대로 OT로 번짐</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Active Directory 도메인에 가입한 EWS·HMI·SCADA 서버·히스토리언과 OT 도메인 컨트롤러 (L2~L3)
+- 수법: GPO에 예약 작업·스크립트를 넣어 와이퍼를 배포·실행(2022 우크라이나·2025 폴란드), 보안 도구·방화벽 설정 해제
+- 권한 상승(OTC-PV-04.1)·방어 회피(OTC-EV-08.1) 전술에 같은 기법으로 나타남 — 예약 작업은 OTC-EX-11, 스크립트 실행은 OTC-EX-05
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): 그룹 정책 개체로 피해 기관 IT 환경에 CaddyWiper를 배포·실행 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2025 폴란드(2025-12): 그룹 정책 개체로 네트워크 공유에 둔 와이퍼를 피해 장치들에 배포 (INC-008, ATT&amp;CK C0063)</t>
+        </is>
+      </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
           <t>T1484.001</t>
@@ -10375,7 +10884,7 @@
       <c r="J49" s="17" t="inlineStr"/>
       <c r="K49" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L49" s="17" t="inlineStr">
@@ -10478,7 +10987,16 @@
           <t>https://attack.mitre.org/techniques/T1484/001</t>
         </is>
       </c>
-      <c r="AM49" s="17" t="inlineStr"/>
+      <c r="AM49" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- GPO 생성·변경 이벤트(디렉터리 서비스 변경 감사 5136 등)와 SYSVOL의 새 스크립트·예약 작업 파일을 감시하고 근무 외 변경을 경보
+- GPO 변경 직후 다수 호스트에서 같은 프로세스가 동시에 생기는 패턴을 상관 분석
+■ 대응
+- OT를 별도 도메인으로 운영해 IT 도메인과의 신뢰 관계를 최소화하고, GPO 편집 권한을 소수 계정으로 제한
+- 도메인 관리자 계정을 특권 접근 관리·다중 인증으로 보호하고, GPO 백업으로 변경 시 즉시 복원</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -10501,12 +11019,24 @@
           <t>시스템 서비스 생성·변조</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may create or modify system-level processes to repeatedly execute malicious payloads as part of persistence.</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr"/>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 Windows 서비스·Linux systemd 같은 시스템 서비스를 새로 만들거나 기존 서비스의 실행 경로를 바꿔, 부팅 때마다 높은 권한으로 악성 코드를 실행할 수 있음
+- OT 호스트에는 SCADA·통신 드라이버 같은 벤더 서비스가 많아 낯선 서비스가 섞여도 눈에 띄지 않고, 서명된 드라이버를 쓰면 정상 구성요소로 보임</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언과 Linux 기반 SCADA·게이트웨이 서버 (L2~L3)
+- 수법: 기존 서비스의 ImagePath를 백도어로 교체(Industroyer), systemd 유닛으로 터널 도구 상주(2022 우크라이나 GOGETTER), 부팅 드라이버 서비스 등록(Stuxnet·Duqu), 서비스 제어 관리자·PsExec로 원격 서비스 실행(NotPetya·Bad Rabbit)
+- 지속(OTC-PE-08)·권한 상승(OTC-PV-05) 전술에 같은 기법으로 나타남 — 통합: Enterprise systemd 서비스(T1543.002)·Windows 서비스(T1543.003)·서비스 실행(T1569.002)
+■ 실제 사례
+- [실제 사고] 2016 우크라이나(2016-12): 임의 시스템 서비스로 Industroyer를 부팅 때 실행하고, 기존 서비스의 ImagePath를 새 백도어로 바꿈 (INC-003, ATT&amp;CK C0025)
+- [실제 사고] 2022 우크라이나(2022-10): systemd에 GOGETTER를 등록해 시스템 시작 때마다 실행되게 함 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] WannaCry(2017-05): 'mssecsvc2.0' 서비스를 만들어 퍼지며 공장 생산 라인을 멈춤 (INC-015, ATT&amp;CK S0366)</t>
+        </is>
+      </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
           <t>T1543</t>
@@ -10529,7 +11059,7 @@
       </c>
       <c r="K50" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L50" s="17" t="inlineStr">
@@ -10639,7 +11169,16 @@
           <t>https://attack.mitre.org/techniques/T1543</t>
         </is>
       </c>
-      <c r="AM50" s="17" t="inlineStr"/>
+      <c r="AM50" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 생성·변경 이벤트(Windows 7045·4697, systemd 유닛 파일 변경)를 수집하고 승인된 서비스 목록과 정기 비교
+- 서비스 실행 파일의 경로·서명 변화와 PsExec 같은 원격 서비스 생성을 경보
+■ 대응
+- 서비스 생성·변경 권한을 관리자로 제한하고, 드라이버 서명 강제와 취약 드라이버 차단 목록 적용
+- 벤더 서비스 기준 목록을 자산 관리에 등록하고, 서비스 변경은 변경 관리로 승인</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -10662,12 +11201,22 @@
           <t>회피용 취약점 악용</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit a software vulnerability to take advantage of a programming error in a program, service, or within the operating system software or kernel itself to evade detection.</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr"/>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 소프트웨어·펌웨어 취약점을 악용해 장치의 무결성 점검·보안 기능을 끄거나 우회해, 심어 둔 코드가 발견되지 않게 할 수 있음
+- 안전 제어기처럼 펌웨어·프로그램 체크섬을 계속 확인하는 장치도 점검 루틴 자체가 무력화되면 이상을 보고하지 못함</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: 안전 제어기(SIS)·PLC의 펌웨어 무결성 점검, EWS·HMI의 보안 소프트웨어·커널 보호, 경계 장비의 보안 기능 (L1~L3.5)
+- 수법: 펌웨어 메모리에 페이로드를 넣은 뒤 RAM/ROM 일관성 점검을 끔(Triton) — 권한 상승용 취약점 악용(OTC-PV-02)으로 얻은 권한을 회피에 쓰는 형태가 일반적
+- 사전에 원격 시스템 정보 탐색(OTC-DS-05)으로 장치 모델·펌웨어 버전과 보안 기능을 확인해 대상에 맞는 취약점을 고름
+■ 실제 사례
+- [실제 사고] Triton(2017-08): Tricon 펌웨어 메모리 영역에 imain.bin을 넣은 뒤 RAM/ROM 일관성 점검을 꺼, 체크섬 기반의 상시 감시를 피함 (INC-004, ATT&amp;CK S1009)</t>
+        </is>
+      </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
           <t>T0820</t>
@@ -10686,7 +11235,7 @@
       <c r="J51" s="17" t="inlineStr"/>
       <c r="K51" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L51" s="17" t="inlineStr">
@@ -10818,7 +11367,16 @@
           <t>https://attack.mitre.org/techniques/T0820</t>
         </is>
       </c>
-      <c r="AM51" s="17" t="inlineStr"/>
+      <c r="AM51" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기 진단 정보(펌웨어·프로그램 체크섬, 자체 진단 상태)를 정기 수집해 점검 기능이 꺼지거나 값이 멈추면 경보
+- EWS·HMI에서는 보안 기능 해제·커널 드라이버 적재 같은 이상을 EDR로 확인
+■ 대응
+- 장치 펌웨어·OS를 패치하고, 무결성 점검 결과를 장치 밖의 별도 감시 시스템에서 교차 확인
+- 안전 제어기 키 스위치를 RUN에 두어 메모리 쓰기 경로를 막고, 펌웨어 업데이트는 서명 검증을 거침</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -10841,12 +11399,24 @@
           <t>위장</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may use masquerading to disguise a malicious application or executable as another file, to avoid operator and engineer suspicion.</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr"/>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 악성 파일·서비스·계정을 벤더 프로그램·업데이트 파일·전력 프로토콜 이름처럼 꾸며, 운영자와 엔지니어가 정상 구성요소로 여기게 할 수 있음
+- OT 호스트에는 벤더별 실행 파일·서비스가 많아 이름만으로 정상 여부를 가리기 어렵고, 탈취한 인증서로 서명하면 서명 검증도 통과함</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: EWS·HMI·SCADA 서버의 실행 파일·DLL·서비스·계정과 경계 장비의 설정 규칙 이름 (L2~L3.5)
+- 수법: SIS 로그 분석 도구 trilog.exe로 위장(Triton), 전력 프로토콜 이름의 DLL·EXE(2016 우크라이나), 정상처럼 보이는 systemd 서비스(2022 우크라이나), 기존 기관명을 흉내 낸 방화벽 규칙(2025 폴란드), update.exe(EKANS), 탈취 인증서 서명(Stuxnet·LockerGoga)
+- 통합: Enterprise 위장(T1036·.004·.005·.008·.010)·코드 서명 위조(T1553.002)·정상 프로그램 변조(T1554) — 엔지니어링 DLL을 바꿔 PLC 호출을 가로채는 Stuxnet 수법은 루트킷(OTC-EV-03)과 연계
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 공격 도구를 Triconex의 SIS 로그 분석 소프트웨어 trilog.exe로 위장하고, 주입기는 표준 Tricon 프로그램처럼 꾸밈 (INC-004, ATT&amp;CK S1009)
+- [실제 사고] 2016 우크라이나(2016-12): 전력 프로토콜 이름을 단 DLL·EXE를 쓰고, 실행 파일을 .txt로 옮긴 뒤 이름을 바꿈 (INC-003, ATT&amp;CK C0025)
+- [실제 사고] 2025 폴란드(2025-12): 방화벽 설정에 이미 있는 기관명을 흉내 낸 규칙을 만들어 탐지를 피함 (INC-008, ATT&amp;CK C0063)</t>
+        </is>
+      </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
           <t>T0849</t>
@@ -10869,7 +11439,7 @@
       </c>
       <c r="K52" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L52" s="17" t="inlineStr">
@@ -10983,7 +11553,16 @@
           <t>https://attack.mitre.org/techniques/T0849</t>
         </is>
       </c>
-      <c r="AM52" s="17" t="inlineStr"/>
+      <c r="AM52" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 벤더 소프트웨어의 실행 파일·DLL·서비스 목록과 해시·서명 기준선을 만들어, 같은 이름인데 해시·경로·서명자가 다르면 경보
+- 확장자와 실제 형식이 다른 파일, 기존 것과 철자가 비슷한 새 서비스·계정 확인
+■ 대응
+- 해시·서명자 기준 애플리케이션 허용 목록을 적용하고 벤더 설치 경로의 쓰기 권한을 제한
+- 탈취·폐기된 코드 서명 인증서를 신뢰 목록에서 빼고, 경계 장비 규칙은 변경 관리 기록과 대조</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -11207,12 +11786,24 @@
           <t>운전 모드 변경</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may change the operating mode of a controller to gain additional access to engineering functions such as Program Download.</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr"/>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 운전 모드를 RUN에서 PROGRAM·STOP·REMOTE로 바꿔, 프로그램 다운로드·메모리 쓰기 같은 엔지니어링 기능을 열거나 제어 로직 실행을 멈출 수 있음
+- 키 스위치를 원격 변경이 가능한 위치에 둔 채 운영하는 경우가 흔해 프로토콜 명령만으로 모드가 바뀌고, 모드 변경을 기록·경보하지 않는 장치도 많음</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: PLC·PAC·DCS 제어기와 안전 제어기(SIS)의 운전 모드(RUN·PROGRAM·STOP·REMOTE)와 물리 키 스위치 (L1)
+- 수법: 공격 도구에 내장된 정지·실행 명령(Triton의 TriStation halt·run, PLC-Blaster의 프로그램 정지 후 재기동), 장치 웹 인터페이스로 모드 변경(INCONTROLLER의 Omron PLC 대상 HTTP 연결)
+- 모드 변경 뒤에는 제어 프로그램 다운로드(OTC-LM-01.0)·제어기 태스크 변조(OTC-EX-02)·시스템 펌웨어 변조(OTC-PE-04.1)가 이어지고, STOP 상태로 두면 장치 정지(OTC-IR-04)와 같은 결과가 남 — 현재 모드는 운전 모드 탐지(OTC-CO-08)로 먼저 확인
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 키 스위치가 PROGRAM 위치에 있던 Tricon 안전 제어기의 프로그램을 TriStation 프로토콜로 멈추고 다시 실행하며 공격 코드를 심음 (INC-004, ATT&amp;CK S1009)
+- [위협인텔] PIPEDREAM(2022-04): INCONTROLLER가 HTTP로 Omron PLC의 운전 모드를 바꾸는 기능을 갖춘 채 배포 전에 발견 (INC-022, ATT&amp;CK S1045)
+- [실증] PLC-Blaster(2016-03): 대상 PLC의 사용자 프로그램을 멈추고 웜 코드를 복사한 뒤 다시 기동 (INC-024, ATT&amp;CK S1006)</t>
+        </is>
+      </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
           <t>T0858</t>
@@ -11231,7 +11822,7 @@
       <c r="J54" s="17" t="inlineStr"/>
       <c r="K54" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L54" s="17" t="inlineStr">
@@ -11344,7 +11935,16 @@
           <t>https://attack.mitre.org/techniques/T0858</t>
         </is>
       </c>
-      <c r="AM54" s="17" t="inlineStr"/>
+      <c r="AM54" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 운전 모드를 바꾸는 기능 코드(정지·실행·모드 전환)를 OT 네트워크 감시로 탐지하고, 장치 이벤트 로그·진단 버퍼의 모드 변경 기록 수집
+- 키 스위치 위치를 감시 신호로 HMI·SCADA에 올려, PROGRAM·REMOTE 상태가 작업 일정 밖에 나타나거나 오래 유지되면 경보
+■ 대응
+- 정상 운전 중에는 키 스위치를 RUN(잠금)에 두고 키를 관리하며, 모드 변경은 변경 관리 절차로 승인
+- 엔지니어링 프로토콜 접근을 지정 EWS로 제한하고 제어기 접근 암호·인증 기능을 켬</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -11367,12 +11967,24 @@
           <t>호스트 흔적 삭제</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to remove indicators of their presence on a system in an effort to cover their tracks.</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr"/>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 이벤트 로그·악성 파일·저장 프로시저를 지우거나 파일 시각을 바꾸고, 제어기를 원래 상태로 되돌려 침입 흔적을 감출 수 있음
+- OT 장치는 로그 보존 용량이 작고 중앙 수집이 안 된 경우가 많아, 현장에서 지우면 사고 원인 분석 자체가 어려워짐</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: EWS·HMI·SCADA 서버의 Windows 이벤트 로그·파일, 제어기 메모리의 공격 프로그램, 경계 장비 로그 (L1~L3.5)
+- 수법: 공격이 실패하면 제어기를 정상 운전 상태로 되돌리고 안 되면 악성 프로그램을 무효 데이터로 덮어씀(Triton), 이벤트 로그 일괄 삭제(KillDisk), 저장 프로시저 삭제·파일 시각 위조(Stuxnet), 실행 뒤 자기 삭제(BlackEnergy 드로퍼·LockerGoga)
+- 통합: Enterprise 흔적 삭제(T1070·.004·.006) — 데이터 파괴(OTC-IR-02)가 복구 방해를 노린다면 이 기법은 흔적 은닉이 목적
+■ 실제 사례
+- [실제 사고] Triton(2017-08): 공격 코드가 실패하면 제어기를 이전 상태로 되돌리고, 정해진 시간 안에 회복되지 않으면 악성 프로그램을 무효 데이터로 덮어씀 (INC-004, ATT&amp;CK C0030)
+- [실제 사고] Stuxnet(2010-06): 악성 코드를 담았던 SQL 저장 프로시저를 지우고 드라이버 파일 시각을 정상 파일과 맞춤 (INC-009, ATT&amp;CK S0603)
+- [실제 사고] 2015 우크라이나(2015-12): 매크로가 떨군 실행 파일이 BlackEnergy 구성요소를 내려놓은 뒤 자신을 삭제 (INC-002, ATT&amp;CK C0028)</t>
+        </is>
+      </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
           <t>T0872</t>
@@ -11395,7 +12007,7 @@
       </c>
       <c r="K55" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L55" s="17" t="inlineStr">
@@ -11524,7 +12136,16 @@
           <t>https://attack.mitre.org/techniques/T0872</t>
         </is>
       </c>
-      <c r="AM55" s="17" t="inlineStr"/>
+      <c r="AM55" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 호스트·장비 로그를 실시간으로 중앙 수집해 현장 삭제와 무관하게 보존하고, 로그 삭제 이벤트(Windows 1102·104)와 로그 공백을 경보
+- 제어기 프로그램·메모리 변경과 예기치 않은 리셋·재시작을 진단 정보로 확인
+■ 대응
+- 로그 저장소 권한을 분리하고 장치 로그를 원격 syslog로 보내며, 보존 기간을 사고 조사 요건에 맞춤
+- 사고 대응 계획에 OT 포렌식 절차(메모리·프로그램 확보 순서)를 넣고 승인된 프로그램 기준본을 보관</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -11547,12 +12168,24 @@
           <t>시스템 바이너리 대리 실행</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may bypass process and/or signature-based defenses by proxying execution of malicious content with signed, or otherwise trusted, binaries.</t>
-        </is>
-      </c>
-      <c r="F56" s="17" t="inlineStr"/>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영체제·SCADA 소프트웨어에 들어 있는 신뢰된 바이너리(rundll32·msiexec·SCADA 명령 도구)로 악성 코드나 명령을 대신 실행시켜, 실행 파일 기반 방어를 우회할 수 있음
+- 실행 주체가 마이크로소프트·벤더 서명 프로그램이라 허용 목록과 서명 검사를 통과하고, SCADA 도구를 쓰면 제어 명령까지 정상 경로로 나감</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Windows 기반 EWS·HMI·SCADA 서버·히스토리언과 설치된 SCADA 애플리케이션 바이너리 (L2~L3)
+- 수법: MicroSCADA scilc.exe에 공격자가 만든 명령 목록 파일을 넘겨 변전소로 비인가 명령 전송(2022 우크라이나), rundll32로 악성 DLL 실행(BlackEnergy·Havex·NotPetya·Bad Rabbit), msiexec로 악성 설치 패키지 실행(Duqu)
+- 통합: Enterprise Msiexec(T1218.007)·Rundll32(T1218.011) — SCADA 바이너리를 통한 명령 전송은 비인가 명령 메시지(OTC-IP-03.1)로 이어짐
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): 'scilc.exe -do pack\scil\s1.txt'로 MicroSCADA가 미리 준비된 SCADA 명령을 원격 변전소로 보내게 함 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2015 우크라이나(2015-12): 백도어가 rundll32.exe로 공급받은 DLL을 실행 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] NotPetya(2017-06): PsExec·wmic로 원격 시스템에 접근한 뒤 rundll32.exe로 자신을 설치 (INC-016, ATT&amp;CK S0368)</t>
+        </is>
+      </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
           <t>T0894</t>
@@ -11575,7 +12208,7 @@
       </c>
       <c r="K56" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L56" s="17" t="inlineStr">
@@ -11682,7 +12315,16 @@
           <t>https://attack.mitre.org/techniques/T0894</t>
         </is>
       </c>
-      <c r="AM56" s="17" t="inlineStr"/>
+      <c r="AM56" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- rundll32·msiexec가 사용자 폴더·임시 경로의 DLL·패키지를 실행하거나 외부 연결을 만들면 EDR로 경보
+- SCADA 명령 도구의 실행 인자·호출 주체를 기록하고, 운영 절차에 없는 명령 파일 실행을 경보
+■ 대응
+- OT 호스트에서 쓰지 않는 시스템 바이너리 실행을 허용 목록으로 제한하고, SCADA 명령 도구는 지정 계정·경로에서만 실행되게 함
+- SCADA 소프트웨어의 스크립트·명령 실행 권한을 역할별로 나누고 실행 기록을 남김</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -12086,12 +12728,23 @@
           <t>그룹 정책 변조</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify Group Policy Objects (GPOs) to subvert the intended discretionary access controls for a domain, usually with the intention of escalating privileges on the domain.</t>
-        </is>
-      </c>
-      <c r="F59" s="17" t="inlineStr"/>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 도메인 관리자 권한으로 그룹 정책 개체(GPO)를 바꿔, 도메인에 속한 OT 호스트 전체에 악성 코드 실행·보안 설정 해제를 한 번에 내릴 수 있음
+- 정상 관리 기능으로 많은 호스트에 동시에 적용돼 파괴형 공격이 매우 빠르게 퍼지고, OT 호스트가 IT 도메인에 묶여 있으면 IT 침해가 그대로 OT로 번짐</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Active Directory 도메인에 가입한 EWS·HMI·SCADA 서버·히스토리언과 OT 도메인 컨트롤러 (L2~L3)
+- 수법: GPO에 예약 작업·스크립트를 넣어 와이퍼를 배포·실행(2022 우크라이나·2025 폴란드), 보안 도구·방화벽 설정 해제
+- 권한 상승(OTC-PV-04.1)·방어 회피(OTC-EV-08.1) 전술에 같은 기법으로 나타남 — 예약 작업은 OTC-EX-11, 스크립트 실행은 OTC-EX-05
+■ 실제 사례
+- [실제 사고] 2022 우크라이나(2022-10): 그룹 정책 개체로 피해 기관 IT 환경에 CaddyWiper를 배포·실행 (INC-006, ATT&amp;CK C0034)
+- [실제 사고] 2025 폴란드(2025-12): 그룹 정책 개체로 네트워크 공유에 둔 와이퍼를 피해 장치들에 배포 (INC-008, ATT&amp;CK C0063)</t>
+        </is>
+      </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
           <t>T1484.001</t>
@@ -12110,7 +12763,7 @@
       <c r="J59" s="17" t="inlineStr"/>
       <c r="K59" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L59" s="17" t="inlineStr">
@@ -12213,7 +12866,16 @@
           <t>https://attack.mitre.org/techniques/T1484/001</t>
         </is>
       </c>
-      <c r="AM59" s="17" t="inlineStr"/>
+      <c r="AM59" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- GPO 생성·변경 이벤트(디렉터리 서비스 변경 감사 5136 등)와 SYSVOL의 새 스크립트·예약 작업 파일을 감시하고 근무 외 변경을 경보
+- GPO 변경 직후 다수 호스트에서 같은 프로세스가 동시에 생기는 패턴을 상관 분석
+■ 대응
+- OT를 별도 도메인으로 운영해 IT 도메인과의 신뢰 관계를 최소화하고, GPO 편집 권한을 소수 계정으로 제한
+- 도메인 관리자 계정을 특권 접근 관리·다중 인증으로 보호하고, GPO 백업으로 변경 시 즉시 복원</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
@@ -12236,12 +12898,24 @@
           <t>보안 도구 무력화</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may disable, degrade, or tamper with security tools or applications (e.g., endpoint detection and response (EDR) tools, intrusion detection systems (IDS), antivirus, logging agents, sensors, etc.) to impair or reduce visibility of defensive capabi…</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="inlineStr"/>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 백신·EDR·로그 수집 에이전트·OT 보안 센서를 멈추거나 설정을 바꿔, 이후 행위가 기록·탐지되지 않게 할 수 있음
+- OT 호스트의 보안 도구는 운영 영향을 우려한 예외 설정이 많고 중앙 관리가 약해, 꺼져도 오랫동안 알아채지 못하는 경우가 많음</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: EWS·HMI·SCADA 서버의 백신·EDR·이벤트 로깅, OT 네트워크 감시 센서, 보안 관리 서버 (L2~L3)
+- 수법: 보안·관리 소프트웨어 프로세스 종료(EKANS), 백신 강제 종료 후 랜섬웨어 실행(LockerGoga), 이벤트 로깅 해제(2016 우크라이나), 인터넷 보안 설정 하향(2015 우크라이나)
+- 구분: 운영 프로세스·서비스 강제 종료는 서비스 중지(OTC-IR-09), 경계 장비 보안 설정 변경은 OTC-EV-10.1
+■ 실제 사례
+- [실제 사고] 2016 우크라이나(2016-12): 침해한 시스템의 이벤트 로깅을 꺼 흔적을 줄임 (INC-003, ATT&amp;CK C0025)
+- [실제 사고] 혼다 공장(2020-06): EKANS가 보안·관리 소프트웨어 프로세스를 멈추고 공장 시스템을 암호화해 일부 생산이 중단 (INC-020, ATT&amp;CK S0605)
+- [실제 사고] 노르스크 하이드로(2019-03): 백신을 'task kill'로 종료한 직후 LockerGoga를 설치 (INC-019, ATT&amp;CK S0372)</t>
+        </is>
+      </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
           <t>T1685</t>
@@ -12264,7 +12938,7 @@
       </c>
       <c r="K60" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L60" s="17" t="inlineStr">
@@ -12370,7 +13044,16 @@
           <t>https://attack.mitre.org/techniques/T1685</t>
         </is>
       </c>
-      <c r="AM60" s="17" t="inlineStr"/>
+      <c r="AM60" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 에이전트의 상태 신호가 끊기거나 서비스가 멈추면 중앙 관리 콘솔에서 경보하고, 로깅 정책 변경 이벤트를 수집
+- OT 네트워크 감시 센서의 수신 트래픽이 갑자기 줄거나 끊기면 확인
+■ 대응
+- 보안 도구의 변조 방지 기능을 켜고, 중지·제거 권한을 별도 관리자 계정으로 제한
+- 보안 도구 예외 설정을 정기 검토하고, 로깅 설정은 그룹 정책·구성 관리로 강제</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
@@ -12393,12 +13076,22 @@
           <t>경계 장비 보안 설정 변조</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may disable network device-based firewall mechanisms entirely or add, delete, or modify particular rules in order to bypass controls limiting network usage.</t>
-        </is>
-      </c>
-      <c r="F61" s="17" t="inlineStr"/>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 경계 방화벽·VPN 장비의 접근 규칙·보안 설정·다중 인증 설정을 바꾸거나 트래픽 로깅을 꺼, 막혀 있던 통신을 열고 자신의 접근을 감출 수 있음
+- 경계 장비 하나의 설정이 IT·OT 분리를 좌우하므로 규칙 하나만 바뀌어도 망 분리가 무력화되고, 장비 로그를 끄면 이후 행위가 남지 않음</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: IT/OT 경계 방화벽, 원격 접속 VPN, 산업용 방화벽·라우터의 ACL·보안 정책·인증 설정 (L3.5)
+- 수법: 장비 CLI로 보안 설정 변경과 트래픽 로깅 해제, 다중 인증 설정 해제(2025 폴란드) — 기존 기관명을 흉내 낸 규칙 이름으로 위장(OTC-EV-02)
+- 통합: Enterprise 다중 인증 설정 변조(T1556.006) — 장비 접근은 공개 애플리케이션 취약점 악용(OTC-IA-02)·유효 계정 악용(OTC-PE-01)으로 확보
+■ 실제 사례
+- [실제 사고] 2025 폴란드(2025-12): FortiGate CLI로 보안 설정을 바꾸고 네트워크 트래픽 로깅을 끄며, 2단계 인증 설정을 해제 (INC-008, ATT&amp;CK C0063)</t>
+        </is>
+      </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
           <t>T1686.002</t>
@@ -12421,7 +13114,7 @@
       </c>
       <c r="K61" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L61" s="17" t="inlineStr">
@@ -12522,7 +13215,16 @@
           <t>https://attack.mitre.org/techniques/T1686/002</t>
         </is>
       </c>
-      <c r="AM61" s="17" t="inlineStr"/>
+      <c r="AM61" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 경계 장비 설정을 정기 백업해 승인 기준본과 비교하고, 규칙·인증·로깅 설정 변경 이벤트를 외부 로그 서버로 보내 경보
+- 장비 로그 전송이 갑자기 끊기거나 줄면 로깅 해제 징후로 확인
+■ 대응
+- 경계 장비 관리 접속을 관리망·다중 인증으로 제한하고, 설정 변경은 변경 관리 승인 뒤 수행
+- 장비 펌웨어를 최신으로 유지하고(KEV 등재 취약점 우선), 관리 계정을 개인별로 나눠 변경 이력을 추적</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
@@ -14613,12 +15315,25 @@
           <t>유효 계정 악용</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may steal the credentials of a specific user or service account using credential access techniques.</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr"/>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취하거나 새로 만든 유효 계정(도메인·로컬·서비스·장치 계정)으로 VPN·원격 서비스·제어 장치에 로그인해, 정상 사용자 권한으로 OT 환경에 머물고 이동할 수 있음
+- 인증을 정상 통과하므로 접근 통제와 다수 탐지 수단을 그대로 지나치며, 퇴사자·휴면·공용 계정 관리가 허술한 OT 환경에서 반복적으로 악용됨</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: IT·OT 도메인 계정, VPN·원격 접속 계정, EWS·HMI 로컬 계정, SQL 서버 계정, RTU·보호 계전기·시리얼 서버 같은 현장 장치 계정, 카메라 클라우드 관리 계정 (L1~L3.5·IoT)
+- 수법: 기업망에서 모은 자격증명으로 VPN·이중 연결(dual-homed) 시스템을 거쳐 제어망 진입(2015·2016 우크라이나), RDP 점프 박스 경유(Triton), 새 관리자·도메인 계정 생성, 해시 재사용 — 계정 탈취 수단은 OTC-LM-07·LM-08·LM-09
+- 통합: Enterprise 유효 계정(T1078·.002~.004)·계정 조작(T1098)·계정 생성(T1136·.001·.002)·해시 전달(T1550.002) — 기본·하드코딩 자격증명은 OTC-PE-05.1·05.2
+- 지속(OTC-PE-01)·측면 이동(OTC-LM-02) 전술에 같은 기법으로 나타나며, 퇴사자에게 남은 원격 접속 권한이 내부자 조작으로 이어진 수도 사고가 반복됨(INC-042, INC-043)
+■ 실제 사례
+- [실제 사고] 2015 우크라이나(2015-12): 기업망에서 탈취한 계정으로 VPN과 이중 연결 시스템을 거쳐 제어망에 들어가고, 권한 있는 도메인 계정을 새로 만들어 머묾 (INC-002, ATT&amp;CK C0028)
+- [실제 사고] 2025 폴란드(2025-12): 유효 계정으로 Hitachi·Mikronika RTU, 보호 계전기, Mikronika HMI, Moxa NPort에 접근하고, 권한 계정으로 FortiGate VPN을 거쳐 하위 망으로 이동 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] 미국 베이 지역 정수장(2021-01): 퇴사한 직원의 TeamViewer 계정으로 제어 시스템에 접속해 정수 처리 프로그램을 삭제 (INC-042)</t>
+        </is>
+      </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
           <t>T0859</t>
@@ -14641,7 +15356,7 @@
       </c>
       <c r="K74" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L74" s="17" t="inlineStr">
@@ -14789,7 +15504,16 @@
           <t>https://attack.mitre.org/techniques/T0859</t>
         </is>
       </c>
-      <c r="AM74" s="17" t="inlineStr"/>
+      <c r="AM74" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 계정의 로그인 시간·출발지·대상 장치를 기준선과 비교하고, 휴면·퇴사자·서비스 계정의 대화형 로그인과 새 관리자 계정 생성을 경보
+- 현장 장치(RTU·계전기·시리얼 서버) 로그인 기록을 VPN·점프 호스트 세션과 상관 분석해 승인된 원격 세션 없이 일어난 장치 접근 확인
+■ 대응
+- OT 계정·도메인을 IT와 분리하고, 원격·특권 접근에 다중 인증과 승인 기반 일시 권한(JIT)을 적용
+- 퇴사·계약 종료 때 원격 접속 계정을 즉시 폐기하고, 공용 계정을 개인 계정으로 바꾸며 계정 목록을 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
@@ -15388,12 +16112,23 @@
           <t>취약한 자격증명 (일반·상위기법)</t>
         </is>
       </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may target insecure credentials as a means to persist on a system or device or move laterally from one system or device to another.</t>
-        </is>
-      </c>
-      <c r="F78" s="17" t="inlineStr"/>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치·소프트웨어에 미리 설정돼 공개된 기본 자격증명이나 펌웨어에 박힌 하드코딩 자격증명, 허술하게 저장된 자격증명을 써서, 계정을 탈취하지 않고도 제어 장치·서버에 로그인하고 머물거나 이동할 수 있음
+- 장치 교체 주기가 길고 일부 자격증명은 사용자가 바꿀 수 없어 노출 상태가 오래 이어지며, 로그인 자체는 정상이라 탐지가 어려움</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: PLC·HMI·RTU·IED·산업용 스위치·시리얼 서버·IoT 기기의 웹·텔넷·SSH·엔지니어링 접속과 SCADA·히스토리언 서버의 DB 계정 (L1~L3·IoT)
+- 하위 기법: 기본 자격증명(OTC-PE-05.1)·하드코딩 자격증명(OTC-PE-05.2) — 이 행은 자격증명을 평문·되돌릴 수 있는 형태로 저장하거나 약한 암호를 허용하는 결함처럼 하위 기법으로 나누기 어려운 근거를 모음
+- CISA ICS 권고에서 보호되지 않은 자격증명·약한 암호 정책(CWE-522·256·257·260·521) 199건, 2025년 이후 48건
+- 지속(OTC-PE-05.0)·측면 이동(OTC-LM-06.0) 전술에 같은 기법으로 나타나며, 실제 사고는 하위 기법에서 집계
+■ 실제 사례
+- [공개 취약점] CISA ICS 권고: 설정 파일·백업·통신에 자격증명이 평문이나 약한 형태로 남는 취약점 다수 — 장치 설정을 얻은 공격자가 그대로 로그인할 수 있음</t>
+        </is>
+      </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
           <t>T1694</t>
@@ -15412,7 +16147,7 @@
       <c r="J78" s="17" t="inlineStr"/>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L78" s="17" t="inlineStr">
@@ -15535,7 +16270,16 @@
           <t>https://attack.mitre.org/techniques/T1694</t>
         </is>
       </c>
-      <c r="AM78" s="17" t="inlineStr"/>
+      <c r="AM78" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 평문 인증 프로토콜(텔넷·FTP·HTTP)의 로그인과 알려진 기본 계정 사용을 OT 네트워크 감시로 탐지하고 장치 로그인 기록 수집
+- 자산 점검 때 자격증명 관련 CISA ICS·벤더 권고 해당 여부를 자산 목록과 대조
+■ 대응
+- 설치·인수 때 기본 자격증명을 바꾸고 장치별 고유 암호를 관리하며, 바꿀 수 없는 자격증명은 네트워크 분리·허용 목록으로 보완
+- 자격증명 저장 결함을 패치하고 암호화 통신(HTTPS·SSH)을 적용하며, 쓰지 않는 텔넷·FTP 서비스를 끔</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
@@ -15558,12 +16302,25 @@
           <t>기본 자격증명</t>
         </is>
       </c>
-      <c r="E79" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage manufacturer or supplier set default credentials on control system devices.</t>
-        </is>
-      </c>
-      <c r="F79" s="17" t="inlineStr"/>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제조사가 출하 때 설정해 매뉴얼·인터넷에 공개된 기본 계정·암호로 PLC·HMI·RTU·IoT 기기에 로그인해, 관리자 권한을 바로 얻고 설정·화면·프로그램을 바꿀 수 있음
+- 검색 엔진으로 노출 장치를 찾아 기본 암호를 넣는 것만으로 대규모 공격이 가능해, 숙련도가 낮은 핵티비스트와 IoT 봇넷이 가장 많이 쓰는 경로임</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: Unitronics Vision 같은 일체형 PLC·HMI, RTU·보호 계전기·시리얼 서버, VNC 기반 HMI, IP 카메라·DVR 등 IoT 기기 (L1~L2·IoT)
+- 인터넷 노출 장치 악용(OTC-IA-11)과 결합해 화면 변조·설정값 조작·관리자 암호 변경(OTC-IR-10)으로 이어지고, IoT 기기는 봇넷 편입(OTC-IM-14.1)이나 기기 파괴로 이어짐
+- CISA ICS 권고에서 기본 자격증명·안전하지 않은 기본 설정(CWE-1392·1393·1188) 48건, 2025년 이후 27건 — KEV: Unitronics Vision 기본 암호(CVE-2023-6448)
+- 통합: Enterprise 기본 계정(T1078.001)
+■ 실제 사례
+- [실제 사고] Unitronics 화면 변조(2023-11): CyberAv3ngers가 인터넷에 노출된 Unitronics PLC·HMI에 기본 암호로 접속해 화면을 바꿨고, 알리퀴파 수도국 가압장은 수동 운전으로 전환 (INC-005, ATT&amp;CK C0031)
+- [실제 사고] 2025 폴란드(2025-12): 기본 자격증명으로 Hitachi·Mikronika RTU, 보호 계전기, Moxa NPort 등에 접근 (INC-008, ATT&amp;CK C0063)
+- [실제 사고] Mirai(2016-10): 텔넷 기본 계정으로 IP 카메라·DVR 수십만 대를 감염시켜 대규모 DDoS 봇넷을 구성 (INC-032)</t>
+        </is>
+      </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
           <t>T1694.001</t>
@@ -15586,7 +16343,7 @@
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L79" s="17" t="inlineStr">
@@ -15722,7 +16479,16 @@
           <t>https://attack.mitre.org/techniques/T1694/001</t>
         </is>
       </c>
-      <c r="AM79" s="17" t="inlineStr"/>
+      <c r="AM79" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 장치 로그인 기록과 OT 네트워크 감시로 기본 계정 이름의 로그인과 반복 로그인 시도를 탐지
+- 외부 공격 표면 점검과 내부 자산 점검으로 기본 암호가 남은 장치를 정기 확인
+■ 대응
+- 설치·인수 시험 항목에 기본 암호 변경을 넣고, 장치별 고유 암호를 암호 관리 도구로 관리
+- 첫 사용 때 암호 변경을 강제하는 제품을 우선 도입하고 장치의 인터넷 노출을 없앰</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
@@ -15745,12 +16511,24 @@
           <t>하드코딩 자격증명</t>
         </is>
       </c>
-      <c r="E80" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage credentials that are hardcoded in software or firmware to gain an unauthorized interactive user session to an asset.</t>
-        </is>
-      </c>
-      <c r="F80" s="17" t="inlineStr"/>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 소프트웨어·펌웨어에 박혀 있는 계정·암호·암호키를 찾아내, 같은 제품을 쓰는 모든 현장의 장치에 로그인하거나 엔지니어링 인증을 우회할 수 있음
+- 사용자가 바꾸거나 끌 수 없는 경우가 많아 패치 전까지 노출이 이어지고, 한 번 공개되면 같은 제품군 전체가 동시에 위험해짐</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>■ OT 관점
+- 대상: SCADA·HMI 소프트웨어의 DB 계정, PLC·제어기의 엔지니어링 인증 키, 임베디드 장치의 서비스·유지보수 계정과 인증서·API 토큰 (L1~L2)
+- 수법: WinCC DB 서버의 하드코딩 암호로 인근 시스템 감염(Stuxnet), Omron PLC의 하드코딩 자격증명으로 로그인(INCONTROLLER, CVE-2022-34151)
+- CISA ICS 권고에서 하드코딩 자격증명·키(CWE-798·321·259) 270건, 2025년 이후 69건 — KEV: Rockwell Logix 제어기 인증 키 노출(CVE-2021-22681)
+■ 실제 사례
+- [실제 사고] Stuxnet(2010-06): WinCC 소프트웨어 DB 서버에 하드코딩된 암호로 인근 시스템에 퍼짐 (INC-009, ATT&amp;CK S0603)
+- [위협인텔] PIPEDREAM(2022-04): INCONTROLLER가 Omron PLC의 하드코딩 자격증명(CVE-2022-34151)으로 로그인하는 기능을 갖춘 채 발견 (INC-022, ATT&amp;CK S1045)
+- [공개 취약점] Rockwell Logix(CVE-2021-22681): 엔지니어링 소프트웨어와 제어기 사이 인증 키가 노출돼 원격에서 제어기 인증을 우회 — KEV 등재</t>
+        </is>
+      </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
           <t>T1694.002</t>
@@ -15769,7 +16547,7 @@
       <c r="J80" s="17" t="inlineStr"/>
       <c r="K80" s="17" t="inlineStr">
         <is>
-          <t>작성 예정</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="L80" s="17" t="inlineStr">
@@ -15872,7 +16650,16 @@
           <t>https://attack.mitre.org/techniques/T1694/002</t>
         </is>
       </c>
-      <c r="AM80" s="17" t="inlineStr"/>
+      <c r="AM80" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CISA ICS·벤더 권고의 하드코딩 자격증명 해당 제품을 자산 목록과 대조하고, 해당 계정·키를 쓰는 로그인을 OT 네트워크 감시 규칙으로 탐지
+- 엔지니어링 프로토콜 세션의 발신지를 지정 EWS 목록과 비교
+■ 대응
+- 벤더 패치·펌웨어 업데이트로 하드코딩 자격증명을 없애고, 패치 전에는 장치 접근을 허용 목록·네트워크 분리로 제한
+- 조달 요건에 하드코딩 자격증명 금지와 자격증명 변경 기능을 명시</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="17" t="inlineStr">
@@ -27411,9 +28198,10 @@
           <t>명령줄 인터페이스</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may utilize command-line interfaces (CLIs) to interact with systems and execute commands.</t>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 EWS·HMI·SCADA 서버의 명령 셸과 RTU·방화벽의 장비 CLI로 명령을 실행해, 도구를 설치하고 설정을 바꾸거나 제어 소프트웨어를 직접 호출할 수 있음
+- 운영·유지보수에 늘 쓰는 인터페이스라 실행 자체가 정상 행위와 같고, 내장 명령만 쓰면 별도 악성 파일 없이도 공격이 진행됨</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -27457,7 +28245,16 @@
       <c r="N20" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="O20" s="17" t="inlineStr"/>
+      <c r="O20" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 호스트에서 명령 셸·PowerShell 실행과 인자를 기록(명령줄 감사)하고, 제어 소프트웨어 명령 도구(scilc.exe 등)를 평소와 다른 부모 프로세스·계정이 호출하면 경보
+- RTU·네트워크 장비의 SSH 접속과 CLI 명령 이력(AAA 기록)을 중앙 수집해 승인되지 않은 명령·설정 변경 확인
+■ 대응
+- OT 호스트에서 쓰지 않는 셸·관리 도구를 제거하거나 애플리케이션 허용 목록으로 막고, 관리자 셸은 점프 호스트·지정 계정에서만 사용
+- 장치·장비 관리 인터페이스는 관리망에서만 열고 root 직접 로그인을 막으며, 명령 권한을 역할별로 나눔</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
@@ -27480,9 +28277,10 @@
           <t>제어기 태스크 변조</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify the tasking of a controller to allow for the execution of their own programs.</t>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 태스크 설정(태스크와 프로그램 조직 단위의 연결·주기·우선순위)을 바꾸거나 새 태스크를 넣어, 자신이 심은 코드를 매 스캔 주기나 특정 조건에서 실행시킬 수 있음
+- 기존 로직은 그대로 두고 실행 흐름만 바꿀 수 있어 로직 비교만으로는 놓치기 쉽고, 태스크 변경을 경보하지 않는 장치가 많음</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -27526,7 +28324,16 @@
       <c r="N21" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O21" s="17" t="inlineStr"/>
+      <c r="O21" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기의 태스크 구성(태스크 목록·주기·우선순위·연결 블록)과 블록 목록을 승인된 기준 프로젝트와 정기 비교하고, 진단 버퍼·변경 경보를 수집
+- 다운로드·온라인 편집 같은 엔지니어링 기능 코드가 지정 EWS 밖에서 오거나 작업 일정 밖에 발생하면 OT 네트워크 감시로 경보
+■ 대응
+- 제어기 접근 보호(암호·보호 레벨)를 켜고 운전 중에는 키 스위치를 RUN에 두어 원격 프로그램 변경을 막음
+- 변경 관리로 승인된 변경만 반영하고, 코드 서명·무결성 검증을 지원하는 제어기를 우선 도입</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
@@ -27549,9 +28356,10 @@
           <t>그래픽 사용자 인터페이스 조작</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to gain access to a machine via a Graphical User Interface (GUI) to enhance execution capabilities.</t>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 원격 데스크톱·VNC·원격 지원 도구로 HMI·EWS 화면을 넘겨받아, 운영자와 같은 방식으로 클릭해 차단기 개방·설정 변경 같은 제어 기능을 실행할 수 있음
+- 운영자 화면에서 이뤄지는 정상 조작이라 명령 자체로는 구분되지 않고, HMI가 공정 배치를 보여주므로 깊은 공정 지식 없이도 의미 있는 조작이 가능함</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -27595,7 +28403,16 @@
       <c r="N22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O22" s="17" t="inlineStr"/>
+      <c r="O22" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- HMI·EWS로 들어오는 원격 화면 세션(RDP·VNC·원격 지원 도구)의 생성·출발지·시간대를 기록하고, 운영자 콘솔이 아닌 세션에서 일어난 제어 조작을 경보
+- HMI 운영자 조작 기록을 로그인 세션과 대조해 근무하지 않는 계정이나 원격 세션의 조작 확인
+■ 대응
+- HMI·EWS 원격 화면 접속은 점프 호스트·다중 인증을 거친 지정 경로로만 허용하고, 쓰지 않는 원격 지원 도구 제거
+- 중요 제어 조작은 확인 창 외에 2인 승인·현장 확인을 거치게 하고, 원격 세션은 녹화·감독</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
@@ -27618,9 +28435,10 @@
           <t>네이티브 API 악용</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may directly interact with the native OS application programming interface (API) to access system functions.</t>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영체제나 제어기 펌웨어가 제공하는 저수준 API(시스템 호출·시스템 함수 블록)를 직접 불러, 메모리·프로세스·통신 같은 하위 기능을 정상 도구 없이 다룰 수 있음
+- 제어기의 시스템 함수 블록은 정상 로직에도 쓰여 악용 호출이 구분되지 않고, 장치 내부의 API 호출을 기록·감시할 수단이 거의 없음</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
@@ -27664,7 +28482,16 @@
       <c r="N23" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="O23" s="17" t="inlineStr"/>
+      <c r="O23" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기 프로그램의 통신·메모리 관련 시스템 함수 사용을 기준 프로젝트와 비교하고, PLC가 평소 없던 TCP 연결을 만들면 OT 네트워크 감시로 경보
+- HMI·EWS에서는 EDR로 프로세스 주입·디스크 직접 접근 같은 의심 API 호출 패턴 탐지(OT 벤더 호환성 확인 후 적용)
+■ 대응
+- 제어기 접근 보호로 프로그램 변경을 막고 쓰지 않는 통신 기능(PUT/GET·개방형 통신)을 끔
+- 호스트에는 애플리케이션 허용 목록을 적용해 비인가 실행 파일이 API를 호출할 기회를 줄임</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -27687,9 +28514,10 @@
           <t>스크립트 실행</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may use scripting languages to execute arbitrary code in the form of a pre-written script or in the form of user-supplied code to an interpreter.</t>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 PowerShell·VBScript·배치 파일·Python 같은 스크립트로 공격 도구를 실행하고 작업을 자동화해, 정상 관리 작업처럼 보이게 할 수 있음
+- OT 호스트에도 운영 자동화용 스크립트 환경이 기본으로 깔려 있고, 메모리에서만 실행하거나 난독화하면 파일 기반 검사로 잡기 어려움</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -27733,7 +28561,16 @@
       <c r="N24" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O24" s="17" t="inlineStr"/>
+      <c r="O24" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 호스트에도 PowerShell 스크립트 블록 로깅과 명령줄 감사를 켜고, wscript·cscript·powershell이 제어 소프트웨어 명령 도구를 부르는 프로세스 체인을 경보
+- 그룹 정책·예약 작업으로 새로 배포된 스크립트 파일과 WMI·PsExec를 통한 원격 스크립트 실행 감시
+■ 대응
+- OT 호스트에서 쓰지 않는 스크립트 엔진을 막고, PowerShell 제한 언어 모드와 서명된 스크립트만 실행하도록 설정
+- 문서 매크로를 기본 차단하고, 운영 자동화 스크립트는 승인된 저장소에서만 배포</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
@@ -27756,9 +28593,10 @@
           <t>운전 모드 변경</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may change the operating mode of a controller to gain additional access to engineering functions such as Program Download.</t>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 운전 모드를 RUN에서 PROGRAM·STOP·REMOTE로 바꿔, 프로그램 다운로드·메모리 쓰기 같은 엔지니어링 기능을 열거나 제어 로직 실행을 멈출 수 있음
+- 키 스위치를 원격 변경이 가능한 위치에 둔 채 운영하는 경우가 흔해 프로토콜 명령만으로 모드가 바뀌고, 모드 변경을 기록·경보하지 않는 장치도 많음</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -27802,7 +28640,16 @@
       <c r="N25" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O25" s="17" t="inlineStr"/>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 운전 모드를 바꾸는 기능 코드(정지·실행·모드 전환)를 OT 네트워크 감시로 탐지하고, 장치 이벤트 로그·진단 버퍼의 모드 변경 기록 수집
+- 키 스위치 위치를 감시 신호로 HMI·SCADA에 올려, PROGRAM·REMOTE 상태가 작업 일정 밖에 나타나거나 오래 유지되면 경보
+■ 대응
+- 정상 운전 중에는 키 스위치를 RUN(잠금)에 두고 키를 관리하며, 모드 변경은 변경 관리 절차로 승인
+- 엔지니어링 프로토콜 접근을 지정 EWS로 제한하고 제어기 접근 암호·인증 기능을 켬</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -27825,9 +28672,10 @@
           <t>사용자 실행 유도</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may rely on a targeted organizations user interaction for the execution of malicious code.</t>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영자·엔지니어가 첨부파일·설치 파일·프로젝트 파일을 직접 열거나 실행하게 만들어, 사용자 권한으로 OT 단말에서 악성 코드를 실행시킬 수 있음
+- 엔지니어링 업무는 벤더 설치 파일·프로젝트 파일을 일상적으로 주고받아 위장이 쉽고, 파일을 여는 행위 자체가 정상 업무라 차단 기준을 세우기 어려움</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -27871,7 +28719,16 @@
       <c r="N26" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="O26" s="17" t="inlineStr"/>
+      <c r="O26" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- Office·PDF 뷰어·압축 프로그램·엔지니어링 소프트웨어가 스크립트 엔진·명령 셸 같은 자식 프로세스를 만들면 EDR로 경보
+- 외부에서 들어온 설치 파일·프로젝트 파일의 출처·해시를 기록하고 벤더 공식 배포본과 대조
+■ 대응
+- OT 단말에서 매크로와 외부 실행 파일을 기본 차단하고, 벤더 소프트웨어는 서명·해시를 확인한 승인 저장소에서만 설치
+- 엔지니어링 소프트웨어를 최신으로 유지하고(KEV·CISA 권고 우선), 출처가 불분명한 프로젝트 파일은 격리 환경에서 먼저 열기</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -27894,9 +28751,10 @@
           <t>API 경유 실행</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to leverage Application Program Interfaces (APIs) used for communication between control software and the hardware.</t>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어 소프트웨어가 장치와 통신할 때 쓰는 API(엔지니어링 프로토콜 함수·벤더 라이브러리)를 호출해, 프로그램 다운로드·메모리 쓰기·장치 설정 같은 기능을 엔지니어링 도구 없이 실행할 수 있음
+- 장치 입장에서는 정상 엔지니어링 요청과 같고, 역분석한 프로토콜이나 공개된 벤더 라이브러리만 있으면 재현할 수 있음</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
@@ -27940,7 +28798,16 @@
       <c r="N27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="17" t="inlineStr"/>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 엔지니어링 프로토콜의 프로그램 다운로드·메모리 쓰기 함수 호출을 OT 네트워크 감시로 탐지하고, 지정 EWS 밖 발신지나 작업 일정 밖 호출을 경보
+- 장치 감사 로그(지원 시)를 엔지니어링 소프트웨어 작업 기록과 대조해 도구 밖에서 이뤄진 호출 확인
+■ 대응
+- 엔지니어링 기능에 인증과 역할별 권한을 적용하고 지정 EWS에서만 허용
+- 키 스위치·접근 보호로 운전 중 프로그래밍 API 사용을 막음</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -27963,9 +28830,10 @@
           <t>후킹</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may hook into application programming interface (API) functions used by processes to redirect calls for execution and privilege escalation means.</t>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 API 함수 주소·명령 처리기를 가로채거나 정상 프로세스에 코드를 주입해, 정상 기능이 호출될 때 자신의 코드가 먼저 실행되게 할 수 있음
+- 신뢰된 프로세스·펌웨어 안에서 실행돼 실행 주체가 정상으로 보이고, 반환값까지 바꿀 수 있어 감염 사실을 숨기는 데도 쓰임</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -28009,7 +28877,16 @@
       <c r="N28" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O28" s="17" t="inlineStr"/>
+      <c r="O28" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- EDR로 원격 스레드 생성·타 프로세스 메모리 쓰기 같은 주입 패턴과 엔지니어링 소프트웨어에 로드된 미서명 DLL 탐지(OT 벤더 호환성 확인 후 적용)
+- PLC·안전 제어기는 벤더 진단 도구로 펌웨어·메모리 무결성을 점검하고, 평소 쓰지 않는 진단 명령 사용을 OT 네트워크 감시로 확인
+■ 대응
+- 엔지니어링 소프트웨어·HMI 설치 경로의 쓰기 권한을 제한하고 DLL 서명 검증·애플리케이션 허용 목록 적용
+- 제어기 펌웨어 무결성 검증 기능을 켜고, 안전 제어기의 원격 프로그래밍은 운전 중 차단</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
@@ -28032,9 +28909,10 @@
           <t>자동 실행 이미지</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage AutoRun functionality or scripts to execute malicious code.</t>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 이동식 매체나 디스크 이미지(ISO)의 자동 실행 기능을 이용해, 매체를 연결·마운트하는 순간 악성 코드를 실행시킬 수 있음
+- 레거시 운영체제를 오래 쓰는 OT 호스트에는 자동 실행이 켜진 채 남은 경우가 있고, 가상화 환경에서는 하이퍼바이저에서 이미지를 붙이기만 해도 VM 안에서 실행이 일어남</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -28078,7 +28956,16 @@
       <c r="N29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O29" s="17" t="inlineStr"/>
+      <c r="O29" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 새 드라이브 문자·마운트 생성과 이동식 매체·이미지에서 시작된 프로세스를 감시하고, 하이퍼바이저의 가상 매체 연결 이벤트를 수집
+- 하이퍼바이저 관리 콘솔 로그인과 VM 설정 변경을 OT 변경 이력과 대조
+■ 대응
+- OT 호스트의 자동 실행·자동 재생을 정책으로 끄고, 이동식 매체는 검사 키오스크를 거친 뒤 사용
+- 가상화 관리 콘솔을 별도 관리망·다중 인증으로 보호하고 VM 가상 매체 연결 권한을 제한</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -28101,9 +28988,10 @@
           <t>예약 작업</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse task scheduling functionality to facilitate initial or recurring execution of malicious code.</t>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 작업 스케줄러·cron·네트워크 장비 예약 작업에 악성 명령을 등록해, 정한 시각에 실행하거나 재부팅 뒤에도 유지하고, 원격 호스트에 작업을 만들어 확산할 수 있음
+- 운영·백업 자동화용 예약 작업이 많아 새 작업이 눈에 띄지 않고, 파괴형 공격은 여러 호스트에서 같은 시각에 동시 실행되게 맞춰 복구를 어렵게 함</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -28147,7 +29035,16 @@
       <c r="N30" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O30" s="17" t="inlineStr"/>
+      <c r="O30" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 작업 스케줄러의 작업 생성·변경 이벤트와 원격 작업 생성(schtasks /s 등)을 수집하고, 승인된 예약 작업 목록과 정기 비교
+- 그룹 정책 변경과 방화벽·네트워크 장비의 예약 작업 설정 변경을 중앙 로그로 경보
+■ 대응
+- 예약 작업 생성 권한을 관리자 계정으로 제한하고, OT 도메인을 IT 도메인과 분리해 GPO 경유 일괄 배포를 막음
+- OT 호스트·경계 장비의 예약 작업을 변경 관리 대상으로 등록하고 설정 백업과 비교 점검</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
@@ -28170,9 +29067,10 @@
           <t>유효 계정 악용</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may steal the credentials of a specific user or service account using credential access techniques.</t>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취하거나 새로 만든 유효 계정(도메인·로컬·서비스·장치 계정)으로 VPN·원격 서비스·제어 장치에 로그인해, 정상 사용자 권한으로 OT 환경에 머물고 이동할 수 있음
+- 인증을 정상 통과하므로 접근 통제와 다수 탐지 수단을 그대로 지나치며, 퇴사자·휴면·공용 계정 관리가 허술한 OT 환경에서 반복적으로 악용됨</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -28216,7 +29114,16 @@
       <c r="N31" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="O31" s="17" t="inlineStr"/>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 계정의 로그인 시간·출발지·대상 장치를 기준선과 비교하고, 휴면·퇴사자·서비스 계정의 대화형 로그인과 새 관리자 계정 생성을 경보
+- 현장 장치(RTU·계전기·시리얼 서버) 로그인 기록을 VPN·점프 호스트 세션과 상관 분석해 승인된 원격 세션 없이 일어난 장치 접근 확인
+■ 대응
+- OT 계정·도메인을 IT와 분리하고, 원격·특권 접근에 다중 인증과 승인 기반 일시 권한(JIT)을 적용
+- 퇴사·계약 종료 때 원격 접속 계정을 즉시 폐기하고, 공용 계정을 개인 계정으로 바꾸며 계정 목록을 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -28239,9 +29146,10 @@
           <t>지멘스 프로젝트 파일</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may infect Siemens PLC project files (i.e., Step 7, WinCC, etc.) to achieve Execution, Persistence, and Lateral Movement objectives.</t>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 Step 7·WinCC 같은 지멘스 PLC 프로젝트 파일에 악성 코드를 심거나 감염된 프로젝트를 들여와, 엔지니어가 프로젝트를 열 때마다 코드가 실행되게 할 수 있음
+- 프로젝트 파일은 EWS 사이와 협력업체 간에 정상적으로 오가므로 감염이 엔지니어링 업무를 따라 퍼지고, 정상 수정과 함께 바뀌면 변경 분석으로 가려내기 어려움</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
@@ -28285,7 +29193,16 @@
       <c r="N32" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="17" t="inlineStr"/>
+      <c r="O32" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 프로젝트 파일·폴더의 예상치 못한 변경(새 DLL·실행 파일, 해시 변화)을 감시하고 버전 관리 저장소의 승인 본과 비교
+- 엔지니어링 소프트웨어가 프로젝트를 열 때 만드는 비정상 자식 프로세스·DLL 로드를 EDR로 확인
+■ 대응
+- 프로젝트 파일을 접근 통제된 버전 관리 저장소에서 관리하고, 협력업체에서 받은 프로젝트는 검사한 뒤 반입
+- 엔지니어링 소프트웨어의 프로젝트 보호(암호·무결성) 기능을 켜고 최신 패치 적용</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -28308,9 +29225,10 @@
           <t>제어 프로그램 변조</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify or add a program on a controller to affect how it interacts with the physical process, peripheral devices and other hosts on the network.</t>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 프로그램을 바꾸거나 새 블록을 추가해, 제어기가 물리 공정·주변 장치·다른 호스트와 상호작용하는 방식을 바꾸고 그 상태로 오래 머물 수 있음
+- 바뀐 프로그램은 제어기를 재시작해도 그대로 실행되고, 엔지니어링 소프트웨어로 읽을 때 원래 코드를 보여주도록 숨길 수도 있어 오프라인 비교 없이는 찾기 어려움</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
@@ -28354,7 +29272,16 @@
       <c r="N33" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O33" s="17" t="inlineStr"/>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기에서 프로그램을 정기적으로 올려받아 승인 기준본과 블록 단위로 비교(체크섬·해시)하고, 온라인 편집·프로그램 추가 기능 코드를 OT 네트워크 감시로 탐지
+- 장치 변경 경보·진단 버퍼와 엔지니어링 소프트웨어 변경 기록을 수집해 변경 관리 기록과 대조
+■ 대응
+- 제어기 접근 보호(읽기·쓰기 암호)와 키 스위치 RUN을 유지하고, 프로그램 변경은 승인 후 지정 EWS에서만 수행
+- 코드 서명·무결성 검증을 지원하는 제어기를 도입하고 승인된 프로그램 백업을 오프라인으로 보관</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -28614,9 +29541,10 @@
           <t>취약한 자격증명 (일반·상위기법)</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may target insecure credentials as a means to persist on a system or device or move laterally from one system or device to another.</t>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치·소프트웨어에 미리 설정돼 공개된 기본 자격증명이나 펌웨어에 박힌 하드코딩 자격증명, 허술하게 저장된 자격증명을 써서, 계정을 탈취하지 않고도 제어 장치·서버에 로그인하고 머물거나 이동할 수 있음
+- 장치 교체 주기가 길고 일부 자격증명은 사용자가 바꿀 수 없어 노출 상태가 오래 이어지며, 로그인 자체는 정상이라 탐지가 어려움</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
@@ -28660,7 +29588,16 @@
       <c r="N37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="17" t="inlineStr"/>
+      <c r="O37" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 평문 인증 프로토콜(텔넷·FTP·HTTP)의 로그인과 알려진 기본 계정 사용을 OT 네트워크 감시로 탐지하고 장치 로그인 기록 수집
+- 자산 점검 때 자격증명 관련 CISA ICS·벤더 권고 해당 여부를 자산 목록과 대조
+■ 대응
+- 설치·인수 때 기본 자격증명을 바꾸고 장치별 고유 암호를 관리하며, 바꿀 수 없는 자격증명은 네트워크 분리·허용 목록으로 보완
+- 자격증명 저장 결함을 패치하고 암호화 통신(HTTPS·SSH)을 적용하며, 쓰지 않는 텔넷·FTP 서비스를 끔</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -28683,9 +29620,10 @@
           <t>기본 자격증명</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage manufacturer or supplier set default credentials on control system devices.</t>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제조사가 출하 때 설정해 매뉴얼·인터넷에 공개된 기본 계정·암호로 PLC·HMI·RTU·IoT 기기에 로그인해, 관리자 권한을 바로 얻고 설정·화면·프로그램을 바꿀 수 있음
+- 검색 엔진으로 노출 장치를 찾아 기본 암호를 넣는 것만으로 대규모 공격이 가능해, 숙련도가 낮은 핵티비스트와 IoT 봇넷이 가장 많이 쓰는 경로임</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
@@ -28729,7 +29667,16 @@
       <c r="N38" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O38" s="17" t="inlineStr"/>
+      <c r="O38" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 장치 로그인 기록과 OT 네트워크 감시로 기본 계정 이름의 로그인과 반복 로그인 시도를 탐지
+- 외부 공격 표면 점검과 내부 자산 점검으로 기본 암호가 남은 장치를 정기 확인
+■ 대응
+- 설치·인수 시험 항목에 기본 암호 변경을 넣고, 장치별 고유 암호를 암호 관리 도구로 관리
+- 첫 사용 때 암호 변경을 강제하는 제품을 우선 도입하고 장치의 인터넷 노출을 없앰</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -28752,9 +29699,10 @@
           <t>하드코딩 자격증명</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage credentials that are hardcoded in software or firmware to gain an unauthorized interactive user session to an asset.</t>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 소프트웨어·펌웨어에 박혀 있는 계정·암호·암호키를 찾아내, 같은 제품을 쓰는 모든 현장의 장치에 로그인하거나 엔지니어링 인증을 우회할 수 있음
+- 사용자가 바꾸거나 끌 수 없는 경우가 많아 패치 전까지 노출이 이어지고, 한 번 공개되면 같은 제품군 전체가 동시에 위험해짐</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr">
@@ -28798,7 +29746,16 @@
       <c r="N39" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O39" s="17" t="inlineStr"/>
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CISA ICS·벤더 권고의 하드코딩 자격증명 해당 제품을 자산 목록과 대조하고, 해당 계정·키를 쓰는 로그인을 OT 네트워크 감시 규칙으로 탐지
+- 엔지니어링 프로토콜 세션의 발신지를 지정 EWS 목록과 비교
+■ 대응
+- 벤더 패치·펌웨어 업데이트로 하드코딩 자격증명을 없애고, 패치 전에는 장치 접근을 허용 목록·네트워크 분리로 제한
+- 조달 요건에 하드코딩 자격증명 금지와 자격증명 변경 기능을 명시</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -28821,9 +29778,10 @@
           <t>예약 작업</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse task scheduling functionality to facilitate initial or recurring execution of malicious code.</t>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 작업 스케줄러·cron·네트워크 장비 예약 작업에 악성 명령을 등록해, 정한 시각에 실행하거나 재부팅 뒤에도 유지하고, 원격 호스트에 작업을 만들어 확산할 수 있음
+- 운영·백업 자동화용 예약 작업이 많아 새 작업이 눈에 띄지 않고, 파괴형 공격은 여러 호스트에서 같은 시각에 동시 실행되게 맞춰 복구를 어렵게 함</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -28867,7 +29825,16 @@
       <c r="N40" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O40" s="17" t="inlineStr"/>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 작업 스케줄러의 작업 생성·변경 이벤트와 원격 작업 생성(schtasks /s 등)을 수집하고, 승인된 예약 작업 목록과 정기 비교
+- 그룹 정책 변경과 방화벽·네트워크 장비의 예약 작업 설정 변경을 중앙 로그로 경보
+■ 대응
+- 예약 작업 생성 권한을 관리자 계정으로 제한하고, OT 도메인을 IT 도메인과 분리해 GPO 경유 일괄 배포를 막음
+- OT 호스트·경계 장비의 예약 작업을 변경 관리 대상으로 등록하고 설정 백업과 비교 점검</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
@@ -28890,9 +29857,10 @@
           <t>SQL 저장 프로시저</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse SQL stored procedures to establish persistent access to systems.</t>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 SCADA·히스토리언이 쓰는 MS-SQL 등 데이터베이스의 저장 프로시저(xp_cmdshell 등)를 악용하거나 새로 등록해, DB 서버에서 OS 명령을 실행하고 접근을 유지할 수 있음
+- DB는 SCADA 운영에 필수라 끌 수 없고, 저장 프로시저 실행은 DB 내부 활동이라 호스트 보안 도구가 잘 보지 못함</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -28936,7 +29904,16 @@
       <c r="N41" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O41" s="17" t="inlineStr"/>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- DB 감사로 xp_cmdshell 활성화·실행, 새 저장 프로시저·시작 프로시저 등록, 연결 서버 생성을 기록하고 경보
+- SQL 서버 프로세스가 명령 셸을 만드는 프로세스 체인을 EDR로 탐지
+■ 대응
+- xp_cmdshell 같은 위험 확장 프로시저를 끄고, SCADA·히스토리언 DB 계정을 최소 권한으로 운영하며 기본·공용 DB 계정 제거
+- DB 서버 접속을 OT 내부 지정 클라이언트로 제한하고 벤더 권고 보안 설정 적용</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -28959,9 +29936,10 @@
           <t>웹셸</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may backdoor web servers with web shells to establish persistent access to systems.</t>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 인터넷이나 OT 경계에 노출된 웹 서버에 웹셸을 심어, 이후 언제든 그 서버로 명령을 실행하고 내부망으로 터널을 뚫을 수 있음
+- 정상 웹 요청처럼 보이는 HTTP(S) 트래픽으로 동작하고 웹 서버 파일 하나만 남아, 처음 악용한 취약점을 패치한 뒤에도 접근이 유지됨</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
@@ -29005,7 +29983,16 @@
       <c r="N42" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O42" s="17" t="inlineStr"/>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 웹 서버 디렉터리의 새·변경 스크립트 파일을 파일 무결성 감시로 탐지하고, 웹 서버 프로세스가 명령 셸을 만들면 경보
+- 웹 로그에서 특정 파일로 반복되는 POST 요청과 HTTP 터널링 패턴 탐지
+■ 대응
+- OT 관련 웹 서버를 인터넷에서 분리하거나 WAF·리버스 프록시 뒤에 두고, 웹 루트 쓰기 권한을 제한
+- 침해 복구 때 패치와 함께 웹 서버 파일 전체의 무결성을 점검하거나 재구축</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -29028,9 +30015,10 @@
           <t>시스템 서비스 생성·변조</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may create or modify system-level processes to repeatedly execute malicious payloads as part of persistence.</t>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 Windows 서비스·Linux systemd 같은 시스템 서비스를 새로 만들거나 기존 서비스의 실행 경로를 바꿔, 부팅 때마다 높은 권한으로 악성 코드를 실행할 수 있음
+- OT 호스트에는 SCADA·통신 드라이버 같은 벤더 서비스가 많아 낯선 서비스가 섞여도 눈에 띄지 않고, 서명된 드라이버를 쓰면 정상 구성요소로 보임</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">
@@ -29074,7 +30062,16 @@
       <c r="N43" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="O43" s="17" t="inlineStr"/>
+      <c r="O43" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 생성·변경 이벤트(Windows 7045·4697, systemd 유닛 파일 변경)를 수집하고 승인된 서비스 목록과 정기 비교
+- 서비스 실행 파일의 경로·서명 변화와 PsExec 같은 원격 서비스 생성을 경보
+■ 대응
+- 서비스 생성·변경 권한을 관리자로 제한하고, 드라이버 서명 강제와 취약 드라이버 차단 목록 적용
+- 벤더 서비스 기준 목록을 자산 관리에 등록하고, 서비스 변경은 변경 관리로 승인</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -29097,9 +30094,10 @@
           <t>후킹</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may hook into application programming interface (API) functions used by processes to redirect calls for execution and privilege escalation means.</t>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 API 함수 주소·명령 처리기를 가로채거나 정상 프로세스에 코드를 주입해, 정상 기능이 호출될 때 자신의 코드가 먼저 실행되게 할 수 있음
+- 신뢰된 프로세스·펌웨어 안에서 실행돼 실행 주체가 정상으로 보이고, 반환값까지 바꿀 수 있어 감염 사실을 숨기는 데도 쓰임</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -29143,7 +30141,16 @@
       <c r="N44" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O44" s="17" t="inlineStr"/>
+      <c r="O44" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- EDR로 원격 스레드 생성·타 프로세스 메모리 쓰기 같은 주입 패턴과 엔지니어링 소프트웨어에 로드된 미서명 DLL 탐지(OT 벤더 호환성 확인 후 적용)
+- PLC·안전 제어기는 벤더 진단 도구로 펌웨어·메모리 무결성을 점검하고, 평소 쓰지 않는 진단 명령 사용을 OT 네트워크 감시로 확인
+■ 대응
+- 엔지니어링 소프트웨어·HMI 설치 경로의 쓰기 권한을 제한하고 DLL 서명 검증·애플리케이션 허용 목록 적용
+- 제어기 펌웨어 무결성 검증 기능을 켜고, 안전 제어기의 원격 프로그래밍은 운전 중 차단</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -29166,9 +30173,10 @@
           <t>권한 상승용 취약점 악용</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit software vulnerabilities in an attempt to elevate privileges.</t>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영체제·엔지니어링 소프트웨어·제어기 펌웨어의 취약점을 악용해, 일반 사용자 권한에서 관리자·커널·펌웨어 수준 권한으로 올라갈 수 있음
+- OT 호스트는 패치 주기가 길어 알려진 로컬 권한 상승 취약점이 오래 남고, 제어기 펌웨어 취약점은 공개와 패치 자체가 늦음</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr">
@@ -29212,7 +30220,16 @@
       <c r="N45" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O45" s="17" t="inlineStr"/>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 일반 계정 프로세스가 SYSTEM·root 권한 프로세스를 만들거나 알려진 취약 드라이버가 적재되면 EDR로 경보
+- 제어기는 벤더 진단으로 메모리·펌웨어 무결성을 점검하고, 비정상 재시작·오류 경보를 확인
+■ 대응
+- 로컬 권한 상승 취약점(KEV 우선)과 엔지니어링 소프트웨어 설치 폴더 권한 결함을 패치하고, 취약 드라이버 차단 목록 적용
+- 운영 계정에 관리자 권한을 주지 않고 애플리케이션 허용 목록·익스플로잇 보호를 적용</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
@@ -29235,9 +30252,10 @@
           <t>예약 작업</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may abuse task scheduling functionality to facilitate initial or recurring execution of malicious code.</t>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 작업 스케줄러·cron·네트워크 장비 예약 작업에 악성 명령을 등록해, 정한 시각에 실행하거나 재부팅 뒤에도 유지하고, 원격 호스트에 작업을 만들어 확산할 수 있음
+- 운영·백업 자동화용 예약 작업이 많아 새 작업이 눈에 띄지 않고, 파괴형 공격은 여러 호스트에서 같은 시각에 동시 실행되게 맞춰 복구를 어렵게 함</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
@@ -29281,7 +30299,16 @@
       <c r="N46" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O46" s="17" t="inlineStr"/>
+      <c r="O46" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 작업 스케줄러의 작업 생성·변경 이벤트와 원격 작업 생성(schtasks /s 등)을 수집하고, 승인된 예약 작업 목록과 정기 비교
+- 그룹 정책 변경과 방화벽·네트워크 장비의 예약 작업 설정 변경을 중앙 로그로 경보
+■ 대응
+- 예약 작업 생성 권한을 관리자 계정으로 제한하고, OT 도메인을 IT 도메인과 분리해 GPO 경유 일괄 배포를 막음
+- OT 호스트·경계 장비의 예약 작업을 변경 관리 대상으로 등록하고 설정 백업과 비교 점검</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
@@ -29304,9 +30331,10 @@
           <t>그룹 정책 변조</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify Group Policy Objects (GPOs) to subvert the intended discretionary access controls for a domain, usually with the intention of escalating privileges on the domain.</t>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 도메인 관리자 권한으로 그룹 정책 개체(GPO)를 바꿔, 도메인에 속한 OT 호스트 전체에 악성 코드 실행·보안 설정 해제를 한 번에 내릴 수 있음
+- 정상 관리 기능으로 많은 호스트에 동시에 적용돼 파괴형 공격이 매우 빠르게 퍼지고, OT 호스트가 IT 도메인에 묶여 있으면 IT 침해가 그대로 OT로 번짐</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr">
@@ -29350,7 +30378,16 @@
       <c r="N47" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O47" s="17" t="inlineStr"/>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- GPO 생성·변경 이벤트(디렉터리 서비스 변경 감사 5136 등)와 SYSVOL의 새 스크립트·예약 작업 파일을 감시하고 근무 외 변경을 경보
+- GPO 변경 직후 다수 호스트에서 같은 프로세스가 동시에 생기는 패턴을 상관 분석
+■ 대응
+- OT를 별도 도메인으로 운영해 IT 도메인과의 신뢰 관계를 최소화하고, GPO 편집 권한을 소수 계정으로 제한
+- 도메인 관리자 계정을 특권 접근 관리·다중 인증으로 보호하고, GPO 백업으로 변경 시 즉시 복원</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -29373,9 +30410,10 @@
           <t>시스템 서비스 생성·변조</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may create or modify system-level processes to repeatedly execute malicious payloads as part of persistence.</t>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 Windows 서비스·Linux systemd 같은 시스템 서비스를 새로 만들거나 기존 서비스의 실행 경로를 바꿔, 부팅 때마다 높은 권한으로 악성 코드를 실행할 수 있음
+- OT 호스트에는 SCADA·통신 드라이버 같은 벤더 서비스가 많아 낯선 서비스가 섞여도 눈에 띄지 않고, 서명된 드라이버를 쓰면 정상 구성요소로 보임</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
@@ -29419,7 +30457,16 @@
       <c r="N48" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="O48" s="17" t="inlineStr"/>
+      <c r="O48" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 서비스 생성·변경 이벤트(Windows 7045·4697, systemd 유닛 파일 변경)를 수집하고 승인된 서비스 목록과 정기 비교
+- 서비스 실행 파일의 경로·서명 변화와 PsExec 같은 원격 서비스 생성을 경보
+■ 대응
+- 서비스 생성·변경 권한을 관리자로 제한하고, 드라이버 서명 강제와 취약 드라이버 차단 목록 적용
+- 벤더 서비스 기준 목록을 자산 관리에 등록하고, 서비스 변경은 변경 관리로 승인</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
@@ -29442,9 +30489,10 @@
           <t>회피용 취약점 악용</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may exploit a software vulnerability to take advantage of a programming error in a program, service, or within the operating system software or kernel itself to evade detection.</t>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 소프트웨어·펌웨어 취약점을 악용해 장치의 무결성 점검·보안 기능을 끄거나 우회해, 심어 둔 코드가 발견되지 않게 할 수 있음
+- 안전 제어기처럼 펌웨어·프로그램 체크섬을 계속 확인하는 장치도 점검 루틴 자체가 무력화되면 이상을 보고하지 못함</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr">
@@ -29488,7 +30536,16 @@
       <c r="N49" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O49" s="17" t="inlineStr"/>
+      <c r="O49" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 제어기 진단 정보(펌웨어·프로그램 체크섬, 자체 진단 상태)를 정기 수집해 점검 기능이 꺼지거나 값이 멈추면 경보
+- EWS·HMI에서는 보안 기능 해제·커널 드라이버 적재 같은 이상을 EDR로 확인
+■ 대응
+- 장치 펌웨어·OS를 패치하고, 무결성 점검 결과를 장치 밖의 별도 감시 시스템에서 교차 확인
+- 안전 제어기 키 스위치를 RUN에 두어 메모리 쓰기 경로를 막고, 펌웨어 업데이트는 서명 검증을 거침</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -29511,9 +30568,10 @@
           <t>위장</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may use masquerading to disguise a malicious application or executable as another file, to avoid operator and engineer suspicion.</t>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 악성 파일·서비스·계정을 벤더 프로그램·업데이트 파일·전력 프로토콜 이름처럼 꾸며, 운영자와 엔지니어가 정상 구성요소로 여기게 할 수 있음
+- OT 호스트에는 벤더별 실행 파일·서비스가 많아 이름만으로 정상 여부를 가리기 어렵고, 탈취한 인증서로 서명하면 서명 검증도 통과함</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -29557,7 +30615,16 @@
       <c r="N50" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="O50" s="17" t="inlineStr"/>
+      <c r="O50" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 벤더 소프트웨어의 실행 파일·DLL·서비스 목록과 해시·서명 기준선을 만들어, 같은 이름인데 해시·경로·서명자가 다르면 경보
+- 확장자와 실제 형식이 다른 파일, 기존 것과 철자가 비슷한 새 서비스·계정 확인
+■ 대응
+- 해시·서명자 기준 애플리케이션 허용 목록을 적용하고 벤더 설치 경로의 쓰기 권한을 제한
+- 탈취·폐기된 코드 서명 인증서를 신뢰 목록에서 빼고, 경계 장비 규칙은 변경 관리 기록과 대조</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -29659,9 +30726,10 @@
           <t>운전 모드 변경</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may change the operating mode of a controller to gain additional access to engineering functions such as Program Download.</t>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제어기의 운전 모드를 RUN에서 PROGRAM·STOP·REMOTE로 바꿔, 프로그램 다운로드·메모리 쓰기 같은 엔지니어링 기능을 열거나 제어 로직 실행을 멈출 수 있음
+- 키 스위치를 원격 변경이 가능한 위치에 둔 채 운영하는 경우가 흔해 프로토콜 명령만으로 모드가 바뀌고, 모드 변경을 기록·경보하지 않는 장치도 많음</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
@@ -29705,7 +30773,16 @@
       <c r="N52" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O52" s="17" t="inlineStr"/>
+      <c r="O52" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 운전 모드를 바꾸는 기능 코드(정지·실행·모드 전환)를 OT 네트워크 감시로 탐지하고, 장치 이벤트 로그·진단 버퍼의 모드 변경 기록 수집
+- 키 스위치 위치를 감시 신호로 HMI·SCADA에 올려, PROGRAM·REMOTE 상태가 작업 일정 밖에 나타나거나 오래 유지되면 경보
+■ 대응
+- 정상 운전 중에는 키 스위치를 RUN(잠금)에 두고 키를 관리하며, 모드 변경은 변경 관리 절차로 승인
+- 엔지니어링 프로토콜 접근을 지정 EWS로 제한하고 제어기 접근 암호·인증 기능을 켬</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -29728,9 +30805,10 @@
           <t>호스트 흔적 삭제</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may attempt to remove indicators of their presence on a system in an effort to cover their tracks.</t>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 이벤트 로그·악성 파일·저장 프로시저를 지우거나 파일 시각을 바꾸고, 제어기를 원래 상태로 되돌려 침입 흔적을 감출 수 있음
+- OT 장치는 로그 보존 용량이 작고 중앙 수집이 안 된 경우가 많아, 현장에서 지우면 사고 원인 분석 자체가 어려워짐</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
@@ -29774,7 +30852,16 @@
       <c r="N53" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="O53" s="17" t="inlineStr"/>
+      <c r="O53" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 호스트·장비 로그를 실시간으로 중앙 수집해 현장 삭제와 무관하게 보존하고, 로그 삭제 이벤트(Windows 1102·104)와 로그 공백을 경보
+- 제어기 프로그램·메모리 변경과 예기치 않은 리셋·재시작을 진단 정보로 확인
+■ 대응
+- 로그 저장소 권한을 분리하고 장치 로그를 원격 syslog로 보내며, 보존 기간을 사고 조사 요건에 맞춤
+- 사고 대응 계획에 OT 포렌식 절차(메모리·프로그램 확보 순서)를 넣고 승인된 프로그램 기준본을 보관</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -29797,9 +30884,10 @@
           <t>시스템 바이너리 대리 실행</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may bypass process and/or signature-based defenses by proxying execution of malicious content with signed, or otherwise trusted, binaries.</t>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 운영체제·SCADA 소프트웨어에 들어 있는 신뢰된 바이너리(rundll32·msiexec·SCADA 명령 도구)로 악성 코드나 명령을 대신 실행시켜, 실행 파일 기반 방어를 우회할 수 있음
+- 실행 주체가 마이크로소프트·벤더 서명 프로그램이라 허용 목록과 서명 검사를 통과하고, SCADA 도구를 쓰면 제어 명령까지 정상 경로로 나감</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
@@ -29843,7 +30931,16 @@
       <c r="N54" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="O54" s="17" t="inlineStr"/>
+      <c r="O54" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- rundll32·msiexec가 사용자 폴더·임시 경로의 DLL·패키지를 실행하거나 외부 연결을 만들면 EDR로 경보
+- SCADA 명령 도구의 실행 인자·호출 주체를 기록하고, 운영 절차에 없는 명령 파일 실행을 경보
+■ 대응
+- OT 호스트에서 쓰지 않는 시스템 바이너리 실행을 허용 목록으로 제한하고, SCADA 명령 도구는 지정 계정·경로에서만 실행되게 함
+- SCADA 소프트웨어의 스크립트·명령 실행 권한을 역할별로 나누고 실행 기록을 남김</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -30024,9 +31121,10 @@
           <t>그룹 정책 변조</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may modify Group Policy Objects (GPOs) to subvert the intended discretionary access controls for a domain, usually with the intention of escalating privileges on the domain.</t>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 도메인 관리자 권한으로 그룹 정책 개체(GPO)를 바꿔, 도메인에 속한 OT 호스트 전체에 악성 코드 실행·보안 설정 해제를 한 번에 내릴 수 있음
+- 정상 관리 기능으로 많은 호스트에 동시에 적용돼 파괴형 공격이 매우 빠르게 퍼지고, OT 호스트가 IT 도메인에 묶여 있으면 IT 침해가 그대로 OT로 번짐</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
@@ -30070,7 +31168,16 @@
       <c r="N57" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O57" s="17" t="inlineStr"/>
+      <c r="O57" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- GPO 생성·변경 이벤트(디렉터리 서비스 변경 감사 5136 등)와 SYSVOL의 새 스크립트·예약 작업 파일을 감시하고 근무 외 변경을 경보
+- GPO 변경 직후 다수 호스트에서 같은 프로세스가 동시에 생기는 패턴을 상관 분석
+■ 대응
+- OT를 별도 도메인으로 운영해 IT 도메인과의 신뢰 관계를 최소화하고, GPO 편집 권한을 소수 계정으로 제한
+- 도메인 관리자 계정을 특권 접근 관리·다중 인증으로 보호하고, GPO 백업으로 변경 시 즉시 복원</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
@@ -30093,9 +31200,10 @@
           <t>보안 도구 무력화</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may disable, degrade, or tamper with security tools or applications (e.g., endpoint detection and response (EDR) tools, intrusion detection systems (IDS), antivirus, logging agents, sensors, etc.) to impair or reduce visibility of defensive capabi…</t>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 백신·EDR·로그 수집 에이전트·OT 보안 센서를 멈추거나 설정을 바꿔, 이후 행위가 기록·탐지되지 않게 할 수 있음
+- OT 호스트의 보안 도구는 운영 영향을 우려한 예외 설정이 많고 중앙 관리가 약해, 꺼져도 오랫동안 알아채지 못하는 경우가 많음</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
@@ -30139,7 +31247,16 @@
       <c r="N58" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="O58" s="17" t="inlineStr"/>
+      <c r="O58" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 에이전트의 상태 신호가 끊기거나 서비스가 멈추면 중앙 관리 콘솔에서 경보하고, 로깅 정책 변경 이벤트를 수집
+- OT 네트워크 감시 센서의 수신 트래픽이 갑자기 줄거나 끊기면 확인
+■ 대응
+- 보안 도구의 변조 방지 기능을 켜고, 중지·제거 권한을 별도 관리자 계정으로 제한
+- 보안 도구 예외 설정을 정기 검토하고, 로깅 설정은 그룹 정책·구성 관리로 강제</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
@@ -30162,9 +31279,10 @@
           <t>경계 장비 보안 설정 변조</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may disable network device-based firewall mechanisms entirely or add, delete, or modify particular rules in order to bypass controls limiting network usage.</t>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 OT 경계 방화벽·VPN 장비의 접근 규칙·보안 설정·다중 인증 설정을 바꾸거나 트래픽 로깅을 꺼, 막혀 있던 통신을 열고 자신의 접근을 감출 수 있음
+- 경계 장비 하나의 설정이 IT·OT 분리를 좌우하므로 규칙 하나만 바뀌어도 망 분리가 무력화되고, 장비 로그를 끄면 이후 행위가 남지 않음</t>
         </is>
       </c>
       <c r="F59" s="17" t="inlineStr">
@@ -30208,7 +31326,16 @@
       <c r="N59" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="O59" s="17" t="inlineStr"/>
+      <c r="O59" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 경계 장비 설정을 정기 백업해 승인 기준본과 비교하고, 규칙·인증·로깅 설정 변경 이벤트를 외부 로그 서버로 보내 경보
+- 장비 로그 전송이 갑자기 끊기거나 줄면 로깅 해제 징후로 확인
+■ 대응
+- 경계 장비 관리 접속을 관리망·다중 인증으로 제한하고, 설정 변경은 변경 관리 승인 뒤 수행
+- 장비 펌웨어를 최신으로 유지하고(KEV 등재 취약점 우선), 관리 계정을 개인별로 나눠 변경 이력을 추적</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
@@ -31059,9 +32186,10 @@
           <t>유효 계정 악용</t>
         </is>
       </c>
-      <c r="E72" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may steal the credentials of a specific user or service account using credential access techniques.</t>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취하거나 새로 만든 유효 계정(도메인·로컬·서비스·장치 계정)으로 VPN·원격 서비스·제어 장치에 로그인해, 정상 사용자 권한으로 OT 환경에 머물고 이동할 수 있음
+- 인증을 정상 통과하므로 접근 통제와 다수 탐지 수단을 그대로 지나치며, 퇴사자·휴면·공용 계정 관리가 허술한 OT 환경에서 반복적으로 악용됨</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -31105,7 +32233,16 @@
       <c r="N72" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="O72" s="17" t="inlineStr"/>
+      <c r="O72" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- OT 계정의 로그인 시간·출발지·대상 장치를 기준선과 비교하고, 휴면·퇴사자·서비스 계정의 대화형 로그인과 새 관리자 계정 생성을 경보
+- 현장 장치(RTU·계전기·시리얼 서버) 로그인 기록을 VPN·점프 호스트 세션과 상관 분석해 승인된 원격 세션 없이 일어난 장치 접근 확인
+■ 대응
+- OT 계정·도메인을 IT와 분리하고, 원격·특권 접근에 다중 인증과 승인 기반 일시 권한(JIT)을 적용
+- 퇴사·계약 종료 때 원격 접속 계정을 즉시 폐기하고, 공용 계정을 개인 계정으로 바꾸며 계정 목록을 정기 검토</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="17" t="inlineStr">
@@ -31355,9 +32492,10 @@
           <t>취약한 자격증명 (일반·상위기법)</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may target insecure credentials as a means to persist on a system or device or move laterally from one system or device to another.</t>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 장치·소프트웨어에 미리 설정돼 공개된 기본 자격증명이나 펌웨어에 박힌 하드코딩 자격증명, 허술하게 저장된 자격증명을 써서, 계정을 탈취하지 않고도 제어 장치·서버에 로그인하고 머물거나 이동할 수 있음
+- 장치 교체 주기가 길고 일부 자격증명은 사용자가 바꿀 수 없어 노출 상태가 오래 이어지며, 로그인 자체는 정상이라 탐지가 어려움</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
@@ -31401,7 +32539,16 @@
       <c r="N76" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="O76" s="17" t="inlineStr"/>
+      <c r="O76" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 평문 인증 프로토콜(텔넷·FTP·HTTP)의 로그인과 알려진 기본 계정 사용을 OT 네트워크 감시로 탐지하고 장치 로그인 기록 수집
+- 자산 점검 때 자격증명 관련 CISA ICS·벤더 권고 해당 여부를 자산 목록과 대조
+■ 대응
+- 설치·인수 때 기본 자격증명을 바꾸고 장치별 고유 암호를 관리하며, 바꿀 수 없는 자격증명은 네트워크 분리·허용 목록으로 보완
+- 자격증명 저장 결함을 패치하고 암호화 통신(HTTPS·SSH)을 적용하며, 쓰지 않는 텔넷·FTP 서비스를 끔</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
@@ -31424,9 +32571,10 @@
           <t>기본 자격증명</t>
         </is>
       </c>
-      <c r="E77" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage manufacturer or supplier set default credentials on control system devices.</t>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 제조사가 출하 때 설정해 매뉴얼·인터넷에 공개된 기본 계정·암호로 PLC·HMI·RTU·IoT 기기에 로그인해, 관리자 권한을 바로 얻고 설정·화면·프로그램을 바꿀 수 있음
+- 검색 엔진으로 노출 장치를 찾아 기본 암호를 넣는 것만으로 대규모 공격이 가능해, 숙련도가 낮은 핵티비스트와 IoT 봇넷이 가장 많이 쓰는 경로임</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr">
@@ -31470,7 +32618,16 @@
       <c r="N77" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O77" s="17" t="inlineStr"/>
+      <c r="O77" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 장치 로그인 기록과 OT 네트워크 감시로 기본 계정 이름의 로그인과 반복 로그인 시도를 탐지
+- 외부 공격 표면 점검과 내부 자산 점검으로 기본 암호가 남은 장치를 정기 확인
+■ 대응
+- 설치·인수 시험 항목에 기본 암호 변경을 넣고, 장치별 고유 암호를 암호 관리 도구로 관리
+- 첫 사용 때 암호 변경을 강제하는 제품을 우선 도입하고 장치의 인터넷 노출을 없앰</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="17" t="inlineStr">
@@ -31493,9 +32650,10 @@
           <t>하드코딩 자격증명</t>
         </is>
       </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>(작성 예정) Adversaries may leverage credentials that are hardcoded in software or firmware to gain an unauthorized interactive user session to an asset.</t>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>- 공격자는 소프트웨어·펌웨어에 박혀 있는 계정·암호·암호키를 찾아내, 같은 제품을 쓰는 모든 현장의 장치에 로그인하거나 엔지니어링 인증을 우회할 수 있음
+- 사용자가 바꾸거나 끌 수 없는 경우가 많아 패치 전까지 노출이 이어지고, 한 번 공개되면 같은 제품군 전체가 동시에 위험해짐</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -31539,7 +32697,16 @@
       <c r="N78" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="O78" s="17" t="inlineStr"/>
+      <c r="O78" s="17" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- CISA ICS·벤더 권고의 하드코딩 자격증명 해당 제품을 자산 목록과 대조하고, 해당 계정·키를 쓰는 로그인을 OT 네트워크 감시 규칙으로 탐지
+- 엔지니어링 프로토콜 세션의 발신지를 지정 EWS 목록과 비교
+■ 대응
+- 벤더 패치·펌웨어 업데이트로 하드코딩 자격증명을 없애고, 패치 전에는 장치 접근을 허용 목록·네트워크 분리로 제한
+- 조달 요건에 하드코딩 자격증명 금지와 자격증명 변경 기능을 명시</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
